--- a/excel-final/Esquema de Direccionamiento IP.xlsx
+++ b/excel-final/Esquema de Direccionamiento IP.xlsx
@@ -784,34 +784,34 @@
     <t>10.192.45.31</t>
   </si>
   <si>
+    <t>/29</t>
+  </si>
+  <si>
+    <t>255.255.255.248</t>
+  </si>
+  <si>
     <t>10.192.45.32</t>
   </si>
   <si>
     <t>10.192.45.33</t>
   </si>
   <si>
+    <t>10.192.45.38</t>
+  </si>
+  <si>
+    <t>10.192.45.39</t>
+  </si>
+  <si>
+    <t>10.192.45.40</t>
+  </si>
+  <si>
+    <t>10.192.45.41</t>
+  </si>
+  <si>
     <t>10.192.45.46</t>
   </si>
   <si>
     <t>10.192.45.47</t>
-  </si>
-  <si>
-    <t>/29</t>
-  </si>
-  <si>
-    <t>255.255.255.248</t>
-  </si>
-  <si>
-    <t>10.192.45.48</t>
-  </si>
-  <si>
-    <t>10.192.45.49</t>
-  </si>
-  <si>
-    <t>10.192.45.54</t>
-  </si>
-  <si>
-    <t>10.192.45.55</t>
   </si>
   <si>
     <t>Validacion:</t>
@@ -1157,7 +1157,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -1193,10 +1193,6 @@
     </font>
     <font/>
     <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <b/>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -1214,7 +1210,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1231,12 +1227,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor theme="0"/>
       </patternFill>
     </fill>
     <fill>
@@ -1296,7 +1286,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="35">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1368,57 +1358,30 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
@@ -3134,542 +3097,572 @@
         <v>226</v>
       </c>
       <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
     </row>
     <row r="2">
       <c r="A2" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-      <c r="J2" s="27"/>
-      <c r="K2" s="27"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="27"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
     </row>
     <row r="3">
       <c r="A3" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
     </row>
     <row r="4">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
     </row>
     <row r="5">
-      <c r="A5" s="27"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="D6" s="28" t="s">
+      <c r="D6" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="E6" s="28" t="s">
+      <c r="E6" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="28" t="s">
+      <c r="F6" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="G6" s="28" t="s">
+      <c r="G6" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="H6" s="28" t="s">
+      <c r="H6" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="28" t="s">
+      <c r="I6" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="J6" s="28" t="s">
+      <c r="J6" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="28" t="s">
+      <c r="K6" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="28" t="s">
+      <c r="L6" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="28" t="s">
+      <c r="M6" s="30" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>70.0</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>88.0</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>30.0</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>7.0</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <v>126.0</v>
       </c>
-      <c r="H7" s="30" t="s">
+      <c r="H7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="I7" s="30" t="s">
+      <c r="I7" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="J7" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="K7" s="30" t="s">
+      <c r="K7" s="31" t="s">
         <v>101</v>
       </c>
-      <c r="L7" s="30" t="s">
+      <c r="L7" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="M7" s="30" t="s">
+      <c r="M7" s="31" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>35.0</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>44.0</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>31.0</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>6.0</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <v>62.0</v>
       </c>
-      <c r="H8" s="30" t="s">
+      <c r="H8" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="I8" s="30" t="s">
+      <c r="I8" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="J8" s="30" t="s">
+      <c r="J8" s="31" t="s">
         <v>231</v>
       </c>
-      <c r="K8" s="30" t="s">
+      <c r="K8" s="31" t="s">
         <v>232</v>
       </c>
-      <c r="L8" s="30" t="s">
+      <c r="L8" s="31" t="s">
         <v>233</v>
       </c>
-      <c r="M8" s="30" t="s">
+      <c r="M8" s="31" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <v>15.0</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>19.0</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="D9" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>32.0</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>5.0</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <v>30.0</v>
       </c>
-      <c r="H9" s="30" t="s">
+      <c r="H9" s="31" t="s">
         <v>205</v>
       </c>
-      <c r="I9" s="30" t="s">
+      <c r="I9" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="J9" s="30" t="s">
+      <c r="J9" s="31" t="s">
         <v>235</v>
       </c>
-      <c r="K9" s="30" t="s">
+      <c r="K9" s="31" t="s">
         <v>236</v>
       </c>
-      <c r="L9" s="30" t="s">
+      <c r="L9" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="M9" s="30" t="s">
+      <c r="M9" s="31" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="s">
+      <c r="A10" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <v>11.0</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>14.0</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="D10" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>33.0</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>4.0</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="31">
         <v>14.0</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="H10" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="I10" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J10" s="30" t="s">
+      <c r="J10" s="31" t="s">
         <v>239</v>
       </c>
-      <c r="K10" s="30" t="s">
+      <c r="K10" s="31" t="s">
         <v>240</v>
       </c>
-      <c r="L10" s="30" t="s">
+      <c r="L10" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="M10" s="30" t="s">
+      <c r="M10" s="31" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="31" t="s">
         <v>191</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <v>10.0</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>13.0</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>34.0</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>4.0</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="31">
         <v>14.0</v>
       </c>
-      <c r="H11" s="30" t="s">
+      <c r="H11" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I11" s="30" t="s">
+      <c r="I11" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J11" s="30" t="s">
+      <c r="J11" s="31" t="s">
         <v>243</v>
       </c>
-      <c r="K11" s="30" t="s">
+      <c r="K11" s="31" t="s">
         <v>244</v>
       </c>
-      <c r="L11" s="30" t="s">
+      <c r="L11" s="31" t="s">
         <v>245</v>
       </c>
-      <c r="M11" s="30" t="s">
+      <c r="M11" s="31" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="s">
+      <c r="A12" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <v>9.0</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>12.0</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D12" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>35.0</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>4.0</v>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="31">
         <v>14.0</v>
       </c>
-      <c r="H12" s="30" t="s">
+      <c r="H12" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I12" s="30" t="s">
+      <c r="I12" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J12" s="30" t="s">
+      <c r="J12" s="31" t="s">
         <v>247</v>
       </c>
-      <c r="K12" s="30" t="s">
+      <c r="K12" s="31" t="s">
         <v>248</v>
       </c>
-      <c r="L12" s="30" t="s">
+      <c r="L12" s="31" t="s">
         <v>249</v>
       </c>
-      <c r="M12" s="30" t="s">
+      <c r="M12" s="31" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="31" t="s">
         <v>203</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <v>6.0</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>8.0</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>36.0</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>4.0</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <v>14.0</v>
       </c>
-      <c r="H13" s="30" t="s">
+      <c r="H13" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I13" s="30" t="s">
+      <c r="I13" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J13" s="30" t="s">
+      <c r="J13" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="K13" s="30" t="s">
+      <c r="K13" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="L13" s="30" t="s">
+      <c r="L13" s="31" t="s">
         <v>253</v>
       </c>
-      <c r="M13" s="30" t="s">
+      <c r="M13" s="31" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="s">
+      <c r="A14" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="B14" s="30">
-        <v>5.0</v>
-      </c>
-      <c r="C14" s="30">
-        <v>7.0</v>
-      </c>
-      <c r="D14" s="30" t="s">
+      <c r="B14" s="31">
+        <v>2.0</v>
+      </c>
+      <c r="C14" s="31">
+        <v>3.0</v>
+      </c>
+      <c r="D14" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>99.0</v>
       </c>
-      <c r="F14" s="30">
-        <v>4.0</v>
-      </c>
-      <c r="G14" s="30">
-        <v>14.0</v>
-      </c>
-      <c r="H14" s="30" t="s">
-        <v>219</v>
-      </c>
-      <c r="I14" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="J14" s="30" t="s">
+      <c r="F14" s="31">
+        <v>3.0</v>
+      </c>
+      <c r="G14" s="31">
+        <v>6.0</v>
+      </c>
+      <c r="H14" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="K14" s="30" t="s">
+      <c r="I14" s="31" t="s">
         <v>256</v>
       </c>
-      <c r="L14" s="30" t="s">
+      <c r="J14" s="31" t="s">
         <v>257</v>
       </c>
-      <c r="M14" s="30" t="s">
+      <c r="K14" s="31" t="s">
         <v>258</v>
       </c>
+      <c r="L14" s="31" t="s">
+        <v>259</v>
+      </c>
+      <c r="M14" s="31" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="B15" s="30">
-        <v>4.0</v>
-      </c>
-      <c r="C15" s="30">
-        <v>5.0</v>
-      </c>
-      <c r="D15" s="30" t="s">
+      <c r="B15" s="31">
+        <v>2.0</v>
+      </c>
+      <c r="C15" s="31">
+        <v>3.0</v>
+      </c>
+      <c r="D15" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>37.0</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>3.0</v>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="31">
         <v>6.0</v>
       </c>
-      <c r="H15" s="30" t="s">
-        <v>259</v>
-      </c>
-      <c r="I15" s="30" t="s">
-        <v>260</v>
-      </c>
-      <c r="J15" s="30" t="s">
+      <c r="H15" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="I15" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="J15" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="K15" s="30" t="s">
+      <c r="K15" s="31" t="s">
         <v>262</v>
       </c>
-      <c r="L15" s="30" t="s">
+      <c r="L15" s="31" t="s">
         <v>263</v>
       </c>
-      <c r="M15" s="30" t="s">
+      <c r="M15" s="31" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="31" t="s">
+      <c r="A16" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="B16" s="28">
-        <v>165.0</v>
-      </c>
-      <c r="C16" s="28">
-        <v>210.0</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="33">
-        <v>294.0</v>
-      </c>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="32"/>
-      <c r="L16" s="32"/>
-      <c r="M16" s="32"/>
+      <c r="B16" s="32">
+        <f>SUM(B7:B15)</f>
+        <v>160</v>
+      </c>
+      <c r="C16" s="32">
+        <v>204.0</v>
+      </c>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="32">
+        <v>286.0</v>
+      </c>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
     </row>
     <row r="17">
-      <c r="A17" s="32"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="32"/>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="29" t="s">
         <v>266</v>
       </c>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:D1"/>
+  </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3695,3045 +3688,3045 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="C1" s="36"/>
+      <c r="C1" s="27"/>
       <c r="D1" s="18"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="37"/>
-      <c r="AG1" s="37"/>
-      <c r="AH1" s="37"/>
-      <c r="AI1" s="37"/>
-      <c r="AJ1" s="37"/>
-      <c r="AK1" s="37"/>
-      <c r="AL1" s="37"/>
-      <c r="AM1" s="37"/>
-      <c r="AN1" s="37"/>
-      <c r="AO1" s="37"/>
-      <c r="AP1" s="37"/>
-      <c r="AQ1" s="37"/>
-      <c r="AR1" s="37"/>
-      <c r="AS1" s="37"/>
-      <c r="AT1" s="37"/>
-      <c r="AU1" s="37"/>
-      <c r="AV1" s="37"/>
-      <c r="AW1" s="37"/>
-      <c r="AX1" s="37"/>
-      <c r="AY1" s="37"/>
-      <c r="AZ1" s="37"/>
-      <c r="BA1" s="37"/>
-      <c r="BB1" s="37"/>
-      <c r="BC1" s="37"/>
-      <c r="BD1" s="37"/>
-      <c r="BE1" s="37"/>
-      <c r="BF1" s="37"/>
-      <c r="BG1" s="37"/>
-      <c r="BH1" s="37"/>
-      <c r="BI1" s="37"/>
-      <c r="BJ1" s="37"/>
-      <c r="BK1" s="37"/>
-      <c r="BL1" s="37"/>
-      <c r="BM1" s="37"/>
-      <c r="BN1" s="37"/>
-      <c r="BO1" s="37"/>
-      <c r="BP1" s="37"/>
-      <c r="BQ1" s="37"/>
-      <c r="BR1" s="37"/>
-      <c r="BS1" s="37"/>
-      <c r="BT1" s="37"/>
-      <c r="BU1" s="37"/>
-      <c r="BV1" s="37"/>
-      <c r="BW1" s="37"/>
-      <c r="BX1" s="37"/>
-      <c r="BY1" s="37"/>
-      <c r="BZ1" s="37"/>
-      <c r="CA1" s="37"/>
-      <c r="CB1" s="37"/>
-      <c r="CC1" s="37"/>
-      <c r="CD1" s="37"/>
-      <c r="CE1" s="37"/>
-      <c r="CF1" s="37"/>
-      <c r="CG1" s="37"/>
-      <c r="CH1" s="37"/>
-      <c r="CI1" s="37"/>
-      <c r="CJ1" s="37"/>
-      <c r="CK1" s="37"/>
-      <c r="CL1" s="37"/>
-      <c r="CM1" s="37"/>
-      <c r="CN1" s="37"/>
-      <c r="CO1" s="37"/>
-      <c r="CP1" s="37"/>
-      <c r="CQ1" s="37"/>
-      <c r="CR1" s="37"/>
-      <c r="CS1" s="37"/>
-      <c r="CT1" s="37"/>
-      <c r="CU1" s="37"/>
-      <c r="CV1" s="37"/>
-      <c r="CW1" s="37"/>
-      <c r="CX1" s="37"/>
-      <c r="CY1" s="37"/>
-      <c r="CZ1" s="37"/>
-      <c r="DA1" s="37"/>
-      <c r="DB1" s="37"/>
-      <c r="DC1" s="37"/>
-      <c r="DD1" s="37"/>
-      <c r="DE1" s="37"/>
-      <c r="DF1" s="37"/>
-      <c r="DG1" s="37"/>
-      <c r="DH1" s="37"/>
-      <c r="DI1" s="37"/>
-      <c r="DJ1" s="37"/>
-      <c r="DK1" s="37"/>
-      <c r="DL1" s="37"/>
-      <c r="DM1" s="37"/>
-      <c r="DN1" s="37"/>
-      <c r="DO1" s="37"/>
-      <c r="DP1" s="37"/>
-      <c r="DQ1" s="37"/>
-      <c r="DR1" s="37"/>
-      <c r="DS1" s="37"/>
-      <c r="DT1" s="37"/>
-      <c r="DU1" s="37"/>
-      <c r="DV1" s="37"/>
-      <c r="DW1" s="37"/>
-      <c r="DX1" s="37"/>
-      <c r="DY1" s="37"/>
-      <c r="DZ1" s="37"/>
-      <c r="EA1" s="37"/>
-      <c r="EB1" s="37"/>
-      <c r="EC1" s="37"/>
-      <c r="ED1" s="37"/>
-      <c r="EE1" s="37"/>
-      <c r="EF1" s="37"/>
-      <c r="EG1" s="37"/>
-      <c r="EH1" s="37"/>
-      <c r="EI1" s="37"/>
-      <c r="EJ1" s="37"/>
-      <c r="EK1" s="37"/>
-      <c r="EL1" s="37"/>
-      <c r="EM1" s="37"/>
-      <c r="EN1" s="37"/>
-      <c r="EO1" s="37"/>
-      <c r="EP1" s="37"/>
-      <c r="EQ1" s="37"/>
-      <c r="ER1" s="37"/>
-      <c r="ES1" s="37"/>
-      <c r="ET1" s="37"/>
-      <c r="EU1" s="37"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
+      <c r="S1" s="28"/>
+      <c r="T1" s="28"/>
+      <c r="U1" s="28"/>
+      <c r="V1" s="28"/>
+      <c r="W1" s="28"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
+      <c r="AA1" s="28"/>
+      <c r="AB1" s="28"/>
+      <c r="AC1" s="28"/>
+      <c r="AD1" s="28"/>
+      <c r="AE1" s="28"/>
+      <c r="AF1" s="28"/>
+      <c r="AG1" s="28"/>
+      <c r="AH1" s="28"/>
+      <c r="AI1" s="28"/>
+      <c r="AJ1" s="28"/>
+      <c r="AK1" s="28"/>
+      <c r="AL1" s="28"/>
+      <c r="AM1" s="28"/>
+      <c r="AN1" s="28"/>
+      <c r="AO1" s="28"/>
+      <c r="AP1" s="28"/>
+      <c r="AQ1" s="28"/>
+      <c r="AR1" s="28"/>
+      <c r="AS1" s="28"/>
+      <c r="AT1" s="28"/>
+      <c r="AU1" s="28"/>
+      <c r="AV1" s="28"/>
+      <c r="AW1" s="28"/>
+      <c r="AX1" s="28"/>
+      <c r="AY1" s="28"/>
+      <c r="AZ1" s="28"/>
+      <c r="BA1" s="28"/>
+      <c r="BB1" s="28"/>
+      <c r="BC1" s="28"/>
+      <c r="BD1" s="28"/>
+      <c r="BE1" s="28"/>
+      <c r="BF1" s="28"/>
+      <c r="BG1" s="28"/>
+      <c r="BH1" s="28"/>
+      <c r="BI1" s="28"/>
+      <c r="BJ1" s="28"/>
+      <c r="BK1" s="28"/>
+      <c r="BL1" s="28"/>
+      <c r="BM1" s="28"/>
+      <c r="BN1" s="28"/>
+      <c r="BO1" s="28"/>
+      <c r="BP1" s="28"/>
+      <c r="BQ1" s="28"/>
+      <c r="BR1" s="28"/>
+      <c r="BS1" s="28"/>
+      <c r="BT1" s="28"/>
+      <c r="BU1" s="28"/>
+      <c r="BV1" s="28"/>
+      <c r="BW1" s="28"/>
+      <c r="BX1" s="28"/>
+      <c r="BY1" s="28"/>
+      <c r="BZ1" s="28"/>
+      <c r="CA1" s="28"/>
+      <c r="CB1" s="28"/>
+      <c r="CC1" s="28"/>
+      <c r="CD1" s="28"/>
+      <c r="CE1" s="28"/>
+      <c r="CF1" s="28"/>
+      <c r="CG1" s="28"/>
+      <c r="CH1" s="28"/>
+      <c r="CI1" s="28"/>
+      <c r="CJ1" s="28"/>
+      <c r="CK1" s="28"/>
+      <c r="CL1" s="28"/>
+      <c r="CM1" s="28"/>
+      <c r="CN1" s="28"/>
+      <c r="CO1" s="28"/>
+      <c r="CP1" s="28"/>
+      <c r="CQ1" s="28"/>
+      <c r="CR1" s="28"/>
+      <c r="CS1" s="28"/>
+      <c r="CT1" s="28"/>
+      <c r="CU1" s="28"/>
+      <c r="CV1" s="28"/>
+      <c r="CW1" s="28"/>
+      <c r="CX1" s="28"/>
+      <c r="CY1" s="28"/>
+      <c r="CZ1" s="28"/>
+      <c r="DA1" s="28"/>
+      <c r="DB1" s="28"/>
+      <c r="DC1" s="28"/>
+      <c r="DD1" s="28"/>
+      <c r="DE1" s="28"/>
+      <c r="DF1" s="28"/>
+      <c r="DG1" s="28"/>
+      <c r="DH1" s="28"/>
+      <c r="DI1" s="28"/>
+      <c r="DJ1" s="28"/>
+      <c r="DK1" s="28"/>
+      <c r="DL1" s="28"/>
+      <c r="DM1" s="28"/>
+      <c r="DN1" s="28"/>
+      <c r="DO1" s="28"/>
+      <c r="DP1" s="28"/>
+      <c r="DQ1" s="28"/>
+      <c r="DR1" s="28"/>
+      <c r="DS1" s="28"/>
+      <c r="DT1" s="28"/>
+      <c r="DU1" s="28"/>
+      <c r="DV1" s="28"/>
+      <c r="DW1" s="28"/>
+      <c r="DX1" s="28"/>
+      <c r="DY1" s="28"/>
+      <c r="DZ1" s="28"/>
+      <c r="EA1" s="28"/>
+      <c r="EB1" s="28"/>
+      <c r="EC1" s="28"/>
+      <c r="ED1" s="28"/>
+      <c r="EE1" s="28"/>
+      <c r="EF1" s="28"/>
+      <c r="EG1" s="28"/>
+      <c r="EH1" s="28"/>
+      <c r="EI1" s="28"/>
+      <c r="EJ1" s="28"/>
+      <c r="EK1" s="28"/>
+      <c r="EL1" s="28"/>
+      <c r="EM1" s="28"/>
+      <c r="EN1" s="28"/>
+      <c r="EO1" s="28"/>
+      <c r="EP1" s="28"/>
+      <c r="EQ1" s="28"/>
+      <c r="ER1" s="28"/>
+      <c r="ES1" s="28"/>
+      <c r="ET1" s="28"/>
+      <c r="EU1" s="28"/>
     </row>
     <row r="2">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="29" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-      <c r="S2" s="37"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="37"/>
-      <c r="Z2" s="37"/>
-      <c r="AA2" s="37"/>
-      <c r="AB2" s="37"/>
-      <c r="AC2" s="37"/>
-      <c r="AD2" s="37"/>
-      <c r="AE2" s="37"/>
-      <c r="AF2" s="37"/>
-      <c r="AG2" s="37"/>
-      <c r="AH2" s="37"/>
-      <c r="AI2" s="37"/>
-      <c r="AJ2" s="37"/>
-      <c r="AK2" s="37"/>
-      <c r="AL2" s="37"/>
-      <c r="AM2" s="37"/>
-      <c r="AN2" s="37"/>
-      <c r="AO2" s="37"/>
-      <c r="AP2" s="37"/>
-      <c r="AQ2" s="37"/>
-      <c r="AR2" s="37"/>
-      <c r="AS2" s="37"/>
-      <c r="AT2" s="37"/>
-      <c r="AU2" s="37"/>
-      <c r="AV2" s="37"/>
-      <c r="AW2" s="37"/>
-      <c r="AX2" s="37"/>
-      <c r="AY2" s="37"/>
-      <c r="AZ2" s="37"/>
-      <c r="BA2" s="37"/>
-      <c r="BB2" s="37"/>
-      <c r="BC2" s="37"/>
-      <c r="BD2" s="37"/>
-      <c r="BE2" s="37"/>
-      <c r="BF2" s="37"/>
-      <c r="BG2" s="37"/>
-      <c r="BH2" s="37"/>
-      <c r="BI2" s="37"/>
-      <c r="BJ2" s="37"/>
-      <c r="BK2" s="37"/>
-      <c r="BL2" s="37"/>
-      <c r="BM2" s="37"/>
-      <c r="BN2" s="37"/>
-      <c r="BO2" s="37"/>
-      <c r="BP2" s="37"/>
-      <c r="BQ2" s="37"/>
-      <c r="BR2" s="37"/>
-      <c r="BS2" s="37"/>
-      <c r="BT2" s="37"/>
-      <c r="BU2" s="37"/>
-      <c r="BV2" s="37"/>
-      <c r="BW2" s="37"/>
-      <c r="BX2" s="37"/>
-      <c r="BY2" s="37"/>
-      <c r="BZ2" s="37"/>
-      <c r="CA2" s="37"/>
-      <c r="CB2" s="37"/>
-      <c r="CC2" s="37"/>
-      <c r="CD2" s="37"/>
-      <c r="CE2" s="37"/>
-      <c r="CF2" s="37"/>
-      <c r="CG2" s="37"/>
-      <c r="CH2" s="37"/>
-      <c r="CI2" s="37"/>
-      <c r="CJ2" s="37"/>
-      <c r="CK2" s="37"/>
-      <c r="CL2" s="37"/>
-      <c r="CM2" s="37"/>
-      <c r="CN2" s="37"/>
-      <c r="CO2" s="37"/>
-      <c r="CP2" s="37"/>
-      <c r="CQ2" s="37"/>
-      <c r="CR2" s="37"/>
-      <c r="CS2" s="37"/>
-      <c r="CT2" s="37"/>
-      <c r="CU2" s="37"/>
-      <c r="CV2" s="37"/>
-      <c r="CW2" s="37"/>
-      <c r="CX2" s="37"/>
-      <c r="CY2" s="37"/>
-      <c r="CZ2" s="37"/>
-      <c r="DA2" s="37"/>
-      <c r="DB2" s="37"/>
-      <c r="DC2" s="37"/>
-      <c r="DD2" s="37"/>
-      <c r="DE2" s="37"/>
-      <c r="DF2" s="37"/>
-      <c r="DG2" s="37"/>
-      <c r="DH2" s="37"/>
-      <c r="DI2" s="37"/>
-      <c r="DJ2" s="37"/>
-      <c r="DK2" s="37"/>
-      <c r="DL2" s="37"/>
-      <c r="DM2" s="37"/>
-      <c r="DN2" s="37"/>
-      <c r="DO2" s="37"/>
-      <c r="DP2" s="37"/>
-      <c r="DQ2" s="37"/>
-      <c r="DR2" s="37"/>
-      <c r="DS2" s="37"/>
-      <c r="DT2" s="37"/>
-      <c r="DU2" s="37"/>
-      <c r="DV2" s="37"/>
-      <c r="DW2" s="37"/>
-      <c r="DX2" s="37"/>
-      <c r="DY2" s="37"/>
-      <c r="DZ2" s="37"/>
-      <c r="EA2" s="37"/>
-      <c r="EB2" s="37"/>
-      <c r="EC2" s="37"/>
-      <c r="ED2" s="37"/>
-      <c r="EE2" s="37"/>
-      <c r="EF2" s="37"/>
-      <c r="EG2" s="37"/>
-      <c r="EH2" s="37"/>
-      <c r="EI2" s="37"/>
-      <c r="EJ2" s="37"/>
-      <c r="EK2" s="37"/>
-      <c r="EL2" s="37"/>
-      <c r="EM2" s="37"/>
-      <c r="EN2" s="37"/>
-      <c r="EO2" s="37"/>
-      <c r="EP2" s="37"/>
-      <c r="EQ2" s="37"/>
-      <c r="ER2" s="37"/>
-      <c r="ES2" s="37"/>
-      <c r="ET2" s="37"/>
-      <c r="EU2" s="37"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
+      <c r="V2" s="28"/>
+      <c r="W2" s="28"/>
+      <c r="X2" s="28"/>
+      <c r="Y2" s="28"/>
+      <c r="Z2" s="28"/>
+      <c r="AA2" s="28"/>
+      <c r="AB2" s="28"/>
+      <c r="AC2" s="28"/>
+      <c r="AD2" s="28"/>
+      <c r="AE2" s="28"/>
+      <c r="AF2" s="28"/>
+      <c r="AG2" s="28"/>
+      <c r="AH2" s="28"/>
+      <c r="AI2" s="28"/>
+      <c r="AJ2" s="28"/>
+      <c r="AK2" s="28"/>
+      <c r="AL2" s="28"/>
+      <c r="AM2" s="28"/>
+      <c r="AN2" s="28"/>
+      <c r="AO2" s="28"/>
+      <c r="AP2" s="28"/>
+      <c r="AQ2" s="28"/>
+      <c r="AR2" s="28"/>
+      <c r="AS2" s="28"/>
+      <c r="AT2" s="28"/>
+      <c r="AU2" s="28"/>
+      <c r="AV2" s="28"/>
+      <c r="AW2" s="28"/>
+      <c r="AX2" s="28"/>
+      <c r="AY2" s="28"/>
+      <c r="AZ2" s="28"/>
+      <c r="BA2" s="28"/>
+      <c r="BB2" s="28"/>
+      <c r="BC2" s="28"/>
+      <c r="BD2" s="28"/>
+      <c r="BE2" s="28"/>
+      <c r="BF2" s="28"/>
+      <c r="BG2" s="28"/>
+      <c r="BH2" s="28"/>
+      <c r="BI2" s="28"/>
+      <c r="BJ2" s="28"/>
+      <c r="BK2" s="28"/>
+      <c r="BL2" s="28"/>
+      <c r="BM2" s="28"/>
+      <c r="BN2" s="28"/>
+      <c r="BO2" s="28"/>
+      <c r="BP2" s="28"/>
+      <c r="BQ2" s="28"/>
+      <c r="BR2" s="28"/>
+      <c r="BS2" s="28"/>
+      <c r="BT2" s="28"/>
+      <c r="BU2" s="28"/>
+      <c r="BV2" s="28"/>
+      <c r="BW2" s="28"/>
+      <c r="BX2" s="28"/>
+      <c r="BY2" s="28"/>
+      <c r="BZ2" s="28"/>
+      <c r="CA2" s="28"/>
+      <c r="CB2" s="28"/>
+      <c r="CC2" s="28"/>
+      <c r="CD2" s="28"/>
+      <c r="CE2" s="28"/>
+      <c r="CF2" s="28"/>
+      <c r="CG2" s="28"/>
+      <c r="CH2" s="28"/>
+      <c r="CI2" s="28"/>
+      <c r="CJ2" s="28"/>
+      <c r="CK2" s="28"/>
+      <c r="CL2" s="28"/>
+      <c r="CM2" s="28"/>
+      <c r="CN2" s="28"/>
+      <c r="CO2" s="28"/>
+      <c r="CP2" s="28"/>
+      <c r="CQ2" s="28"/>
+      <c r="CR2" s="28"/>
+      <c r="CS2" s="28"/>
+      <c r="CT2" s="28"/>
+      <c r="CU2" s="28"/>
+      <c r="CV2" s="28"/>
+      <c r="CW2" s="28"/>
+      <c r="CX2" s="28"/>
+      <c r="CY2" s="28"/>
+      <c r="CZ2" s="28"/>
+      <c r="DA2" s="28"/>
+      <c r="DB2" s="28"/>
+      <c r="DC2" s="28"/>
+      <c r="DD2" s="28"/>
+      <c r="DE2" s="28"/>
+      <c r="DF2" s="28"/>
+      <c r="DG2" s="28"/>
+      <c r="DH2" s="28"/>
+      <c r="DI2" s="28"/>
+      <c r="DJ2" s="28"/>
+      <c r="DK2" s="28"/>
+      <c r="DL2" s="28"/>
+      <c r="DM2" s="28"/>
+      <c r="DN2" s="28"/>
+      <c r="DO2" s="28"/>
+      <c r="DP2" s="28"/>
+      <c r="DQ2" s="28"/>
+      <c r="DR2" s="28"/>
+      <c r="DS2" s="28"/>
+      <c r="DT2" s="28"/>
+      <c r="DU2" s="28"/>
+      <c r="DV2" s="28"/>
+      <c r="DW2" s="28"/>
+      <c r="DX2" s="28"/>
+      <c r="DY2" s="28"/>
+      <c r="DZ2" s="28"/>
+      <c r="EA2" s="28"/>
+      <c r="EB2" s="28"/>
+      <c r="EC2" s="28"/>
+      <c r="ED2" s="28"/>
+      <c r="EE2" s="28"/>
+      <c r="EF2" s="28"/>
+      <c r="EG2" s="28"/>
+      <c r="EH2" s="28"/>
+      <c r="EI2" s="28"/>
+      <c r="EJ2" s="28"/>
+      <c r="EK2" s="28"/>
+      <c r="EL2" s="28"/>
+      <c r="EM2" s="28"/>
+      <c r="EN2" s="28"/>
+      <c r="EO2" s="28"/>
+      <c r="EP2" s="28"/>
+      <c r="EQ2" s="28"/>
+      <c r="ER2" s="28"/>
+      <c r="ES2" s="28"/>
+      <c r="ET2" s="28"/>
+      <c r="EU2" s="28"/>
     </row>
     <row r="3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="29" t="s">
         <v>268</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
-      <c r="S3" s="37"/>
-      <c r="T3" s="37"/>
-      <c r="U3" s="37"/>
-      <c r="V3" s="37"/>
-      <c r="W3" s="37"/>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="37"/>
-      <c r="Z3" s="37"/>
-      <c r="AA3" s="37"/>
-      <c r="AB3" s="37"/>
-      <c r="AC3" s="37"/>
-      <c r="AD3" s="37"/>
-      <c r="AE3" s="37"/>
-      <c r="AF3" s="37"/>
-      <c r="AG3" s="37"/>
-      <c r="AH3" s="37"/>
-      <c r="AI3" s="37"/>
-      <c r="AJ3" s="37"/>
-      <c r="AK3" s="37"/>
-      <c r="AL3" s="37"/>
-      <c r="AM3" s="37"/>
-      <c r="AN3" s="37"/>
-      <c r="AO3" s="37"/>
-      <c r="AP3" s="37"/>
-      <c r="AQ3" s="37"/>
-      <c r="AR3" s="37"/>
-      <c r="AS3" s="37"/>
-      <c r="AT3" s="37"/>
-      <c r="AU3" s="37"/>
-      <c r="AV3" s="37"/>
-      <c r="AW3" s="37"/>
-      <c r="AX3" s="37"/>
-      <c r="AY3" s="37"/>
-      <c r="AZ3" s="37"/>
-      <c r="BA3" s="37"/>
-      <c r="BB3" s="37"/>
-      <c r="BC3" s="37"/>
-      <c r="BD3" s="37"/>
-      <c r="BE3" s="37"/>
-      <c r="BF3" s="37"/>
-      <c r="BG3" s="37"/>
-      <c r="BH3" s="37"/>
-      <c r="BI3" s="37"/>
-      <c r="BJ3" s="37"/>
-      <c r="BK3" s="37"/>
-      <c r="BL3" s="37"/>
-      <c r="BM3" s="37"/>
-      <c r="BN3" s="37"/>
-      <c r="BO3" s="37"/>
-      <c r="BP3" s="37"/>
-      <c r="BQ3" s="37"/>
-      <c r="BR3" s="37"/>
-      <c r="BS3" s="37"/>
-      <c r="BT3" s="37"/>
-      <c r="BU3" s="37"/>
-      <c r="BV3" s="37"/>
-      <c r="BW3" s="37"/>
-      <c r="BX3" s="37"/>
-      <c r="BY3" s="37"/>
-      <c r="BZ3" s="37"/>
-      <c r="CA3" s="37"/>
-      <c r="CB3" s="37"/>
-      <c r="CC3" s="37"/>
-      <c r="CD3" s="37"/>
-      <c r="CE3" s="37"/>
-      <c r="CF3" s="37"/>
-      <c r="CG3" s="37"/>
-      <c r="CH3" s="37"/>
-      <c r="CI3" s="37"/>
-      <c r="CJ3" s="37"/>
-      <c r="CK3" s="37"/>
-      <c r="CL3" s="37"/>
-      <c r="CM3" s="37"/>
-      <c r="CN3" s="37"/>
-      <c r="CO3" s="37"/>
-      <c r="CP3" s="37"/>
-      <c r="CQ3" s="37"/>
-      <c r="CR3" s="37"/>
-      <c r="CS3" s="37"/>
-      <c r="CT3" s="37"/>
-      <c r="CU3" s="37"/>
-      <c r="CV3" s="37"/>
-      <c r="CW3" s="37"/>
-      <c r="CX3" s="37"/>
-      <c r="CY3" s="37"/>
-      <c r="CZ3" s="37"/>
-      <c r="DA3" s="37"/>
-      <c r="DB3" s="37"/>
-      <c r="DC3" s="37"/>
-      <c r="DD3" s="37"/>
-      <c r="DE3" s="37"/>
-      <c r="DF3" s="37"/>
-      <c r="DG3" s="37"/>
-      <c r="DH3" s="37"/>
-      <c r="DI3" s="37"/>
-      <c r="DJ3" s="37"/>
-      <c r="DK3" s="37"/>
-      <c r="DL3" s="37"/>
-      <c r="DM3" s="37"/>
-      <c r="DN3" s="37"/>
-      <c r="DO3" s="37"/>
-      <c r="DP3" s="37"/>
-      <c r="DQ3" s="37"/>
-      <c r="DR3" s="37"/>
-      <c r="DS3" s="37"/>
-      <c r="DT3" s="37"/>
-      <c r="DU3" s="37"/>
-      <c r="DV3" s="37"/>
-      <c r="DW3" s="37"/>
-      <c r="DX3" s="37"/>
-      <c r="DY3" s="37"/>
-      <c r="DZ3" s="37"/>
-      <c r="EA3" s="37"/>
-      <c r="EB3" s="37"/>
-      <c r="EC3" s="37"/>
-      <c r="ED3" s="37"/>
-      <c r="EE3" s="37"/>
-      <c r="EF3" s="37"/>
-      <c r="EG3" s="37"/>
-      <c r="EH3" s="37"/>
-      <c r="EI3" s="37"/>
-      <c r="EJ3" s="37"/>
-      <c r="EK3" s="37"/>
-      <c r="EL3" s="37"/>
-      <c r="EM3" s="37"/>
-      <c r="EN3" s="37"/>
-      <c r="EO3" s="37"/>
-      <c r="EP3" s="37"/>
-      <c r="EQ3" s="37"/>
-      <c r="ER3" s="37"/>
-      <c r="ES3" s="37"/>
-      <c r="ET3" s="37"/>
-      <c r="EU3" s="37"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="28"/>
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="28"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="28"/>
+      <c r="AC3" s="28"/>
+      <c r="AD3" s="28"/>
+      <c r="AE3" s="28"/>
+      <c r="AF3" s="28"/>
+      <c r="AG3" s="28"/>
+      <c r="AH3" s="28"/>
+      <c r="AI3" s="28"/>
+      <c r="AJ3" s="28"/>
+      <c r="AK3" s="28"/>
+      <c r="AL3" s="28"/>
+      <c r="AM3" s="28"/>
+      <c r="AN3" s="28"/>
+      <c r="AO3" s="28"/>
+      <c r="AP3" s="28"/>
+      <c r="AQ3" s="28"/>
+      <c r="AR3" s="28"/>
+      <c r="AS3" s="28"/>
+      <c r="AT3" s="28"/>
+      <c r="AU3" s="28"/>
+      <c r="AV3" s="28"/>
+      <c r="AW3" s="28"/>
+      <c r="AX3" s="28"/>
+      <c r="AY3" s="28"/>
+      <c r="AZ3" s="28"/>
+      <c r="BA3" s="28"/>
+      <c r="BB3" s="28"/>
+      <c r="BC3" s="28"/>
+      <c r="BD3" s="28"/>
+      <c r="BE3" s="28"/>
+      <c r="BF3" s="28"/>
+      <c r="BG3" s="28"/>
+      <c r="BH3" s="28"/>
+      <c r="BI3" s="28"/>
+      <c r="BJ3" s="28"/>
+      <c r="BK3" s="28"/>
+      <c r="BL3" s="28"/>
+      <c r="BM3" s="28"/>
+      <c r="BN3" s="28"/>
+      <c r="BO3" s="28"/>
+      <c r="BP3" s="28"/>
+      <c r="BQ3" s="28"/>
+      <c r="BR3" s="28"/>
+      <c r="BS3" s="28"/>
+      <c r="BT3" s="28"/>
+      <c r="BU3" s="28"/>
+      <c r="BV3" s="28"/>
+      <c r="BW3" s="28"/>
+      <c r="BX3" s="28"/>
+      <c r="BY3" s="28"/>
+      <c r="BZ3" s="28"/>
+      <c r="CA3" s="28"/>
+      <c r="CB3" s="28"/>
+      <c r="CC3" s="28"/>
+      <c r="CD3" s="28"/>
+      <c r="CE3" s="28"/>
+      <c r="CF3" s="28"/>
+      <c r="CG3" s="28"/>
+      <c r="CH3" s="28"/>
+      <c r="CI3" s="28"/>
+      <c r="CJ3" s="28"/>
+      <c r="CK3" s="28"/>
+      <c r="CL3" s="28"/>
+      <c r="CM3" s="28"/>
+      <c r="CN3" s="28"/>
+      <c r="CO3" s="28"/>
+      <c r="CP3" s="28"/>
+      <c r="CQ3" s="28"/>
+      <c r="CR3" s="28"/>
+      <c r="CS3" s="28"/>
+      <c r="CT3" s="28"/>
+      <c r="CU3" s="28"/>
+      <c r="CV3" s="28"/>
+      <c r="CW3" s="28"/>
+      <c r="CX3" s="28"/>
+      <c r="CY3" s="28"/>
+      <c r="CZ3" s="28"/>
+      <c r="DA3" s="28"/>
+      <c r="DB3" s="28"/>
+      <c r="DC3" s="28"/>
+      <c r="DD3" s="28"/>
+      <c r="DE3" s="28"/>
+      <c r="DF3" s="28"/>
+      <c r="DG3" s="28"/>
+      <c r="DH3" s="28"/>
+      <c r="DI3" s="28"/>
+      <c r="DJ3" s="28"/>
+      <c r="DK3" s="28"/>
+      <c r="DL3" s="28"/>
+      <c r="DM3" s="28"/>
+      <c r="DN3" s="28"/>
+      <c r="DO3" s="28"/>
+      <c r="DP3" s="28"/>
+      <c r="DQ3" s="28"/>
+      <c r="DR3" s="28"/>
+      <c r="DS3" s="28"/>
+      <c r="DT3" s="28"/>
+      <c r="DU3" s="28"/>
+      <c r="DV3" s="28"/>
+      <c r="DW3" s="28"/>
+      <c r="DX3" s="28"/>
+      <c r="DY3" s="28"/>
+      <c r="DZ3" s="28"/>
+      <c r="EA3" s="28"/>
+      <c r="EB3" s="28"/>
+      <c r="EC3" s="28"/>
+      <c r="ED3" s="28"/>
+      <c r="EE3" s="28"/>
+      <c r="EF3" s="28"/>
+      <c r="EG3" s="28"/>
+      <c r="EH3" s="28"/>
+      <c r="EI3" s="28"/>
+      <c r="EJ3" s="28"/>
+      <c r="EK3" s="28"/>
+      <c r="EL3" s="28"/>
+      <c r="EM3" s="28"/>
+      <c r="EN3" s="28"/>
+      <c r="EO3" s="28"/>
+      <c r="EP3" s="28"/>
+      <c r="EQ3" s="28"/>
+      <c r="ER3" s="28"/>
+      <c r="ES3" s="28"/>
+      <c r="ET3" s="28"/>
+      <c r="EU3" s="28"/>
     </row>
     <row r="4">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="37"/>
-      <c r="Q4" s="37"/>
-      <c r="R4" s="37"/>
-      <c r="S4" s="37"/>
-      <c r="T4" s="37"/>
-      <c r="U4" s="37"/>
-      <c r="V4" s="37"/>
-      <c r="W4" s="37"/>
-      <c r="X4" s="37"/>
-      <c r="Y4" s="37"/>
-      <c r="Z4" s="37"/>
-      <c r="AA4" s="37"/>
-      <c r="AB4" s="37"/>
-      <c r="AC4" s="37"/>
-      <c r="AD4" s="37"/>
-      <c r="AE4" s="37"/>
-      <c r="AF4" s="37"/>
-      <c r="AG4" s="37"/>
-      <c r="AH4" s="37"/>
-      <c r="AI4" s="37"/>
-      <c r="AJ4" s="37"/>
-      <c r="AK4" s="37"/>
-      <c r="AL4" s="37"/>
-      <c r="AM4" s="37"/>
-      <c r="AN4" s="37"/>
-      <c r="AO4" s="37"/>
-      <c r="AP4" s="37"/>
-      <c r="AQ4" s="37"/>
-      <c r="AR4" s="37"/>
-      <c r="AS4" s="37"/>
-      <c r="AT4" s="37"/>
-      <c r="AU4" s="37"/>
-      <c r="AV4" s="37"/>
-      <c r="AW4" s="37"/>
-      <c r="AX4" s="37"/>
-      <c r="AY4" s="37"/>
-      <c r="AZ4" s="37"/>
-      <c r="BA4" s="37"/>
-      <c r="BB4" s="37"/>
-      <c r="BC4" s="37"/>
-      <c r="BD4" s="37"/>
-      <c r="BE4" s="37"/>
-      <c r="BF4" s="37"/>
-      <c r="BG4" s="37"/>
-      <c r="BH4" s="37"/>
-      <c r="BI4" s="37"/>
-      <c r="BJ4" s="37"/>
-      <c r="BK4" s="37"/>
-      <c r="BL4" s="37"/>
-      <c r="BM4" s="37"/>
-      <c r="BN4" s="37"/>
-      <c r="BO4" s="37"/>
-      <c r="BP4" s="37"/>
-      <c r="BQ4" s="37"/>
-      <c r="BR4" s="37"/>
-      <c r="BS4" s="37"/>
-      <c r="BT4" s="37"/>
-      <c r="BU4" s="37"/>
-      <c r="BV4" s="37"/>
-      <c r="BW4" s="37"/>
-      <c r="BX4" s="37"/>
-      <c r="BY4" s="37"/>
-      <c r="BZ4" s="37"/>
-      <c r="CA4" s="37"/>
-      <c r="CB4" s="37"/>
-      <c r="CC4" s="37"/>
-      <c r="CD4" s="37"/>
-      <c r="CE4" s="37"/>
-      <c r="CF4" s="37"/>
-      <c r="CG4" s="37"/>
-      <c r="CH4" s="37"/>
-      <c r="CI4" s="37"/>
-      <c r="CJ4" s="37"/>
-      <c r="CK4" s="37"/>
-      <c r="CL4" s="37"/>
-      <c r="CM4" s="37"/>
-      <c r="CN4" s="37"/>
-      <c r="CO4" s="37"/>
-      <c r="CP4" s="37"/>
-      <c r="CQ4" s="37"/>
-      <c r="CR4" s="37"/>
-      <c r="CS4" s="37"/>
-      <c r="CT4" s="37"/>
-      <c r="CU4" s="37"/>
-      <c r="CV4" s="37"/>
-      <c r="CW4" s="37"/>
-      <c r="CX4" s="37"/>
-      <c r="CY4" s="37"/>
-      <c r="CZ4" s="37"/>
-      <c r="DA4" s="37"/>
-      <c r="DB4" s="37"/>
-      <c r="DC4" s="37"/>
-      <c r="DD4" s="37"/>
-      <c r="DE4" s="37"/>
-      <c r="DF4" s="37"/>
-      <c r="DG4" s="37"/>
-      <c r="DH4" s="37"/>
-      <c r="DI4" s="37"/>
-      <c r="DJ4" s="37"/>
-      <c r="DK4" s="37"/>
-      <c r="DL4" s="37"/>
-      <c r="DM4" s="37"/>
-      <c r="DN4" s="37"/>
-      <c r="DO4" s="37"/>
-      <c r="DP4" s="37"/>
-      <c r="DQ4" s="37"/>
-      <c r="DR4" s="37"/>
-      <c r="DS4" s="37"/>
-      <c r="DT4" s="37"/>
-      <c r="DU4" s="37"/>
-      <c r="DV4" s="37"/>
-      <c r="DW4" s="37"/>
-      <c r="DX4" s="37"/>
-      <c r="DY4" s="37"/>
-      <c r="DZ4" s="37"/>
-      <c r="EA4" s="37"/>
-      <c r="EB4" s="37"/>
-      <c r="EC4" s="37"/>
-      <c r="ED4" s="37"/>
-      <c r="EE4" s="37"/>
-      <c r="EF4" s="37"/>
-      <c r="EG4" s="37"/>
-      <c r="EH4" s="37"/>
-      <c r="EI4" s="37"/>
-      <c r="EJ4" s="37"/>
-      <c r="EK4" s="37"/>
-      <c r="EL4" s="37"/>
-      <c r="EM4" s="37"/>
-      <c r="EN4" s="37"/>
-      <c r="EO4" s="37"/>
-      <c r="EP4" s="37"/>
-      <c r="EQ4" s="37"/>
-      <c r="ER4" s="37"/>
-      <c r="ES4" s="37"/>
-      <c r="ET4" s="37"/>
-      <c r="EU4" s="37"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="28"/>
+      <c r="AA4" s="28"/>
+      <c r="AB4" s="28"/>
+      <c r="AC4" s="28"/>
+      <c r="AD4" s="28"/>
+      <c r="AE4" s="28"/>
+      <c r="AF4" s="28"/>
+      <c r="AG4" s="28"/>
+      <c r="AH4" s="28"/>
+      <c r="AI4" s="28"/>
+      <c r="AJ4" s="28"/>
+      <c r="AK4" s="28"/>
+      <c r="AL4" s="28"/>
+      <c r="AM4" s="28"/>
+      <c r="AN4" s="28"/>
+      <c r="AO4" s="28"/>
+      <c r="AP4" s="28"/>
+      <c r="AQ4" s="28"/>
+      <c r="AR4" s="28"/>
+      <c r="AS4" s="28"/>
+      <c r="AT4" s="28"/>
+      <c r="AU4" s="28"/>
+      <c r="AV4" s="28"/>
+      <c r="AW4" s="28"/>
+      <c r="AX4" s="28"/>
+      <c r="AY4" s="28"/>
+      <c r="AZ4" s="28"/>
+      <c r="BA4" s="28"/>
+      <c r="BB4" s="28"/>
+      <c r="BC4" s="28"/>
+      <c r="BD4" s="28"/>
+      <c r="BE4" s="28"/>
+      <c r="BF4" s="28"/>
+      <c r="BG4" s="28"/>
+      <c r="BH4" s="28"/>
+      <c r="BI4" s="28"/>
+      <c r="BJ4" s="28"/>
+      <c r="BK4" s="28"/>
+      <c r="BL4" s="28"/>
+      <c r="BM4" s="28"/>
+      <c r="BN4" s="28"/>
+      <c r="BO4" s="28"/>
+      <c r="BP4" s="28"/>
+      <c r="BQ4" s="28"/>
+      <c r="BR4" s="28"/>
+      <c r="BS4" s="28"/>
+      <c r="BT4" s="28"/>
+      <c r="BU4" s="28"/>
+      <c r="BV4" s="28"/>
+      <c r="BW4" s="28"/>
+      <c r="BX4" s="28"/>
+      <c r="BY4" s="28"/>
+      <c r="BZ4" s="28"/>
+      <c r="CA4" s="28"/>
+      <c r="CB4" s="28"/>
+      <c r="CC4" s="28"/>
+      <c r="CD4" s="28"/>
+      <c r="CE4" s="28"/>
+      <c r="CF4" s="28"/>
+      <c r="CG4" s="28"/>
+      <c r="CH4" s="28"/>
+      <c r="CI4" s="28"/>
+      <c r="CJ4" s="28"/>
+      <c r="CK4" s="28"/>
+      <c r="CL4" s="28"/>
+      <c r="CM4" s="28"/>
+      <c r="CN4" s="28"/>
+      <c r="CO4" s="28"/>
+      <c r="CP4" s="28"/>
+      <c r="CQ4" s="28"/>
+      <c r="CR4" s="28"/>
+      <c r="CS4" s="28"/>
+      <c r="CT4" s="28"/>
+      <c r="CU4" s="28"/>
+      <c r="CV4" s="28"/>
+      <c r="CW4" s="28"/>
+      <c r="CX4" s="28"/>
+      <c r="CY4" s="28"/>
+      <c r="CZ4" s="28"/>
+      <c r="DA4" s="28"/>
+      <c r="DB4" s="28"/>
+      <c r="DC4" s="28"/>
+      <c r="DD4" s="28"/>
+      <c r="DE4" s="28"/>
+      <c r="DF4" s="28"/>
+      <c r="DG4" s="28"/>
+      <c r="DH4" s="28"/>
+      <c r="DI4" s="28"/>
+      <c r="DJ4" s="28"/>
+      <c r="DK4" s="28"/>
+      <c r="DL4" s="28"/>
+      <c r="DM4" s="28"/>
+      <c r="DN4" s="28"/>
+      <c r="DO4" s="28"/>
+      <c r="DP4" s="28"/>
+      <c r="DQ4" s="28"/>
+      <c r="DR4" s="28"/>
+      <c r="DS4" s="28"/>
+      <c r="DT4" s="28"/>
+      <c r="DU4" s="28"/>
+      <c r="DV4" s="28"/>
+      <c r="DW4" s="28"/>
+      <c r="DX4" s="28"/>
+      <c r="DY4" s="28"/>
+      <c r="DZ4" s="28"/>
+      <c r="EA4" s="28"/>
+      <c r="EB4" s="28"/>
+      <c r="EC4" s="28"/>
+      <c r="ED4" s="28"/>
+      <c r="EE4" s="28"/>
+      <c r="EF4" s="28"/>
+      <c r="EG4" s="28"/>
+      <c r="EH4" s="28"/>
+      <c r="EI4" s="28"/>
+      <c r="EJ4" s="28"/>
+      <c r="EK4" s="28"/>
+      <c r="EL4" s="28"/>
+      <c r="EM4" s="28"/>
+      <c r="EN4" s="28"/>
+      <c r="EO4" s="28"/>
+      <c r="EP4" s="28"/>
+      <c r="EQ4" s="28"/>
+      <c r="ER4" s="28"/>
+      <c r="ES4" s="28"/>
+      <c r="ET4" s="28"/>
+      <c r="EU4" s="28"/>
     </row>
     <row r="5">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="37"/>
-      <c r="P5" s="37"/>
-      <c r="Q5" s="37"/>
-      <c r="R5" s="37"/>
-      <c r="S5" s="37"/>
-      <c r="T5" s="37"/>
-      <c r="U5" s="37"/>
-      <c r="V5" s="37"/>
-      <c r="W5" s="37"/>
-      <c r="X5" s="37"/>
-      <c r="Y5" s="37"/>
-      <c r="Z5" s="37"/>
-      <c r="AA5" s="37"/>
-      <c r="AB5" s="37"/>
-      <c r="AC5" s="37"/>
-      <c r="AD5" s="37"/>
-      <c r="AE5" s="37"/>
-      <c r="AF5" s="37"/>
-      <c r="AG5" s="37"/>
-      <c r="AH5" s="37"/>
-      <c r="AI5" s="37"/>
-      <c r="AJ5" s="37"/>
-      <c r="AK5" s="37"/>
-      <c r="AL5" s="37"/>
-      <c r="AM5" s="37"/>
-      <c r="AN5" s="37"/>
-      <c r="AO5" s="37"/>
-      <c r="AP5" s="37"/>
-      <c r="AQ5" s="37"/>
-      <c r="AR5" s="37"/>
-      <c r="AS5" s="37"/>
-      <c r="AT5" s="37"/>
-      <c r="AU5" s="37"/>
-      <c r="AV5" s="37"/>
-      <c r="AW5" s="37"/>
-      <c r="AX5" s="37"/>
-      <c r="AY5" s="37"/>
-      <c r="AZ5" s="37"/>
-      <c r="BA5" s="37"/>
-      <c r="BB5" s="37"/>
-      <c r="BC5" s="37"/>
-      <c r="BD5" s="37"/>
-      <c r="BE5" s="37"/>
-      <c r="BF5" s="37"/>
-      <c r="BG5" s="37"/>
-      <c r="BH5" s="37"/>
-      <c r="BI5" s="37"/>
-      <c r="BJ5" s="37"/>
-      <c r="BK5" s="37"/>
-      <c r="BL5" s="37"/>
-      <c r="BM5" s="37"/>
-      <c r="BN5" s="37"/>
-      <c r="BO5" s="37"/>
-      <c r="BP5" s="37"/>
-      <c r="BQ5" s="37"/>
-      <c r="BR5" s="37"/>
-      <c r="BS5" s="37"/>
-      <c r="BT5" s="37"/>
-      <c r="BU5" s="37"/>
-      <c r="BV5" s="37"/>
-      <c r="BW5" s="37"/>
-      <c r="BX5" s="37"/>
-      <c r="BY5" s="37"/>
-      <c r="BZ5" s="37"/>
-      <c r="CA5" s="37"/>
-      <c r="CB5" s="37"/>
-      <c r="CC5" s="37"/>
-      <c r="CD5" s="37"/>
-      <c r="CE5" s="37"/>
-      <c r="CF5" s="37"/>
-      <c r="CG5" s="37"/>
-      <c r="CH5" s="37"/>
-      <c r="CI5" s="37"/>
-      <c r="CJ5" s="37"/>
-      <c r="CK5" s="37"/>
-      <c r="CL5" s="37"/>
-      <c r="CM5" s="37"/>
-      <c r="CN5" s="37"/>
-      <c r="CO5" s="37"/>
-      <c r="CP5" s="37"/>
-      <c r="CQ5" s="37"/>
-      <c r="CR5" s="37"/>
-      <c r="CS5" s="37"/>
-      <c r="CT5" s="37"/>
-      <c r="CU5" s="37"/>
-      <c r="CV5" s="37"/>
-      <c r="CW5" s="37"/>
-      <c r="CX5" s="37"/>
-      <c r="CY5" s="37"/>
-      <c r="CZ5" s="37"/>
-      <c r="DA5" s="37"/>
-      <c r="DB5" s="37"/>
-      <c r="DC5" s="37"/>
-      <c r="DD5" s="37"/>
-      <c r="DE5" s="37"/>
-      <c r="DF5" s="37"/>
-      <c r="DG5" s="37"/>
-      <c r="DH5" s="37"/>
-      <c r="DI5" s="37"/>
-      <c r="DJ5" s="37"/>
-      <c r="DK5" s="37"/>
-      <c r="DL5" s="37"/>
-      <c r="DM5" s="37"/>
-      <c r="DN5" s="37"/>
-      <c r="DO5" s="37"/>
-      <c r="DP5" s="37"/>
-      <c r="DQ5" s="37"/>
-      <c r="DR5" s="37"/>
-      <c r="DS5" s="37"/>
-      <c r="DT5" s="37"/>
-      <c r="DU5" s="37"/>
-      <c r="DV5" s="37"/>
-      <c r="DW5" s="37"/>
-      <c r="DX5" s="37"/>
-      <c r="DY5" s="37"/>
-      <c r="DZ5" s="37"/>
-      <c r="EA5" s="37"/>
-      <c r="EB5" s="37"/>
-      <c r="EC5" s="37"/>
-      <c r="ED5" s="37"/>
-      <c r="EE5" s="37"/>
-      <c r="EF5" s="37"/>
-      <c r="EG5" s="37"/>
-      <c r="EH5" s="37"/>
-      <c r="EI5" s="37"/>
-      <c r="EJ5" s="37"/>
-      <c r="EK5" s="37"/>
-      <c r="EL5" s="37"/>
-      <c r="EM5" s="37"/>
-      <c r="EN5" s="37"/>
-      <c r="EO5" s="37"/>
-      <c r="EP5" s="37"/>
-      <c r="EQ5" s="37"/>
-      <c r="ER5" s="37"/>
-      <c r="ES5" s="37"/>
-      <c r="ET5" s="37"/>
-      <c r="EU5" s="37"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="28"/>
+      <c r="AD5" s="28"/>
+      <c r="AE5" s="28"/>
+      <c r="AF5" s="28"/>
+      <c r="AG5" s="28"/>
+      <c r="AH5" s="28"/>
+      <c r="AI5" s="28"/>
+      <c r="AJ5" s="28"/>
+      <c r="AK5" s="28"/>
+      <c r="AL5" s="28"/>
+      <c r="AM5" s="28"/>
+      <c r="AN5" s="28"/>
+      <c r="AO5" s="28"/>
+      <c r="AP5" s="28"/>
+      <c r="AQ5" s="28"/>
+      <c r="AR5" s="28"/>
+      <c r="AS5" s="28"/>
+      <c r="AT5" s="28"/>
+      <c r="AU5" s="28"/>
+      <c r="AV5" s="28"/>
+      <c r="AW5" s="28"/>
+      <c r="AX5" s="28"/>
+      <c r="AY5" s="28"/>
+      <c r="AZ5" s="28"/>
+      <c r="BA5" s="28"/>
+      <c r="BB5" s="28"/>
+      <c r="BC5" s="28"/>
+      <c r="BD5" s="28"/>
+      <c r="BE5" s="28"/>
+      <c r="BF5" s="28"/>
+      <c r="BG5" s="28"/>
+      <c r="BH5" s="28"/>
+      <c r="BI5" s="28"/>
+      <c r="BJ5" s="28"/>
+      <c r="BK5" s="28"/>
+      <c r="BL5" s="28"/>
+      <c r="BM5" s="28"/>
+      <c r="BN5" s="28"/>
+      <c r="BO5" s="28"/>
+      <c r="BP5" s="28"/>
+      <c r="BQ5" s="28"/>
+      <c r="BR5" s="28"/>
+      <c r="BS5" s="28"/>
+      <c r="BT5" s="28"/>
+      <c r="BU5" s="28"/>
+      <c r="BV5" s="28"/>
+      <c r="BW5" s="28"/>
+      <c r="BX5" s="28"/>
+      <c r="BY5" s="28"/>
+      <c r="BZ5" s="28"/>
+      <c r="CA5" s="28"/>
+      <c r="CB5" s="28"/>
+      <c r="CC5" s="28"/>
+      <c r="CD5" s="28"/>
+      <c r="CE5" s="28"/>
+      <c r="CF5" s="28"/>
+      <c r="CG5" s="28"/>
+      <c r="CH5" s="28"/>
+      <c r="CI5" s="28"/>
+      <c r="CJ5" s="28"/>
+      <c r="CK5" s="28"/>
+      <c r="CL5" s="28"/>
+      <c r="CM5" s="28"/>
+      <c r="CN5" s="28"/>
+      <c r="CO5" s="28"/>
+      <c r="CP5" s="28"/>
+      <c r="CQ5" s="28"/>
+      <c r="CR5" s="28"/>
+      <c r="CS5" s="28"/>
+      <c r="CT5" s="28"/>
+      <c r="CU5" s="28"/>
+      <c r="CV5" s="28"/>
+      <c r="CW5" s="28"/>
+      <c r="CX5" s="28"/>
+      <c r="CY5" s="28"/>
+      <c r="CZ5" s="28"/>
+      <c r="DA5" s="28"/>
+      <c r="DB5" s="28"/>
+      <c r="DC5" s="28"/>
+      <c r="DD5" s="28"/>
+      <c r="DE5" s="28"/>
+      <c r="DF5" s="28"/>
+      <c r="DG5" s="28"/>
+      <c r="DH5" s="28"/>
+      <c r="DI5" s="28"/>
+      <c r="DJ5" s="28"/>
+      <c r="DK5" s="28"/>
+      <c r="DL5" s="28"/>
+      <c r="DM5" s="28"/>
+      <c r="DN5" s="28"/>
+      <c r="DO5" s="28"/>
+      <c r="DP5" s="28"/>
+      <c r="DQ5" s="28"/>
+      <c r="DR5" s="28"/>
+      <c r="DS5" s="28"/>
+      <c r="DT5" s="28"/>
+      <c r="DU5" s="28"/>
+      <c r="DV5" s="28"/>
+      <c r="DW5" s="28"/>
+      <c r="DX5" s="28"/>
+      <c r="DY5" s="28"/>
+      <c r="DZ5" s="28"/>
+      <c r="EA5" s="28"/>
+      <c r="EB5" s="28"/>
+      <c r="EC5" s="28"/>
+      <c r="ED5" s="28"/>
+      <c r="EE5" s="28"/>
+      <c r="EF5" s="28"/>
+      <c r="EG5" s="28"/>
+      <c r="EH5" s="28"/>
+      <c r="EI5" s="28"/>
+      <c r="EJ5" s="28"/>
+      <c r="EK5" s="28"/>
+      <c r="EL5" s="28"/>
+      <c r="EM5" s="28"/>
+      <c r="EN5" s="28"/>
+      <c r="EO5" s="28"/>
+      <c r="EP5" s="28"/>
+      <c r="EQ5" s="28"/>
+      <c r="ER5" s="28"/>
+      <c r="ES5" s="28"/>
+      <c r="ET5" s="28"/>
+      <c r="EU5" s="28"/>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="J6" s="40" t="s">
+      <c r="J6" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="40" t="s">
+      <c r="K6" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="40" t="s">
+      <c r="L6" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="40" t="s">
+      <c r="M6" s="30" t="s">
         <v>228</v>
       </c>
-      <c r="N6" s="37"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="37"/>
-      <c r="Q6" s="37"/>
-      <c r="R6" s="37"/>
-      <c r="S6" s="37"/>
-      <c r="T6" s="37"/>
-      <c r="U6" s="37"/>
-      <c r="V6" s="37"/>
-      <c r="W6" s="37"/>
-      <c r="X6" s="37"/>
-      <c r="Y6" s="37"/>
-      <c r="Z6" s="37"/>
-      <c r="AA6" s="37"/>
-      <c r="AB6" s="37"/>
-      <c r="AC6" s="37"/>
-      <c r="AD6" s="37"/>
-      <c r="AE6" s="37"/>
-      <c r="AF6" s="37"/>
-      <c r="AG6" s="37"/>
-      <c r="AH6" s="37"/>
-      <c r="AI6" s="37"/>
-      <c r="AJ6" s="37"/>
-      <c r="AK6" s="37"/>
-      <c r="AL6" s="37"/>
-      <c r="AM6" s="37"/>
-      <c r="AN6" s="37"/>
-      <c r="AO6" s="37"/>
-      <c r="AP6" s="37"/>
-      <c r="AQ6" s="37"/>
-      <c r="AR6" s="37"/>
-      <c r="AS6" s="37"/>
-      <c r="AT6" s="37"/>
-      <c r="AU6" s="37"/>
-      <c r="AV6" s="37"/>
-      <c r="AW6" s="37"/>
-      <c r="AX6" s="37"/>
-      <c r="AY6" s="37"/>
-      <c r="AZ6" s="37"/>
-      <c r="BA6" s="37"/>
-      <c r="BB6" s="37"/>
-      <c r="BC6" s="37"/>
-      <c r="BD6" s="37"/>
-      <c r="BE6" s="37"/>
-      <c r="BF6" s="37"/>
-      <c r="BG6" s="37"/>
-      <c r="BH6" s="37"/>
-      <c r="BI6" s="37"/>
-      <c r="BJ6" s="37"/>
-      <c r="BK6" s="37"/>
-      <c r="BL6" s="37"/>
-      <c r="BM6" s="37"/>
-      <c r="BN6" s="37"/>
-      <c r="BO6" s="37"/>
-      <c r="BP6" s="37"/>
-      <c r="BQ6" s="37"/>
-      <c r="BR6" s="37"/>
-      <c r="BS6" s="37"/>
-      <c r="BT6" s="37"/>
-      <c r="BU6" s="37"/>
-      <c r="BV6" s="37"/>
-      <c r="BW6" s="37"/>
-      <c r="BX6" s="37"/>
-      <c r="BY6" s="37"/>
-      <c r="BZ6" s="37"/>
-      <c r="CA6" s="37"/>
-      <c r="CB6" s="37"/>
-      <c r="CC6" s="37"/>
-      <c r="CD6" s="37"/>
-      <c r="CE6" s="37"/>
-      <c r="CF6" s="37"/>
-      <c r="CG6" s="37"/>
-      <c r="CH6" s="37"/>
-      <c r="CI6" s="37"/>
-      <c r="CJ6" s="37"/>
-      <c r="CK6" s="37"/>
-      <c r="CL6" s="37"/>
-      <c r="CM6" s="37"/>
-      <c r="CN6" s="37"/>
-      <c r="CO6" s="37"/>
-      <c r="CP6" s="37"/>
-      <c r="CQ6" s="37"/>
-      <c r="CR6" s="37"/>
-      <c r="CS6" s="37"/>
-      <c r="CT6" s="37"/>
-      <c r="CU6" s="37"/>
-      <c r="CV6" s="37"/>
-      <c r="CW6" s="37"/>
-      <c r="CX6" s="37"/>
-      <c r="CY6" s="37"/>
-      <c r="CZ6" s="37"/>
-      <c r="DA6" s="37"/>
-      <c r="DB6" s="37"/>
-      <c r="DC6" s="37"/>
-      <c r="DD6" s="37"/>
-      <c r="DE6" s="37"/>
-      <c r="DF6" s="37"/>
-      <c r="DG6" s="37"/>
-      <c r="DH6" s="37"/>
-      <c r="DI6" s="37"/>
-      <c r="DJ6" s="37"/>
-      <c r="DK6" s="37"/>
-      <c r="DL6" s="37"/>
-      <c r="DM6" s="37"/>
-      <c r="DN6" s="37"/>
-      <c r="DO6" s="37"/>
-      <c r="DP6" s="37"/>
-      <c r="DQ6" s="37"/>
-      <c r="DR6" s="37"/>
-      <c r="DS6" s="37"/>
-      <c r="DT6" s="37"/>
-      <c r="DU6" s="37"/>
-      <c r="DV6" s="37"/>
-      <c r="DW6" s="37"/>
-      <c r="DX6" s="37"/>
-      <c r="DY6" s="37"/>
-      <c r="DZ6" s="37"/>
-      <c r="EA6" s="37"/>
-      <c r="EB6" s="37"/>
-      <c r="EC6" s="37"/>
-      <c r="ED6" s="37"/>
-      <c r="EE6" s="37"/>
-      <c r="EF6" s="37"/>
-      <c r="EG6" s="37"/>
-      <c r="EH6" s="37"/>
-      <c r="EI6" s="37"/>
-      <c r="EJ6" s="37"/>
-      <c r="EK6" s="37"/>
-      <c r="EL6" s="37"/>
-      <c r="EM6" s="37"/>
-      <c r="EN6" s="37"/>
-      <c r="EO6" s="37"/>
-      <c r="EP6" s="37"/>
-      <c r="EQ6" s="37"/>
-      <c r="ER6" s="37"/>
-      <c r="ES6" s="37"/>
-      <c r="ET6" s="37"/>
-      <c r="EU6" s="37"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="28"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="28"/>
+      <c r="W6" s="28"/>
+      <c r="X6" s="28"/>
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28"/>
+      <c r="AB6" s="28"/>
+      <c r="AC6" s="28"/>
+      <c r="AD6" s="28"/>
+      <c r="AE6" s="28"/>
+      <c r="AF6" s="28"/>
+      <c r="AG6" s="28"/>
+      <c r="AH6" s="28"/>
+      <c r="AI6" s="28"/>
+      <c r="AJ6" s="28"/>
+      <c r="AK6" s="28"/>
+      <c r="AL6" s="28"/>
+      <c r="AM6" s="28"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
+      <c r="AP6" s="28"/>
+      <c r="AQ6" s="28"/>
+      <c r="AR6" s="28"/>
+      <c r="AS6" s="28"/>
+      <c r="AT6" s="28"/>
+      <c r="AU6" s="28"/>
+      <c r="AV6" s="28"/>
+      <c r="AW6" s="28"/>
+      <c r="AX6" s="28"/>
+      <c r="AY6" s="28"/>
+      <c r="AZ6" s="28"/>
+      <c r="BA6" s="28"/>
+      <c r="BB6" s="28"/>
+      <c r="BC6" s="28"/>
+      <c r="BD6" s="28"/>
+      <c r="BE6" s="28"/>
+      <c r="BF6" s="28"/>
+      <c r="BG6" s="28"/>
+      <c r="BH6" s="28"/>
+      <c r="BI6" s="28"/>
+      <c r="BJ6" s="28"/>
+      <c r="BK6" s="28"/>
+      <c r="BL6" s="28"/>
+      <c r="BM6" s="28"/>
+      <c r="BN6" s="28"/>
+      <c r="BO6" s="28"/>
+      <c r="BP6" s="28"/>
+      <c r="BQ6" s="28"/>
+      <c r="BR6" s="28"/>
+      <c r="BS6" s="28"/>
+      <c r="BT6" s="28"/>
+      <c r="BU6" s="28"/>
+      <c r="BV6" s="28"/>
+      <c r="BW6" s="28"/>
+      <c r="BX6" s="28"/>
+      <c r="BY6" s="28"/>
+      <c r="BZ6" s="28"/>
+      <c r="CA6" s="28"/>
+      <c r="CB6" s="28"/>
+      <c r="CC6" s="28"/>
+      <c r="CD6" s="28"/>
+      <c r="CE6" s="28"/>
+      <c r="CF6" s="28"/>
+      <c r="CG6" s="28"/>
+      <c r="CH6" s="28"/>
+      <c r="CI6" s="28"/>
+      <c r="CJ6" s="28"/>
+      <c r="CK6" s="28"/>
+      <c r="CL6" s="28"/>
+      <c r="CM6" s="28"/>
+      <c r="CN6" s="28"/>
+      <c r="CO6" s="28"/>
+      <c r="CP6" s="28"/>
+      <c r="CQ6" s="28"/>
+      <c r="CR6" s="28"/>
+      <c r="CS6" s="28"/>
+      <c r="CT6" s="28"/>
+      <c r="CU6" s="28"/>
+      <c r="CV6" s="28"/>
+      <c r="CW6" s="28"/>
+      <c r="CX6" s="28"/>
+      <c r="CY6" s="28"/>
+      <c r="CZ6" s="28"/>
+      <c r="DA6" s="28"/>
+      <c r="DB6" s="28"/>
+      <c r="DC6" s="28"/>
+      <c r="DD6" s="28"/>
+      <c r="DE6" s="28"/>
+      <c r="DF6" s="28"/>
+      <c r="DG6" s="28"/>
+      <c r="DH6" s="28"/>
+      <c r="DI6" s="28"/>
+      <c r="DJ6" s="28"/>
+      <c r="DK6" s="28"/>
+      <c r="DL6" s="28"/>
+      <c r="DM6" s="28"/>
+      <c r="DN6" s="28"/>
+      <c r="DO6" s="28"/>
+      <c r="DP6" s="28"/>
+      <c r="DQ6" s="28"/>
+      <c r="DR6" s="28"/>
+      <c r="DS6" s="28"/>
+      <c r="DT6" s="28"/>
+      <c r="DU6" s="28"/>
+      <c r="DV6" s="28"/>
+      <c r="DW6" s="28"/>
+      <c r="DX6" s="28"/>
+      <c r="DY6" s="28"/>
+      <c r="DZ6" s="28"/>
+      <c r="EA6" s="28"/>
+      <c r="EB6" s="28"/>
+      <c r="EC6" s="28"/>
+      <c r="ED6" s="28"/>
+      <c r="EE6" s="28"/>
+      <c r="EF6" s="28"/>
+      <c r="EG6" s="28"/>
+      <c r="EH6" s="28"/>
+      <c r="EI6" s="28"/>
+      <c r="EJ6" s="28"/>
+      <c r="EK6" s="28"/>
+      <c r="EL6" s="28"/>
+      <c r="EM6" s="28"/>
+      <c r="EN6" s="28"/>
+      <c r="EO6" s="28"/>
+      <c r="EP6" s="28"/>
+      <c r="EQ6" s="28"/>
+      <c r="ER6" s="28"/>
+      <c r="ES6" s="28"/>
+      <c r="ET6" s="28"/>
+      <c r="EU6" s="28"/>
     </row>
     <row r="7" ht="24.75" customHeight="1">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="B7" s="41">
+      <c r="B7" s="31">
         <v>78.0</v>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="31">
         <v>98.0</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="31">
         <v>20.0</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="31">
         <v>7.0</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="31">
         <v>126.0</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="I7" s="41" t="s">
+      <c r="I7" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="J7" s="41" t="s">
+      <c r="J7" s="31" t="s">
         <v>106</v>
       </c>
-      <c r="K7" s="41" t="s">
+      <c r="K7" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="L7" s="41" t="s">
+      <c r="L7" s="31" t="s">
         <v>269</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="31" t="s">
         <v>270</v>
       </c>
-      <c r="N7" s="37"/>
-      <c r="O7" s="37"/>
-      <c r="P7" s="37"/>
-      <c r="Q7" s="37"/>
-      <c r="R7" s="37"/>
-      <c r="S7" s="37"/>
-      <c r="T7" s="37"/>
-      <c r="U7" s="37"/>
-      <c r="V7" s="37"/>
-      <c r="W7" s="37"/>
-      <c r="X7" s="37"/>
-      <c r="Y7" s="37"/>
-      <c r="Z7" s="37"/>
-      <c r="AA7" s="37"/>
-      <c r="AB7" s="37"/>
-      <c r="AC7" s="37"/>
-      <c r="AD7" s="37"/>
-      <c r="AE7" s="37"/>
-      <c r="AF7" s="37"/>
-      <c r="AG7" s="37"/>
-      <c r="AH7" s="37"/>
-      <c r="AI7" s="37"/>
-      <c r="AJ7" s="37"/>
-      <c r="AK7" s="37"/>
-      <c r="AL7" s="37"/>
-      <c r="AM7" s="37"/>
-      <c r="AN7" s="37"/>
-      <c r="AO7" s="37"/>
-      <c r="AP7" s="37"/>
-      <c r="AQ7" s="37"/>
-      <c r="AR7" s="37"/>
-      <c r="AS7" s="37"/>
-      <c r="AT7" s="37"/>
-      <c r="AU7" s="37"/>
-      <c r="AV7" s="37"/>
-      <c r="AW7" s="37"/>
-      <c r="AX7" s="37"/>
-      <c r="AY7" s="37"/>
-      <c r="AZ7" s="37"/>
-      <c r="BA7" s="37"/>
-      <c r="BB7" s="37"/>
-      <c r="BC7" s="37"/>
-      <c r="BD7" s="37"/>
-      <c r="BE7" s="37"/>
-      <c r="BF7" s="37"/>
-      <c r="BG7" s="37"/>
-      <c r="BH7" s="37"/>
-      <c r="BI7" s="37"/>
-      <c r="BJ7" s="37"/>
-      <c r="BK7" s="37"/>
-      <c r="BL7" s="37"/>
-      <c r="BM7" s="37"/>
-      <c r="BN7" s="37"/>
-      <c r="BO7" s="37"/>
-      <c r="BP7" s="37"/>
-      <c r="BQ7" s="37"/>
-      <c r="BR7" s="37"/>
-      <c r="BS7" s="37"/>
-      <c r="BT7" s="37"/>
-      <c r="BU7" s="37"/>
-      <c r="BV7" s="37"/>
-      <c r="BW7" s="37"/>
-      <c r="BX7" s="37"/>
-      <c r="BY7" s="37"/>
-      <c r="BZ7" s="37"/>
-      <c r="CA7" s="37"/>
-      <c r="CB7" s="37"/>
-      <c r="CC7" s="37"/>
-      <c r="CD7" s="37"/>
-      <c r="CE7" s="37"/>
-      <c r="CF7" s="37"/>
-      <c r="CG7" s="37"/>
-      <c r="CH7" s="37"/>
-      <c r="CI7" s="37"/>
-      <c r="CJ7" s="37"/>
-      <c r="CK7" s="37"/>
-      <c r="CL7" s="37"/>
-      <c r="CM7" s="37"/>
-      <c r="CN7" s="37"/>
-      <c r="CO7" s="37"/>
-      <c r="CP7" s="37"/>
-      <c r="CQ7" s="37"/>
-      <c r="CR7" s="37"/>
-      <c r="CS7" s="37"/>
-      <c r="CT7" s="37"/>
-      <c r="CU7" s="37"/>
-      <c r="CV7" s="37"/>
-      <c r="CW7" s="37"/>
-      <c r="CX7" s="37"/>
-      <c r="CY7" s="37"/>
-      <c r="CZ7" s="37"/>
-      <c r="DA7" s="37"/>
-      <c r="DB7" s="37"/>
-      <c r="DC7" s="37"/>
-      <c r="DD7" s="37"/>
-      <c r="DE7" s="37"/>
-      <c r="DF7" s="37"/>
-      <c r="DG7" s="37"/>
-      <c r="DH7" s="37"/>
-      <c r="DI7" s="37"/>
-      <c r="DJ7" s="37"/>
-      <c r="DK7" s="37"/>
-      <c r="DL7" s="37"/>
-      <c r="DM7" s="37"/>
-      <c r="DN7" s="37"/>
-      <c r="DO7" s="37"/>
-      <c r="DP7" s="37"/>
-      <c r="DQ7" s="37"/>
-      <c r="DR7" s="37"/>
-      <c r="DS7" s="37"/>
-      <c r="DT7" s="37"/>
-      <c r="DU7" s="37"/>
-      <c r="DV7" s="37"/>
-      <c r="DW7" s="37"/>
-      <c r="DX7" s="37"/>
-      <c r="DY7" s="37"/>
-      <c r="DZ7" s="37"/>
-      <c r="EA7" s="37"/>
-      <c r="EB7" s="37"/>
-      <c r="EC7" s="37"/>
-      <c r="ED7" s="37"/>
-      <c r="EE7" s="37"/>
-      <c r="EF7" s="37"/>
-      <c r="EG7" s="37"/>
-      <c r="EH7" s="37"/>
-      <c r="EI7" s="37"/>
-      <c r="EJ7" s="37"/>
-      <c r="EK7" s="37"/>
-      <c r="EL7" s="37"/>
-      <c r="EM7" s="37"/>
-      <c r="EN7" s="37"/>
-      <c r="EO7" s="37"/>
-      <c r="EP7" s="37"/>
-      <c r="EQ7" s="37"/>
-      <c r="ER7" s="37"/>
-      <c r="ES7" s="37"/>
-      <c r="ET7" s="37"/>
-      <c r="EU7" s="37"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28"/>
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28"/>
+      <c r="T7" s="28"/>
+      <c r="U7" s="28"/>
+      <c r="V7" s="28"/>
+      <c r="W7" s="28"/>
+      <c r="X7" s="28"/>
+      <c r="Y7" s="28"/>
+      <c r="Z7" s="28"/>
+      <c r="AA7" s="28"/>
+      <c r="AB7" s="28"/>
+      <c r="AC7" s="28"/>
+      <c r="AD7" s="28"/>
+      <c r="AE7" s="28"/>
+      <c r="AF7" s="28"/>
+      <c r="AG7" s="28"/>
+      <c r="AH7" s="28"/>
+      <c r="AI7" s="28"/>
+      <c r="AJ7" s="28"/>
+      <c r="AK7" s="28"/>
+      <c r="AL7" s="28"/>
+      <c r="AM7" s="28"/>
+      <c r="AN7" s="28"/>
+      <c r="AO7" s="28"/>
+      <c r="AP7" s="28"/>
+      <c r="AQ7" s="28"/>
+      <c r="AR7" s="28"/>
+      <c r="AS7" s="28"/>
+      <c r="AT7" s="28"/>
+      <c r="AU7" s="28"/>
+      <c r="AV7" s="28"/>
+      <c r="AW7" s="28"/>
+      <c r="AX7" s="28"/>
+      <c r="AY7" s="28"/>
+      <c r="AZ7" s="28"/>
+      <c r="BA7" s="28"/>
+      <c r="BB7" s="28"/>
+      <c r="BC7" s="28"/>
+      <c r="BD7" s="28"/>
+      <c r="BE7" s="28"/>
+      <c r="BF7" s="28"/>
+      <c r="BG7" s="28"/>
+      <c r="BH7" s="28"/>
+      <c r="BI7" s="28"/>
+      <c r="BJ7" s="28"/>
+      <c r="BK7" s="28"/>
+      <c r="BL7" s="28"/>
+      <c r="BM7" s="28"/>
+      <c r="BN7" s="28"/>
+      <c r="BO7" s="28"/>
+      <c r="BP7" s="28"/>
+      <c r="BQ7" s="28"/>
+      <c r="BR7" s="28"/>
+      <c r="BS7" s="28"/>
+      <c r="BT7" s="28"/>
+      <c r="BU7" s="28"/>
+      <c r="BV7" s="28"/>
+      <c r="BW7" s="28"/>
+      <c r="BX7" s="28"/>
+      <c r="BY7" s="28"/>
+      <c r="BZ7" s="28"/>
+      <c r="CA7" s="28"/>
+      <c r="CB7" s="28"/>
+      <c r="CC7" s="28"/>
+      <c r="CD7" s="28"/>
+      <c r="CE7" s="28"/>
+      <c r="CF7" s="28"/>
+      <c r="CG7" s="28"/>
+      <c r="CH7" s="28"/>
+      <c r="CI7" s="28"/>
+      <c r="CJ7" s="28"/>
+      <c r="CK7" s="28"/>
+      <c r="CL7" s="28"/>
+      <c r="CM7" s="28"/>
+      <c r="CN7" s="28"/>
+      <c r="CO7" s="28"/>
+      <c r="CP7" s="28"/>
+      <c r="CQ7" s="28"/>
+      <c r="CR7" s="28"/>
+      <c r="CS7" s="28"/>
+      <c r="CT7" s="28"/>
+      <c r="CU7" s="28"/>
+      <c r="CV7" s="28"/>
+      <c r="CW7" s="28"/>
+      <c r="CX7" s="28"/>
+      <c r="CY7" s="28"/>
+      <c r="CZ7" s="28"/>
+      <c r="DA7" s="28"/>
+      <c r="DB7" s="28"/>
+      <c r="DC7" s="28"/>
+      <c r="DD7" s="28"/>
+      <c r="DE7" s="28"/>
+      <c r="DF7" s="28"/>
+      <c r="DG7" s="28"/>
+      <c r="DH7" s="28"/>
+      <c r="DI7" s="28"/>
+      <c r="DJ7" s="28"/>
+      <c r="DK7" s="28"/>
+      <c r="DL7" s="28"/>
+      <c r="DM7" s="28"/>
+      <c r="DN7" s="28"/>
+      <c r="DO7" s="28"/>
+      <c r="DP7" s="28"/>
+      <c r="DQ7" s="28"/>
+      <c r="DR7" s="28"/>
+      <c r="DS7" s="28"/>
+      <c r="DT7" s="28"/>
+      <c r="DU7" s="28"/>
+      <c r="DV7" s="28"/>
+      <c r="DW7" s="28"/>
+      <c r="DX7" s="28"/>
+      <c r="DY7" s="28"/>
+      <c r="DZ7" s="28"/>
+      <c r="EA7" s="28"/>
+      <c r="EB7" s="28"/>
+      <c r="EC7" s="28"/>
+      <c r="ED7" s="28"/>
+      <c r="EE7" s="28"/>
+      <c r="EF7" s="28"/>
+      <c r="EG7" s="28"/>
+      <c r="EH7" s="28"/>
+      <c r="EI7" s="28"/>
+      <c r="EJ7" s="28"/>
+      <c r="EK7" s="28"/>
+      <c r="EL7" s="28"/>
+      <c r="EM7" s="28"/>
+      <c r="EN7" s="28"/>
+      <c r="EO7" s="28"/>
+      <c r="EP7" s="28"/>
+      <c r="EQ7" s="28"/>
+      <c r="ER7" s="28"/>
+      <c r="ES7" s="28"/>
+      <c r="ET7" s="28"/>
+      <c r="EU7" s="28"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="B8" s="41">
+      <c r="B8" s="31">
         <v>40.0</v>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="31">
         <v>50.0</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="31">
         <v>21.0</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="31">
         <v>6.0</v>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="31">
         <v>62.0</v>
       </c>
-      <c r="H8" s="41" t="s">
+      <c r="H8" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="I8" s="41" t="s">
+      <c r="I8" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="J8" s="41" t="s">
+      <c r="J8" s="31" t="s">
         <v>271</v>
       </c>
-      <c r="K8" s="41" t="s">
+      <c r="K8" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="L8" s="41" t="s">
+      <c r="L8" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="M8" s="41" t="s">
+      <c r="M8" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="37"/>
-      <c r="R8" s="37"/>
-      <c r="S8" s="37"/>
-      <c r="T8" s="37"/>
-      <c r="U8" s="37"/>
-      <c r="V8" s="37"/>
-      <c r="W8" s="37"/>
-      <c r="X8" s="37"/>
-      <c r="Y8" s="37"/>
-      <c r="Z8" s="37"/>
-      <c r="AA8" s="37"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="37"/>
-      <c r="AD8" s="37"/>
-      <c r="AE8" s="37"/>
-      <c r="AF8" s="37"/>
-      <c r="AG8" s="37"/>
-      <c r="AH8" s="37"/>
-      <c r="AI8" s="37"/>
-      <c r="AJ8" s="37"/>
-      <c r="AK8" s="37"/>
-      <c r="AL8" s="37"/>
-      <c r="AM8" s="37"/>
-      <c r="AN8" s="37"/>
-      <c r="AO8" s="37"/>
-      <c r="AP8" s="37"/>
-      <c r="AQ8" s="37"/>
-      <c r="AR8" s="37"/>
-      <c r="AS8" s="37"/>
-      <c r="AT8" s="37"/>
-      <c r="AU8" s="37"/>
-      <c r="AV8" s="37"/>
-      <c r="AW8" s="37"/>
-      <c r="AX8" s="37"/>
-      <c r="AY8" s="37"/>
-      <c r="AZ8" s="37"/>
-      <c r="BA8" s="37"/>
-      <c r="BB8" s="37"/>
-      <c r="BC8" s="37"/>
-      <c r="BD8" s="37"/>
-      <c r="BE8" s="37"/>
-      <c r="BF8" s="37"/>
-      <c r="BG8" s="37"/>
-      <c r="BH8" s="37"/>
-      <c r="BI8" s="37"/>
-      <c r="BJ8" s="37"/>
-      <c r="BK8" s="37"/>
-      <c r="BL8" s="37"/>
-      <c r="BM8" s="37"/>
-      <c r="BN8" s="37"/>
-      <c r="BO8" s="37"/>
-      <c r="BP8" s="37"/>
-      <c r="BQ8" s="37"/>
-      <c r="BR8" s="37"/>
-      <c r="BS8" s="37"/>
-      <c r="BT8" s="37"/>
-      <c r="BU8" s="37"/>
-      <c r="BV8" s="37"/>
-      <c r="BW8" s="37"/>
-      <c r="BX8" s="37"/>
-      <c r="BY8" s="37"/>
-      <c r="BZ8" s="37"/>
-      <c r="CA8" s="37"/>
-      <c r="CB8" s="37"/>
-      <c r="CC8" s="37"/>
-      <c r="CD8" s="37"/>
-      <c r="CE8" s="37"/>
-      <c r="CF8" s="37"/>
-      <c r="CG8" s="37"/>
-      <c r="CH8" s="37"/>
-      <c r="CI8" s="37"/>
-      <c r="CJ8" s="37"/>
-      <c r="CK8" s="37"/>
-      <c r="CL8" s="37"/>
-      <c r="CM8" s="37"/>
-      <c r="CN8" s="37"/>
-      <c r="CO8" s="37"/>
-      <c r="CP8" s="37"/>
-      <c r="CQ8" s="37"/>
-      <c r="CR8" s="37"/>
-      <c r="CS8" s="37"/>
-      <c r="CT8" s="37"/>
-      <c r="CU8" s="37"/>
-      <c r="CV8" s="37"/>
-      <c r="CW8" s="37"/>
-      <c r="CX8" s="37"/>
-      <c r="CY8" s="37"/>
-      <c r="CZ8" s="37"/>
-      <c r="DA8" s="37"/>
-      <c r="DB8" s="37"/>
-      <c r="DC8" s="37"/>
-      <c r="DD8" s="37"/>
-      <c r="DE8" s="37"/>
-      <c r="DF8" s="37"/>
-      <c r="DG8" s="37"/>
-      <c r="DH8" s="37"/>
-      <c r="DI8" s="37"/>
-      <c r="DJ8" s="37"/>
-      <c r="DK8" s="37"/>
-      <c r="DL8" s="37"/>
-      <c r="DM8" s="37"/>
-      <c r="DN8" s="37"/>
-      <c r="DO8" s="37"/>
-      <c r="DP8" s="37"/>
-      <c r="DQ8" s="37"/>
-      <c r="DR8" s="37"/>
-      <c r="DS8" s="37"/>
-      <c r="DT8" s="37"/>
-      <c r="DU8" s="37"/>
-      <c r="DV8" s="37"/>
-      <c r="DW8" s="37"/>
-      <c r="DX8" s="37"/>
-      <c r="DY8" s="37"/>
-      <c r="DZ8" s="37"/>
-      <c r="EA8" s="37"/>
-      <c r="EB8" s="37"/>
-      <c r="EC8" s="37"/>
-      <c r="ED8" s="37"/>
-      <c r="EE8" s="37"/>
-      <c r="EF8" s="37"/>
-      <c r="EG8" s="37"/>
-      <c r="EH8" s="37"/>
-      <c r="EI8" s="37"/>
-      <c r="EJ8" s="37"/>
-      <c r="EK8" s="37"/>
-      <c r="EL8" s="37"/>
-      <c r="EM8" s="37"/>
-      <c r="EN8" s="37"/>
-      <c r="EO8" s="37"/>
-      <c r="EP8" s="37"/>
-      <c r="EQ8" s="37"/>
-      <c r="ER8" s="37"/>
-      <c r="ES8" s="37"/>
-      <c r="ET8" s="37"/>
-      <c r="EU8" s="37"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="28"/>
+      <c r="Q8" s="28"/>
+      <c r="R8" s="28"/>
+      <c r="S8" s="28"/>
+      <c r="T8" s="28"/>
+      <c r="U8" s="28"/>
+      <c r="V8" s="28"/>
+      <c r="W8" s="28"/>
+      <c r="X8" s="28"/>
+      <c r="Y8" s="28"/>
+      <c r="Z8" s="28"/>
+      <c r="AA8" s="28"/>
+      <c r="AB8" s="28"/>
+      <c r="AC8" s="28"/>
+      <c r="AD8" s="28"/>
+      <c r="AE8" s="28"/>
+      <c r="AF8" s="28"/>
+      <c r="AG8" s="28"/>
+      <c r="AH8" s="28"/>
+      <c r="AI8" s="28"/>
+      <c r="AJ8" s="28"/>
+      <c r="AK8" s="28"/>
+      <c r="AL8" s="28"/>
+      <c r="AM8" s="28"/>
+      <c r="AN8" s="28"/>
+      <c r="AO8" s="28"/>
+      <c r="AP8" s="28"/>
+      <c r="AQ8" s="28"/>
+      <c r="AR8" s="28"/>
+      <c r="AS8" s="28"/>
+      <c r="AT8" s="28"/>
+      <c r="AU8" s="28"/>
+      <c r="AV8" s="28"/>
+      <c r="AW8" s="28"/>
+      <c r="AX8" s="28"/>
+      <c r="AY8" s="28"/>
+      <c r="AZ8" s="28"/>
+      <c r="BA8" s="28"/>
+      <c r="BB8" s="28"/>
+      <c r="BC8" s="28"/>
+      <c r="BD8" s="28"/>
+      <c r="BE8" s="28"/>
+      <c r="BF8" s="28"/>
+      <c r="BG8" s="28"/>
+      <c r="BH8" s="28"/>
+      <c r="BI8" s="28"/>
+      <c r="BJ8" s="28"/>
+      <c r="BK8" s="28"/>
+      <c r="BL8" s="28"/>
+      <c r="BM8" s="28"/>
+      <c r="BN8" s="28"/>
+      <c r="BO8" s="28"/>
+      <c r="BP8" s="28"/>
+      <c r="BQ8" s="28"/>
+      <c r="BR8" s="28"/>
+      <c r="BS8" s="28"/>
+      <c r="BT8" s="28"/>
+      <c r="BU8" s="28"/>
+      <c r="BV8" s="28"/>
+      <c r="BW8" s="28"/>
+      <c r="BX8" s="28"/>
+      <c r="BY8" s="28"/>
+      <c r="BZ8" s="28"/>
+      <c r="CA8" s="28"/>
+      <c r="CB8" s="28"/>
+      <c r="CC8" s="28"/>
+      <c r="CD8" s="28"/>
+      <c r="CE8" s="28"/>
+      <c r="CF8" s="28"/>
+      <c r="CG8" s="28"/>
+      <c r="CH8" s="28"/>
+      <c r="CI8" s="28"/>
+      <c r="CJ8" s="28"/>
+      <c r="CK8" s="28"/>
+      <c r="CL8" s="28"/>
+      <c r="CM8" s="28"/>
+      <c r="CN8" s="28"/>
+      <c r="CO8" s="28"/>
+      <c r="CP8" s="28"/>
+      <c r="CQ8" s="28"/>
+      <c r="CR8" s="28"/>
+      <c r="CS8" s="28"/>
+      <c r="CT8" s="28"/>
+      <c r="CU8" s="28"/>
+      <c r="CV8" s="28"/>
+      <c r="CW8" s="28"/>
+      <c r="CX8" s="28"/>
+      <c r="CY8" s="28"/>
+      <c r="CZ8" s="28"/>
+      <c r="DA8" s="28"/>
+      <c r="DB8" s="28"/>
+      <c r="DC8" s="28"/>
+      <c r="DD8" s="28"/>
+      <c r="DE8" s="28"/>
+      <c r="DF8" s="28"/>
+      <c r="DG8" s="28"/>
+      <c r="DH8" s="28"/>
+      <c r="DI8" s="28"/>
+      <c r="DJ8" s="28"/>
+      <c r="DK8" s="28"/>
+      <c r="DL8" s="28"/>
+      <c r="DM8" s="28"/>
+      <c r="DN8" s="28"/>
+      <c r="DO8" s="28"/>
+      <c r="DP8" s="28"/>
+      <c r="DQ8" s="28"/>
+      <c r="DR8" s="28"/>
+      <c r="DS8" s="28"/>
+      <c r="DT8" s="28"/>
+      <c r="DU8" s="28"/>
+      <c r="DV8" s="28"/>
+      <c r="DW8" s="28"/>
+      <c r="DX8" s="28"/>
+      <c r="DY8" s="28"/>
+      <c r="DZ8" s="28"/>
+      <c r="EA8" s="28"/>
+      <c r="EB8" s="28"/>
+      <c r="EC8" s="28"/>
+      <c r="ED8" s="28"/>
+      <c r="EE8" s="28"/>
+      <c r="EF8" s="28"/>
+      <c r="EG8" s="28"/>
+      <c r="EH8" s="28"/>
+      <c r="EI8" s="28"/>
+      <c r="EJ8" s="28"/>
+      <c r="EK8" s="28"/>
+      <c r="EL8" s="28"/>
+      <c r="EM8" s="28"/>
+      <c r="EN8" s="28"/>
+      <c r="EO8" s="28"/>
+      <c r="EP8" s="28"/>
+      <c r="EQ8" s="28"/>
+      <c r="ER8" s="28"/>
+      <c r="ES8" s="28"/>
+      <c r="ET8" s="28"/>
+      <c r="EU8" s="28"/>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="B9" s="41">
+      <c r="B9" s="31">
         <v>16.0</v>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="31">
         <v>20.0</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="31">
         <v>22.0</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="31">
         <v>5.0</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="31">
         <v>30.0</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="H9" s="31" t="s">
         <v>205</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="31" t="s">
         <v>275</v>
       </c>
-      <c r="K9" s="41" t="s">
+      <c r="K9" s="31" t="s">
         <v>276</v>
       </c>
-      <c r="L9" s="41" t="s">
+      <c r="L9" s="31" t="s">
         <v>277</v>
       </c>
-      <c r="M9" s="41" t="s">
+      <c r="M9" s="31" t="s">
         <v>278</v>
       </c>
-      <c r="N9" s="37"/>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="37"/>
-      <c r="T9" s="37"/>
-      <c r="U9" s="37"/>
-      <c r="V9" s="37"/>
-      <c r="W9" s="37"/>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="37"/>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="37"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="37"/>
-      <c r="AD9" s="37"/>
-      <c r="AE9" s="37"/>
-      <c r="AF9" s="37"/>
-      <c r="AG9" s="37"/>
-      <c r="AH9" s="37"/>
-      <c r="AI9" s="37"/>
-      <c r="AJ9" s="37"/>
-      <c r="AK9" s="37"/>
-      <c r="AL9" s="37"/>
-      <c r="AM9" s="37"/>
-      <c r="AN9" s="37"/>
-      <c r="AO9" s="37"/>
-      <c r="AP9" s="37"/>
-      <c r="AQ9" s="37"/>
-      <c r="AR9" s="37"/>
-      <c r="AS9" s="37"/>
-      <c r="AT9" s="37"/>
-      <c r="AU9" s="37"/>
-      <c r="AV9" s="37"/>
-      <c r="AW9" s="37"/>
-      <c r="AX9" s="37"/>
-      <c r="AY9" s="37"/>
-      <c r="AZ9" s="37"/>
-      <c r="BA9" s="37"/>
-      <c r="BB9" s="37"/>
-      <c r="BC9" s="37"/>
-      <c r="BD9" s="37"/>
-      <c r="BE9" s="37"/>
-      <c r="BF9" s="37"/>
-      <c r="BG9" s="37"/>
-      <c r="BH9" s="37"/>
-      <c r="BI9" s="37"/>
-      <c r="BJ9" s="37"/>
-      <c r="BK9" s="37"/>
-      <c r="BL9" s="37"/>
-      <c r="BM9" s="37"/>
-      <c r="BN9" s="37"/>
-      <c r="BO9" s="37"/>
-      <c r="BP9" s="37"/>
-      <c r="BQ9" s="37"/>
-      <c r="BR9" s="37"/>
-      <c r="BS9" s="37"/>
-      <c r="BT9" s="37"/>
-      <c r="BU9" s="37"/>
-      <c r="BV9" s="37"/>
-      <c r="BW9" s="37"/>
-      <c r="BX9" s="37"/>
-      <c r="BY9" s="37"/>
-      <c r="BZ9" s="37"/>
-      <c r="CA9" s="37"/>
-      <c r="CB9" s="37"/>
-      <c r="CC9" s="37"/>
-      <c r="CD9" s="37"/>
-      <c r="CE9" s="37"/>
-      <c r="CF9" s="37"/>
-      <c r="CG9" s="37"/>
-      <c r="CH9" s="37"/>
-      <c r="CI9" s="37"/>
-      <c r="CJ9" s="37"/>
-      <c r="CK9" s="37"/>
-      <c r="CL9" s="37"/>
-      <c r="CM9" s="37"/>
-      <c r="CN9" s="37"/>
-      <c r="CO9" s="37"/>
-      <c r="CP9" s="37"/>
-      <c r="CQ9" s="37"/>
-      <c r="CR9" s="37"/>
-      <c r="CS9" s="37"/>
-      <c r="CT9" s="37"/>
-      <c r="CU9" s="37"/>
-      <c r="CV9" s="37"/>
-      <c r="CW9" s="37"/>
-      <c r="CX9" s="37"/>
-      <c r="CY9" s="37"/>
-      <c r="CZ9" s="37"/>
-      <c r="DA9" s="37"/>
-      <c r="DB9" s="37"/>
-      <c r="DC9" s="37"/>
-      <c r="DD9" s="37"/>
-      <c r="DE9" s="37"/>
-      <c r="DF9" s="37"/>
-      <c r="DG9" s="37"/>
-      <c r="DH9" s="37"/>
-      <c r="DI9" s="37"/>
-      <c r="DJ9" s="37"/>
-      <c r="DK9" s="37"/>
-      <c r="DL9" s="37"/>
-      <c r="DM9" s="37"/>
-      <c r="DN9" s="37"/>
-      <c r="DO9" s="37"/>
-      <c r="DP9" s="37"/>
-      <c r="DQ9" s="37"/>
-      <c r="DR9" s="37"/>
-      <c r="DS9" s="37"/>
-      <c r="DT9" s="37"/>
-      <c r="DU9" s="37"/>
-      <c r="DV9" s="37"/>
-      <c r="DW9" s="37"/>
-      <c r="DX9" s="37"/>
-      <c r="DY9" s="37"/>
-      <c r="DZ9" s="37"/>
-      <c r="EA9" s="37"/>
-      <c r="EB9" s="37"/>
-      <c r="EC9" s="37"/>
-      <c r="ED9" s="37"/>
-      <c r="EE9" s="37"/>
-      <c r="EF9" s="37"/>
-      <c r="EG9" s="37"/>
-      <c r="EH9" s="37"/>
-      <c r="EI9" s="37"/>
-      <c r="EJ9" s="37"/>
-      <c r="EK9" s="37"/>
-      <c r="EL9" s="37"/>
-      <c r="EM9" s="37"/>
-      <c r="EN9" s="37"/>
-      <c r="EO9" s="37"/>
-      <c r="EP9" s="37"/>
-      <c r="EQ9" s="37"/>
-      <c r="ER9" s="37"/>
-      <c r="ES9" s="37"/>
-      <c r="ET9" s="37"/>
-      <c r="EU9" s="37"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28"/>
+      <c r="P9" s="28"/>
+      <c r="Q9" s="28"/>
+      <c r="R9" s="28"/>
+      <c r="S9" s="28"/>
+      <c r="T9" s="28"/>
+      <c r="U9" s="28"/>
+      <c r="V9" s="28"/>
+      <c r="W9" s="28"/>
+      <c r="X9" s="28"/>
+      <c r="Y9" s="28"/>
+      <c r="Z9" s="28"/>
+      <c r="AA9" s="28"/>
+      <c r="AB9" s="28"/>
+      <c r="AC9" s="28"/>
+      <c r="AD9" s="28"/>
+      <c r="AE9" s="28"/>
+      <c r="AF9" s="28"/>
+      <c r="AG9" s="28"/>
+      <c r="AH9" s="28"/>
+      <c r="AI9" s="28"/>
+      <c r="AJ9" s="28"/>
+      <c r="AK9" s="28"/>
+      <c r="AL9" s="28"/>
+      <c r="AM9" s="28"/>
+      <c r="AN9" s="28"/>
+      <c r="AO9" s="28"/>
+      <c r="AP9" s="28"/>
+      <c r="AQ9" s="28"/>
+      <c r="AR9" s="28"/>
+      <c r="AS9" s="28"/>
+      <c r="AT9" s="28"/>
+      <c r="AU9" s="28"/>
+      <c r="AV9" s="28"/>
+      <c r="AW9" s="28"/>
+      <c r="AX9" s="28"/>
+      <c r="AY9" s="28"/>
+      <c r="AZ9" s="28"/>
+      <c r="BA9" s="28"/>
+      <c r="BB9" s="28"/>
+      <c r="BC9" s="28"/>
+      <c r="BD9" s="28"/>
+      <c r="BE9" s="28"/>
+      <c r="BF9" s="28"/>
+      <c r="BG9" s="28"/>
+      <c r="BH9" s="28"/>
+      <c r="BI9" s="28"/>
+      <c r="BJ9" s="28"/>
+      <c r="BK9" s="28"/>
+      <c r="BL9" s="28"/>
+      <c r="BM9" s="28"/>
+      <c r="BN9" s="28"/>
+      <c r="BO9" s="28"/>
+      <c r="BP9" s="28"/>
+      <c r="BQ9" s="28"/>
+      <c r="BR9" s="28"/>
+      <c r="BS9" s="28"/>
+      <c r="BT9" s="28"/>
+      <c r="BU9" s="28"/>
+      <c r="BV9" s="28"/>
+      <c r="BW9" s="28"/>
+      <c r="BX9" s="28"/>
+      <c r="BY9" s="28"/>
+      <c r="BZ9" s="28"/>
+      <c r="CA9" s="28"/>
+      <c r="CB9" s="28"/>
+      <c r="CC9" s="28"/>
+      <c r="CD9" s="28"/>
+      <c r="CE9" s="28"/>
+      <c r="CF9" s="28"/>
+      <c r="CG9" s="28"/>
+      <c r="CH9" s="28"/>
+      <c r="CI9" s="28"/>
+      <c r="CJ9" s="28"/>
+      <c r="CK9" s="28"/>
+      <c r="CL9" s="28"/>
+      <c r="CM9" s="28"/>
+      <c r="CN9" s="28"/>
+      <c r="CO9" s="28"/>
+      <c r="CP9" s="28"/>
+      <c r="CQ9" s="28"/>
+      <c r="CR9" s="28"/>
+      <c r="CS9" s="28"/>
+      <c r="CT9" s="28"/>
+      <c r="CU9" s="28"/>
+      <c r="CV9" s="28"/>
+      <c r="CW9" s="28"/>
+      <c r="CX9" s="28"/>
+      <c r="CY9" s="28"/>
+      <c r="CZ9" s="28"/>
+      <c r="DA9" s="28"/>
+      <c r="DB9" s="28"/>
+      <c r="DC9" s="28"/>
+      <c r="DD9" s="28"/>
+      <c r="DE9" s="28"/>
+      <c r="DF9" s="28"/>
+      <c r="DG9" s="28"/>
+      <c r="DH9" s="28"/>
+      <c r="DI9" s="28"/>
+      <c r="DJ9" s="28"/>
+      <c r="DK9" s="28"/>
+      <c r="DL9" s="28"/>
+      <c r="DM9" s="28"/>
+      <c r="DN9" s="28"/>
+      <c r="DO9" s="28"/>
+      <c r="DP9" s="28"/>
+      <c r="DQ9" s="28"/>
+      <c r="DR9" s="28"/>
+      <c r="DS9" s="28"/>
+      <c r="DT9" s="28"/>
+      <c r="DU9" s="28"/>
+      <c r="DV9" s="28"/>
+      <c r="DW9" s="28"/>
+      <c r="DX9" s="28"/>
+      <c r="DY9" s="28"/>
+      <c r="DZ9" s="28"/>
+      <c r="EA9" s="28"/>
+      <c r="EB9" s="28"/>
+      <c r="EC9" s="28"/>
+      <c r="ED9" s="28"/>
+      <c r="EE9" s="28"/>
+      <c r="EF9" s="28"/>
+      <c r="EG9" s="28"/>
+      <c r="EH9" s="28"/>
+      <c r="EI9" s="28"/>
+      <c r="EJ9" s="28"/>
+      <c r="EK9" s="28"/>
+      <c r="EL9" s="28"/>
+      <c r="EM9" s="28"/>
+      <c r="EN9" s="28"/>
+      <c r="EO9" s="28"/>
+      <c r="EP9" s="28"/>
+      <c r="EQ9" s="28"/>
+      <c r="ER9" s="28"/>
+      <c r="ES9" s="28"/>
+      <c r="ET9" s="28"/>
+      <c r="EU9" s="28"/>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="41">
+      <c r="B10" s="31">
         <v>12.0</v>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="31">
         <v>15.0</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="31">
         <v>23.0</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="31">
         <v>5.0</v>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="31">
         <v>30.0</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="H10" s="31" t="s">
         <v>205</v>
       </c>
-      <c r="I10" s="41" t="s">
+      <c r="I10" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="J10" s="41" t="s">
+      <c r="J10" s="31" t="s">
         <v>279</v>
       </c>
-      <c r="K10" s="41" t="s">
+      <c r="K10" s="31" t="s">
         <v>280</v>
       </c>
-      <c r="L10" s="41" t="s">
+      <c r="L10" s="31" t="s">
         <v>281</v>
       </c>
-      <c r="M10" s="41" t="s">
+      <c r="M10" s="31" t="s">
         <v>282</v>
       </c>
-      <c r="N10" s="37"/>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
-      <c r="S10" s="37"/>
-      <c r="T10" s="37"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="37"/>
-      <c r="W10" s="37"/>
-      <c r="X10" s="37"/>
-      <c r="Y10" s="37"/>
-      <c r="Z10" s="37"/>
-      <c r="AA10" s="37"/>
-      <c r="AB10" s="37"/>
-      <c r="AC10" s="37"/>
-      <c r="AD10" s="37"/>
-      <c r="AE10" s="37"/>
-      <c r="AF10" s="37"/>
-      <c r="AG10" s="37"/>
-      <c r="AH10" s="37"/>
-      <c r="AI10" s="37"/>
-      <c r="AJ10" s="37"/>
-      <c r="AK10" s="37"/>
-      <c r="AL10" s="37"/>
-      <c r="AM10" s="37"/>
-      <c r="AN10" s="37"/>
-      <c r="AO10" s="37"/>
-      <c r="AP10" s="37"/>
-      <c r="AQ10" s="37"/>
-      <c r="AR10" s="37"/>
-      <c r="AS10" s="37"/>
-      <c r="AT10" s="37"/>
-      <c r="AU10" s="37"/>
-      <c r="AV10" s="37"/>
-      <c r="AW10" s="37"/>
-      <c r="AX10" s="37"/>
-      <c r="AY10" s="37"/>
-      <c r="AZ10" s="37"/>
-      <c r="BA10" s="37"/>
-      <c r="BB10" s="37"/>
-      <c r="BC10" s="37"/>
-      <c r="BD10" s="37"/>
-      <c r="BE10" s="37"/>
-      <c r="BF10" s="37"/>
-      <c r="BG10" s="37"/>
-      <c r="BH10" s="37"/>
-      <c r="BI10" s="37"/>
-      <c r="BJ10" s="37"/>
-      <c r="BK10" s="37"/>
-      <c r="BL10" s="37"/>
-      <c r="BM10" s="37"/>
-      <c r="BN10" s="37"/>
-      <c r="BO10" s="37"/>
-      <c r="BP10" s="37"/>
-      <c r="BQ10" s="37"/>
-      <c r="BR10" s="37"/>
-      <c r="BS10" s="37"/>
-      <c r="BT10" s="37"/>
-      <c r="BU10" s="37"/>
-      <c r="BV10" s="37"/>
-      <c r="BW10" s="37"/>
-      <c r="BX10" s="37"/>
-      <c r="BY10" s="37"/>
-      <c r="BZ10" s="37"/>
-      <c r="CA10" s="37"/>
-      <c r="CB10" s="37"/>
-      <c r="CC10" s="37"/>
-      <c r="CD10" s="37"/>
-      <c r="CE10" s="37"/>
-      <c r="CF10" s="37"/>
-      <c r="CG10" s="37"/>
-      <c r="CH10" s="37"/>
-      <c r="CI10" s="37"/>
-      <c r="CJ10" s="37"/>
-      <c r="CK10" s="37"/>
-      <c r="CL10" s="37"/>
-      <c r="CM10" s="37"/>
-      <c r="CN10" s="37"/>
-      <c r="CO10" s="37"/>
-      <c r="CP10" s="37"/>
-      <c r="CQ10" s="37"/>
-      <c r="CR10" s="37"/>
-      <c r="CS10" s="37"/>
-      <c r="CT10" s="37"/>
-      <c r="CU10" s="37"/>
-      <c r="CV10" s="37"/>
-      <c r="CW10" s="37"/>
-      <c r="CX10" s="37"/>
-      <c r="CY10" s="37"/>
-      <c r="CZ10" s="37"/>
-      <c r="DA10" s="37"/>
-      <c r="DB10" s="37"/>
-      <c r="DC10" s="37"/>
-      <c r="DD10" s="37"/>
-      <c r="DE10" s="37"/>
-      <c r="DF10" s="37"/>
-      <c r="DG10" s="37"/>
-      <c r="DH10" s="37"/>
-      <c r="DI10" s="37"/>
-      <c r="DJ10" s="37"/>
-      <c r="DK10" s="37"/>
-      <c r="DL10" s="37"/>
-      <c r="DM10" s="37"/>
-      <c r="DN10" s="37"/>
-      <c r="DO10" s="37"/>
-      <c r="DP10" s="37"/>
-      <c r="DQ10" s="37"/>
-      <c r="DR10" s="37"/>
-      <c r="DS10" s="37"/>
-      <c r="DT10" s="37"/>
-      <c r="DU10" s="37"/>
-      <c r="DV10" s="37"/>
-      <c r="DW10" s="37"/>
-      <c r="DX10" s="37"/>
-      <c r="DY10" s="37"/>
-      <c r="DZ10" s="37"/>
-      <c r="EA10" s="37"/>
-      <c r="EB10" s="37"/>
-      <c r="EC10" s="37"/>
-      <c r="ED10" s="37"/>
-      <c r="EE10" s="37"/>
-      <c r="EF10" s="37"/>
-      <c r="EG10" s="37"/>
-      <c r="EH10" s="37"/>
-      <c r="EI10" s="37"/>
-      <c r="EJ10" s="37"/>
-      <c r="EK10" s="37"/>
-      <c r="EL10" s="37"/>
-      <c r="EM10" s="37"/>
-      <c r="EN10" s="37"/>
-      <c r="EO10" s="37"/>
-      <c r="EP10" s="37"/>
-      <c r="EQ10" s="37"/>
-      <c r="ER10" s="37"/>
-      <c r="ES10" s="37"/>
-      <c r="ET10" s="37"/>
-      <c r="EU10" s="37"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28"/>
+      <c r="P10" s="28"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="28"/>
+      <c r="T10" s="28"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="28"/>
+      <c r="Z10" s="28"/>
+      <c r="AA10" s="28"/>
+      <c r="AB10" s="28"/>
+      <c r="AC10" s="28"/>
+      <c r="AD10" s="28"/>
+      <c r="AE10" s="28"/>
+      <c r="AF10" s="28"/>
+      <c r="AG10" s="28"/>
+      <c r="AH10" s="28"/>
+      <c r="AI10" s="28"/>
+      <c r="AJ10" s="28"/>
+      <c r="AK10" s="28"/>
+      <c r="AL10" s="28"/>
+      <c r="AM10" s="28"/>
+      <c r="AN10" s="28"/>
+      <c r="AO10" s="28"/>
+      <c r="AP10" s="28"/>
+      <c r="AQ10" s="28"/>
+      <c r="AR10" s="28"/>
+      <c r="AS10" s="28"/>
+      <c r="AT10" s="28"/>
+      <c r="AU10" s="28"/>
+      <c r="AV10" s="28"/>
+      <c r="AW10" s="28"/>
+      <c r="AX10" s="28"/>
+      <c r="AY10" s="28"/>
+      <c r="AZ10" s="28"/>
+      <c r="BA10" s="28"/>
+      <c r="BB10" s="28"/>
+      <c r="BC10" s="28"/>
+      <c r="BD10" s="28"/>
+      <c r="BE10" s="28"/>
+      <c r="BF10" s="28"/>
+      <c r="BG10" s="28"/>
+      <c r="BH10" s="28"/>
+      <c r="BI10" s="28"/>
+      <c r="BJ10" s="28"/>
+      <c r="BK10" s="28"/>
+      <c r="BL10" s="28"/>
+      <c r="BM10" s="28"/>
+      <c r="BN10" s="28"/>
+      <c r="BO10" s="28"/>
+      <c r="BP10" s="28"/>
+      <c r="BQ10" s="28"/>
+      <c r="BR10" s="28"/>
+      <c r="BS10" s="28"/>
+      <c r="BT10" s="28"/>
+      <c r="BU10" s="28"/>
+      <c r="BV10" s="28"/>
+      <c r="BW10" s="28"/>
+      <c r="BX10" s="28"/>
+      <c r="BY10" s="28"/>
+      <c r="BZ10" s="28"/>
+      <c r="CA10" s="28"/>
+      <c r="CB10" s="28"/>
+      <c r="CC10" s="28"/>
+      <c r="CD10" s="28"/>
+      <c r="CE10" s="28"/>
+      <c r="CF10" s="28"/>
+      <c r="CG10" s="28"/>
+      <c r="CH10" s="28"/>
+      <c r="CI10" s="28"/>
+      <c r="CJ10" s="28"/>
+      <c r="CK10" s="28"/>
+      <c r="CL10" s="28"/>
+      <c r="CM10" s="28"/>
+      <c r="CN10" s="28"/>
+      <c r="CO10" s="28"/>
+      <c r="CP10" s="28"/>
+      <c r="CQ10" s="28"/>
+      <c r="CR10" s="28"/>
+      <c r="CS10" s="28"/>
+      <c r="CT10" s="28"/>
+      <c r="CU10" s="28"/>
+      <c r="CV10" s="28"/>
+      <c r="CW10" s="28"/>
+      <c r="CX10" s="28"/>
+      <c r="CY10" s="28"/>
+      <c r="CZ10" s="28"/>
+      <c r="DA10" s="28"/>
+      <c r="DB10" s="28"/>
+      <c r="DC10" s="28"/>
+      <c r="DD10" s="28"/>
+      <c r="DE10" s="28"/>
+      <c r="DF10" s="28"/>
+      <c r="DG10" s="28"/>
+      <c r="DH10" s="28"/>
+      <c r="DI10" s="28"/>
+      <c r="DJ10" s="28"/>
+      <c r="DK10" s="28"/>
+      <c r="DL10" s="28"/>
+      <c r="DM10" s="28"/>
+      <c r="DN10" s="28"/>
+      <c r="DO10" s="28"/>
+      <c r="DP10" s="28"/>
+      <c r="DQ10" s="28"/>
+      <c r="DR10" s="28"/>
+      <c r="DS10" s="28"/>
+      <c r="DT10" s="28"/>
+      <c r="DU10" s="28"/>
+      <c r="DV10" s="28"/>
+      <c r="DW10" s="28"/>
+      <c r="DX10" s="28"/>
+      <c r="DY10" s="28"/>
+      <c r="DZ10" s="28"/>
+      <c r="EA10" s="28"/>
+      <c r="EB10" s="28"/>
+      <c r="EC10" s="28"/>
+      <c r="ED10" s="28"/>
+      <c r="EE10" s="28"/>
+      <c r="EF10" s="28"/>
+      <c r="EG10" s="28"/>
+      <c r="EH10" s="28"/>
+      <c r="EI10" s="28"/>
+      <c r="EJ10" s="28"/>
+      <c r="EK10" s="28"/>
+      <c r="EL10" s="28"/>
+      <c r="EM10" s="28"/>
+      <c r="EN10" s="28"/>
+      <c r="EO10" s="28"/>
+      <c r="EP10" s="28"/>
+      <c r="EQ10" s="28"/>
+      <c r="ER10" s="28"/>
+      <c r="ES10" s="28"/>
+      <c r="ET10" s="28"/>
+      <c r="EU10" s="28"/>
     </row>
     <row r="11">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="31" t="s">
         <v>191</v>
       </c>
-      <c r="B11" s="41">
+      <c r="B11" s="31">
         <v>11.0</v>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="31">
         <v>14.0</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="D11" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="31">
         <v>24.0</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="31">
         <v>4.0</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="31">
         <v>14.0</v>
       </c>
-      <c r="H11" s="41" t="s">
+      <c r="H11" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I11" s="41" t="s">
+      <c r="I11" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J11" s="41" t="s">
+      <c r="J11" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="K11" s="41" t="s">
+      <c r="K11" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="L11" s="41" t="s">
+      <c r="L11" s="31" t="s">
         <v>285</v>
       </c>
-      <c r="M11" s="41" t="s">
+      <c r="M11" s="31" t="s">
         <v>286</v>
       </c>
-      <c r="N11" s="37"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="37"/>
-      <c r="Q11" s="37"/>
-      <c r="R11" s="37"/>
-      <c r="S11" s="37"/>
-      <c r="T11" s="37"/>
-      <c r="U11" s="37"/>
-      <c r="V11" s="37"/>
-      <c r="W11" s="37"/>
-      <c r="X11" s="37"/>
-      <c r="Y11" s="37"/>
-      <c r="Z11" s="37"/>
-      <c r="AA11" s="37"/>
-      <c r="AB11" s="37"/>
-      <c r="AC11" s="37"/>
-      <c r="AD11" s="37"/>
-      <c r="AE11" s="37"/>
-      <c r="AF11" s="37"/>
-      <c r="AG11" s="37"/>
-      <c r="AH11" s="37"/>
-      <c r="AI11" s="37"/>
-      <c r="AJ11" s="37"/>
-      <c r="AK11" s="37"/>
-      <c r="AL11" s="37"/>
-      <c r="AM11" s="37"/>
-      <c r="AN11" s="37"/>
-      <c r="AO11" s="37"/>
-      <c r="AP11" s="37"/>
-      <c r="AQ11" s="37"/>
-      <c r="AR11" s="37"/>
-      <c r="AS11" s="37"/>
-      <c r="AT11" s="37"/>
-      <c r="AU11" s="37"/>
-      <c r="AV11" s="37"/>
-      <c r="AW11" s="37"/>
-      <c r="AX11" s="37"/>
-      <c r="AY11" s="37"/>
-      <c r="AZ11" s="37"/>
-      <c r="BA11" s="37"/>
-      <c r="BB11" s="37"/>
-      <c r="BC11" s="37"/>
-      <c r="BD11" s="37"/>
-      <c r="BE11" s="37"/>
-      <c r="BF11" s="37"/>
-      <c r="BG11" s="37"/>
-      <c r="BH11" s="37"/>
-      <c r="BI11" s="37"/>
-      <c r="BJ11" s="37"/>
-      <c r="BK11" s="37"/>
-      <c r="BL11" s="37"/>
-      <c r="BM11" s="37"/>
-      <c r="BN11" s="37"/>
-      <c r="BO11" s="37"/>
-      <c r="BP11" s="37"/>
-      <c r="BQ11" s="37"/>
-      <c r="BR11" s="37"/>
-      <c r="BS11" s="37"/>
-      <c r="BT11" s="37"/>
-      <c r="BU11" s="37"/>
-      <c r="BV11" s="37"/>
-      <c r="BW11" s="37"/>
-      <c r="BX11" s="37"/>
-      <c r="BY11" s="37"/>
-      <c r="BZ11" s="37"/>
-      <c r="CA11" s="37"/>
-      <c r="CB11" s="37"/>
-      <c r="CC11" s="37"/>
-      <c r="CD11" s="37"/>
-      <c r="CE11" s="37"/>
-      <c r="CF11" s="37"/>
-      <c r="CG11" s="37"/>
-      <c r="CH11" s="37"/>
-      <c r="CI11" s="37"/>
-      <c r="CJ11" s="37"/>
-      <c r="CK11" s="37"/>
-      <c r="CL11" s="37"/>
-      <c r="CM11" s="37"/>
-      <c r="CN11" s="37"/>
-      <c r="CO11" s="37"/>
-      <c r="CP11" s="37"/>
-      <c r="CQ11" s="37"/>
-      <c r="CR11" s="37"/>
-      <c r="CS11" s="37"/>
-      <c r="CT11" s="37"/>
-      <c r="CU11" s="37"/>
-      <c r="CV11" s="37"/>
-      <c r="CW11" s="37"/>
-      <c r="CX11" s="37"/>
-      <c r="CY11" s="37"/>
-      <c r="CZ11" s="37"/>
-      <c r="DA11" s="37"/>
-      <c r="DB11" s="37"/>
-      <c r="DC11" s="37"/>
-      <c r="DD11" s="37"/>
-      <c r="DE11" s="37"/>
-      <c r="DF11" s="37"/>
-      <c r="DG11" s="37"/>
-      <c r="DH11" s="37"/>
-      <c r="DI11" s="37"/>
-      <c r="DJ11" s="37"/>
-      <c r="DK11" s="37"/>
-      <c r="DL11" s="37"/>
-      <c r="DM11" s="37"/>
-      <c r="DN11" s="37"/>
-      <c r="DO11" s="37"/>
-      <c r="DP11" s="37"/>
-      <c r="DQ11" s="37"/>
-      <c r="DR11" s="37"/>
-      <c r="DS11" s="37"/>
-      <c r="DT11" s="37"/>
-      <c r="DU11" s="37"/>
-      <c r="DV11" s="37"/>
-      <c r="DW11" s="37"/>
-      <c r="DX11" s="37"/>
-      <c r="DY11" s="37"/>
-      <c r="DZ11" s="37"/>
-      <c r="EA11" s="37"/>
-      <c r="EB11" s="37"/>
-      <c r="EC11" s="37"/>
-      <c r="ED11" s="37"/>
-      <c r="EE11" s="37"/>
-      <c r="EF11" s="37"/>
-      <c r="EG11" s="37"/>
-      <c r="EH11" s="37"/>
-      <c r="EI11" s="37"/>
-      <c r="EJ11" s="37"/>
-      <c r="EK11" s="37"/>
-      <c r="EL11" s="37"/>
-      <c r="EM11" s="37"/>
-      <c r="EN11" s="37"/>
-      <c r="EO11" s="37"/>
-      <c r="EP11" s="37"/>
-      <c r="EQ11" s="37"/>
-      <c r="ER11" s="37"/>
-      <c r="ES11" s="37"/>
-      <c r="ET11" s="37"/>
-      <c r="EU11" s="37"/>
+      <c r="N11" s="28"/>
+      <c r="O11" s="28"/>
+      <c r="P11" s="28"/>
+      <c r="Q11" s="28"/>
+      <c r="R11" s="28"/>
+      <c r="S11" s="28"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="28"/>
+      <c r="V11" s="28"/>
+      <c r="W11" s="28"/>
+      <c r="X11" s="28"/>
+      <c r="Y11" s="28"/>
+      <c r="Z11" s="28"/>
+      <c r="AA11" s="28"/>
+      <c r="AB11" s="28"/>
+      <c r="AC11" s="28"/>
+      <c r="AD11" s="28"/>
+      <c r="AE11" s="28"/>
+      <c r="AF11" s="28"/>
+      <c r="AG11" s="28"/>
+      <c r="AH11" s="28"/>
+      <c r="AI11" s="28"/>
+      <c r="AJ11" s="28"/>
+      <c r="AK11" s="28"/>
+      <c r="AL11" s="28"/>
+      <c r="AM11" s="28"/>
+      <c r="AN11" s="28"/>
+      <c r="AO11" s="28"/>
+      <c r="AP11" s="28"/>
+      <c r="AQ11" s="28"/>
+      <c r="AR11" s="28"/>
+      <c r="AS11" s="28"/>
+      <c r="AT11" s="28"/>
+      <c r="AU11" s="28"/>
+      <c r="AV11" s="28"/>
+      <c r="AW11" s="28"/>
+      <c r="AX11" s="28"/>
+      <c r="AY11" s="28"/>
+      <c r="AZ11" s="28"/>
+      <c r="BA11" s="28"/>
+      <c r="BB11" s="28"/>
+      <c r="BC11" s="28"/>
+      <c r="BD11" s="28"/>
+      <c r="BE11" s="28"/>
+      <c r="BF11" s="28"/>
+      <c r="BG11" s="28"/>
+      <c r="BH11" s="28"/>
+      <c r="BI11" s="28"/>
+      <c r="BJ11" s="28"/>
+      <c r="BK11" s="28"/>
+      <c r="BL11" s="28"/>
+      <c r="BM11" s="28"/>
+      <c r="BN11" s="28"/>
+      <c r="BO11" s="28"/>
+      <c r="BP11" s="28"/>
+      <c r="BQ11" s="28"/>
+      <c r="BR11" s="28"/>
+      <c r="BS11" s="28"/>
+      <c r="BT11" s="28"/>
+      <c r="BU11" s="28"/>
+      <c r="BV11" s="28"/>
+      <c r="BW11" s="28"/>
+      <c r="BX11" s="28"/>
+      <c r="BY11" s="28"/>
+      <c r="BZ11" s="28"/>
+      <c r="CA11" s="28"/>
+      <c r="CB11" s="28"/>
+      <c r="CC11" s="28"/>
+      <c r="CD11" s="28"/>
+      <c r="CE11" s="28"/>
+      <c r="CF11" s="28"/>
+      <c r="CG11" s="28"/>
+      <c r="CH11" s="28"/>
+      <c r="CI11" s="28"/>
+      <c r="CJ11" s="28"/>
+      <c r="CK11" s="28"/>
+      <c r="CL11" s="28"/>
+      <c r="CM11" s="28"/>
+      <c r="CN11" s="28"/>
+      <c r="CO11" s="28"/>
+      <c r="CP11" s="28"/>
+      <c r="CQ11" s="28"/>
+      <c r="CR11" s="28"/>
+      <c r="CS11" s="28"/>
+      <c r="CT11" s="28"/>
+      <c r="CU11" s="28"/>
+      <c r="CV11" s="28"/>
+      <c r="CW11" s="28"/>
+      <c r="CX11" s="28"/>
+      <c r="CY11" s="28"/>
+      <c r="CZ11" s="28"/>
+      <c r="DA11" s="28"/>
+      <c r="DB11" s="28"/>
+      <c r="DC11" s="28"/>
+      <c r="DD11" s="28"/>
+      <c r="DE11" s="28"/>
+      <c r="DF11" s="28"/>
+      <c r="DG11" s="28"/>
+      <c r="DH11" s="28"/>
+      <c r="DI11" s="28"/>
+      <c r="DJ11" s="28"/>
+      <c r="DK11" s="28"/>
+      <c r="DL11" s="28"/>
+      <c r="DM11" s="28"/>
+      <c r="DN11" s="28"/>
+      <c r="DO11" s="28"/>
+      <c r="DP11" s="28"/>
+      <c r="DQ11" s="28"/>
+      <c r="DR11" s="28"/>
+      <c r="DS11" s="28"/>
+      <c r="DT11" s="28"/>
+      <c r="DU11" s="28"/>
+      <c r="DV11" s="28"/>
+      <c r="DW11" s="28"/>
+      <c r="DX11" s="28"/>
+      <c r="DY11" s="28"/>
+      <c r="DZ11" s="28"/>
+      <c r="EA11" s="28"/>
+      <c r="EB11" s="28"/>
+      <c r="EC11" s="28"/>
+      <c r="ED11" s="28"/>
+      <c r="EE11" s="28"/>
+      <c r="EF11" s="28"/>
+      <c r="EG11" s="28"/>
+      <c r="EH11" s="28"/>
+      <c r="EI11" s="28"/>
+      <c r="EJ11" s="28"/>
+      <c r="EK11" s="28"/>
+      <c r="EL11" s="28"/>
+      <c r="EM11" s="28"/>
+      <c r="EN11" s="28"/>
+      <c r="EO11" s="28"/>
+      <c r="EP11" s="28"/>
+      <c r="EQ11" s="28"/>
+      <c r="ER11" s="28"/>
+      <c r="ES11" s="28"/>
+      <c r="ET11" s="28"/>
+      <c r="EU11" s="28"/>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="31">
         <v>10.0</v>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="31">
         <v>13.0</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="D12" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="31">
         <v>25.0</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="31">
         <v>4.0</v>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="31">
         <v>14.0</v>
       </c>
-      <c r="H12" s="41" t="s">
+      <c r="H12" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I12" s="41" t="s">
+      <c r="I12" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J12" s="41" t="s">
+      <c r="J12" s="31" t="s">
         <v>287</v>
       </c>
-      <c r="K12" s="41" t="s">
+      <c r="K12" s="31" t="s">
         <v>288</v>
       </c>
-      <c r="L12" s="41" t="s">
+      <c r="L12" s="31" t="s">
         <v>289</v>
       </c>
-      <c r="M12" s="41" t="s">
+      <c r="M12" s="31" t="s">
         <v>290</v>
       </c>
-      <c r="N12" s="37"/>
-      <c r="O12" s="37"/>
-      <c r="P12" s="37"/>
-      <c r="Q12" s="37"/>
-      <c r="R12" s="37"/>
-      <c r="S12" s="37"/>
-      <c r="T12" s="37"/>
-      <c r="U12" s="37"/>
-      <c r="V12" s="37"/>
-      <c r="W12" s="37"/>
-      <c r="X12" s="37"/>
-      <c r="Y12" s="37"/>
-      <c r="Z12" s="37"/>
-      <c r="AA12" s="37"/>
-      <c r="AB12" s="37"/>
-      <c r="AC12" s="37"/>
-      <c r="AD12" s="37"/>
-      <c r="AE12" s="37"/>
-      <c r="AF12" s="37"/>
-      <c r="AG12" s="37"/>
-      <c r="AH12" s="37"/>
-      <c r="AI12" s="37"/>
-      <c r="AJ12" s="37"/>
-      <c r="AK12" s="37"/>
-      <c r="AL12" s="37"/>
-      <c r="AM12" s="37"/>
-      <c r="AN12" s="37"/>
-      <c r="AO12" s="37"/>
-      <c r="AP12" s="37"/>
-      <c r="AQ12" s="37"/>
-      <c r="AR12" s="37"/>
-      <c r="AS12" s="37"/>
-      <c r="AT12" s="37"/>
-      <c r="AU12" s="37"/>
-      <c r="AV12" s="37"/>
-      <c r="AW12" s="37"/>
-      <c r="AX12" s="37"/>
-      <c r="AY12" s="37"/>
-      <c r="AZ12" s="37"/>
-      <c r="BA12" s="37"/>
-      <c r="BB12" s="37"/>
-      <c r="BC12" s="37"/>
-      <c r="BD12" s="37"/>
-      <c r="BE12" s="37"/>
-      <c r="BF12" s="37"/>
-      <c r="BG12" s="37"/>
-      <c r="BH12" s="37"/>
-      <c r="BI12" s="37"/>
-      <c r="BJ12" s="37"/>
-      <c r="BK12" s="37"/>
-      <c r="BL12" s="37"/>
-      <c r="BM12" s="37"/>
-      <c r="BN12" s="37"/>
-      <c r="BO12" s="37"/>
-      <c r="BP12" s="37"/>
-      <c r="BQ12" s="37"/>
-      <c r="BR12" s="37"/>
-      <c r="BS12" s="37"/>
-      <c r="BT12" s="37"/>
-      <c r="BU12" s="37"/>
-      <c r="BV12" s="37"/>
-      <c r="BW12" s="37"/>
-      <c r="BX12" s="37"/>
-      <c r="BY12" s="37"/>
-      <c r="BZ12" s="37"/>
-      <c r="CA12" s="37"/>
-      <c r="CB12" s="37"/>
-      <c r="CC12" s="37"/>
-      <c r="CD12" s="37"/>
-      <c r="CE12" s="37"/>
-      <c r="CF12" s="37"/>
-      <c r="CG12" s="37"/>
-      <c r="CH12" s="37"/>
-      <c r="CI12" s="37"/>
-      <c r="CJ12" s="37"/>
-      <c r="CK12" s="37"/>
-      <c r="CL12" s="37"/>
-      <c r="CM12" s="37"/>
-      <c r="CN12" s="37"/>
-      <c r="CO12" s="37"/>
-      <c r="CP12" s="37"/>
-      <c r="CQ12" s="37"/>
-      <c r="CR12" s="37"/>
-      <c r="CS12" s="37"/>
-      <c r="CT12" s="37"/>
-      <c r="CU12" s="37"/>
-      <c r="CV12" s="37"/>
-      <c r="CW12" s="37"/>
-      <c r="CX12" s="37"/>
-      <c r="CY12" s="37"/>
-      <c r="CZ12" s="37"/>
-      <c r="DA12" s="37"/>
-      <c r="DB12" s="37"/>
-      <c r="DC12" s="37"/>
-      <c r="DD12" s="37"/>
-      <c r="DE12" s="37"/>
-      <c r="DF12" s="37"/>
-      <c r="DG12" s="37"/>
-      <c r="DH12" s="37"/>
-      <c r="DI12" s="37"/>
-      <c r="DJ12" s="37"/>
-      <c r="DK12" s="37"/>
-      <c r="DL12" s="37"/>
-      <c r="DM12" s="37"/>
-      <c r="DN12" s="37"/>
-      <c r="DO12" s="37"/>
-      <c r="DP12" s="37"/>
-      <c r="DQ12" s="37"/>
-      <c r="DR12" s="37"/>
-      <c r="DS12" s="37"/>
-      <c r="DT12" s="37"/>
-      <c r="DU12" s="37"/>
-      <c r="DV12" s="37"/>
-      <c r="DW12" s="37"/>
-      <c r="DX12" s="37"/>
-      <c r="DY12" s="37"/>
-      <c r="DZ12" s="37"/>
-      <c r="EA12" s="37"/>
-      <c r="EB12" s="37"/>
-      <c r="EC12" s="37"/>
-      <c r="ED12" s="37"/>
-      <c r="EE12" s="37"/>
-      <c r="EF12" s="37"/>
-      <c r="EG12" s="37"/>
-      <c r="EH12" s="37"/>
-      <c r="EI12" s="37"/>
-      <c r="EJ12" s="37"/>
-      <c r="EK12" s="37"/>
-      <c r="EL12" s="37"/>
-      <c r="EM12" s="37"/>
-      <c r="EN12" s="37"/>
-      <c r="EO12" s="37"/>
-      <c r="EP12" s="37"/>
-      <c r="EQ12" s="37"/>
-      <c r="ER12" s="37"/>
-      <c r="ES12" s="37"/>
-      <c r="ET12" s="37"/>
-      <c r="EU12" s="37"/>
+      <c r="N12" s="28"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="28"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="28"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="28"/>
+      <c r="W12" s="28"/>
+      <c r="X12" s="28"/>
+      <c r="Y12" s="28"/>
+      <c r="Z12" s="28"/>
+      <c r="AA12" s="28"/>
+      <c r="AB12" s="28"/>
+      <c r="AC12" s="28"/>
+      <c r="AD12" s="28"/>
+      <c r="AE12" s="28"/>
+      <c r="AF12" s="28"/>
+      <c r="AG12" s="28"/>
+      <c r="AH12" s="28"/>
+      <c r="AI12" s="28"/>
+      <c r="AJ12" s="28"/>
+      <c r="AK12" s="28"/>
+      <c r="AL12" s="28"/>
+      <c r="AM12" s="28"/>
+      <c r="AN12" s="28"/>
+      <c r="AO12" s="28"/>
+      <c r="AP12" s="28"/>
+      <c r="AQ12" s="28"/>
+      <c r="AR12" s="28"/>
+      <c r="AS12" s="28"/>
+      <c r="AT12" s="28"/>
+      <c r="AU12" s="28"/>
+      <c r="AV12" s="28"/>
+      <c r="AW12" s="28"/>
+      <c r="AX12" s="28"/>
+      <c r="AY12" s="28"/>
+      <c r="AZ12" s="28"/>
+      <c r="BA12" s="28"/>
+      <c r="BB12" s="28"/>
+      <c r="BC12" s="28"/>
+      <c r="BD12" s="28"/>
+      <c r="BE12" s="28"/>
+      <c r="BF12" s="28"/>
+      <c r="BG12" s="28"/>
+      <c r="BH12" s="28"/>
+      <c r="BI12" s="28"/>
+      <c r="BJ12" s="28"/>
+      <c r="BK12" s="28"/>
+      <c r="BL12" s="28"/>
+      <c r="BM12" s="28"/>
+      <c r="BN12" s="28"/>
+      <c r="BO12" s="28"/>
+      <c r="BP12" s="28"/>
+      <c r="BQ12" s="28"/>
+      <c r="BR12" s="28"/>
+      <c r="BS12" s="28"/>
+      <c r="BT12" s="28"/>
+      <c r="BU12" s="28"/>
+      <c r="BV12" s="28"/>
+      <c r="BW12" s="28"/>
+      <c r="BX12" s="28"/>
+      <c r="BY12" s="28"/>
+      <c r="BZ12" s="28"/>
+      <c r="CA12" s="28"/>
+      <c r="CB12" s="28"/>
+      <c r="CC12" s="28"/>
+      <c r="CD12" s="28"/>
+      <c r="CE12" s="28"/>
+      <c r="CF12" s="28"/>
+      <c r="CG12" s="28"/>
+      <c r="CH12" s="28"/>
+      <c r="CI12" s="28"/>
+      <c r="CJ12" s="28"/>
+      <c r="CK12" s="28"/>
+      <c r="CL12" s="28"/>
+      <c r="CM12" s="28"/>
+      <c r="CN12" s="28"/>
+      <c r="CO12" s="28"/>
+      <c r="CP12" s="28"/>
+      <c r="CQ12" s="28"/>
+      <c r="CR12" s="28"/>
+      <c r="CS12" s="28"/>
+      <c r="CT12" s="28"/>
+      <c r="CU12" s="28"/>
+      <c r="CV12" s="28"/>
+      <c r="CW12" s="28"/>
+      <c r="CX12" s="28"/>
+      <c r="CY12" s="28"/>
+      <c r="CZ12" s="28"/>
+      <c r="DA12" s="28"/>
+      <c r="DB12" s="28"/>
+      <c r="DC12" s="28"/>
+      <c r="DD12" s="28"/>
+      <c r="DE12" s="28"/>
+      <c r="DF12" s="28"/>
+      <c r="DG12" s="28"/>
+      <c r="DH12" s="28"/>
+      <c r="DI12" s="28"/>
+      <c r="DJ12" s="28"/>
+      <c r="DK12" s="28"/>
+      <c r="DL12" s="28"/>
+      <c r="DM12" s="28"/>
+      <c r="DN12" s="28"/>
+      <c r="DO12" s="28"/>
+      <c r="DP12" s="28"/>
+      <c r="DQ12" s="28"/>
+      <c r="DR12" s="28"/>
+      <c r="DS12" s="28"/>
+      <c r="DT12" s="28"/>
+      <c r="DU12" s="28"/>
+      <c r="DV12" s="28"/>
+      <c r="DW12" s="28"/>
+      <c r="DX12" s="28"/>
+      <c r="DY12" s="28"/>
+      <c r="DZ12" s="28"/>
+      <c r="EA12" s="28"/>
+      <c r="EB12" s="28"/>
+      <c r="EC12" s="28"/>
+      <c r="ED12" s="28"/>
+      <c r="EE12" s="28"/>
+      <c r="EF12" s="28"/>
+      <c r="EG12" s="28"/>
+      <c r="EH12" s="28"/>
+      <c r="EI12" s="28"/>
+      <c r="EJ12" s="28"/>
+      <c r="EK12" s="28"/>
+      <c r="EL12" s="28"/>
+      <c r="EM12" s="28"/>
+      <c r="EN12" s="28"/>
+      <c r="EO12" s="28"/>
+      <c r="EP12" s="28"/>
+      <c r="EQ12" s="28"/>
+      <c r="ER12" s="28"/>
+      <c r="ES12" s="28"/>
+      <c r="ET12" s="28"/>
+      <c r="EU12" s="28"/>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="B13" s="41">
+      <c r="B13" s="31">
         <v>10.0</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="31">
         <v>13.0</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="D13" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="31">
         <v>99.0</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="31">
         <v>4.0</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="31">
         <v>14.0</v>
       </c>
-      <c r="H13" s="41" t="s">
+      <c r="H13" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J13" s="41" t="s">
+      <c r="J13" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="K13" s="41" t="s">
+      <c r="K13" s="31" t="s">
         <v>292</v>
       </c>
-      <c r="L13" s="41" t="s">
+      <c r="L13" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="M13" s="41" t="s">
+      <c r="M13" s="31" t="s">
         <v>294</v>
       </c>
-      <c r="N13" s="37"/>
-      <c r="O13" s="37"/>
-      <c r="P13" s="37"/>
-      <c r="Q13" s="37"/>
-      <c r="R13" s="37"/>
-      <c r="S13" s="37"/>
-      <c r="T13" s="37"/>
-      <c r="U13" s="37"/>
-      <c r="V13" s="37"/>
-      <c r="W13" s="37"/>
-      <c r="X13" s="37"/>
-      <c r="Y13" s="37"/>
-      <c r="Z13" s="37"/>
-      <c r="AA13" s="37"/>
-      <c r="AB13" s="37"/>
-      <c r="AC13" s="37"/>
-      <c r="AD13" s="37"/>
-      <c r="AE13" s="37"/>
-      <c r="AF13" s="37"/>
-      <c r="AG13" s="37"/>
-      <c r="AH13" s="37"/>
-      <c r="AI13" s="37"/>
-      <c r="AJ13" s="37"/>
-      <c r="AK13" s="37"/>
-      <c r="AL13" s="37"/>
-      <c r="AM13" s="37"/>
-      <c r="AN13" s="37"/>
-      <c r="AO13" s="37"/>
-      <c r="AP13" s="37"/>
-      <c r="AQ13" s="37"/>
-      <c r="AR13" s="37"/>
-      <c r="AS13" s="37"/>
-      <c r="AT13" s="37"/>
-      <c r="AU13" s="37"/>
-      <c r="AV13" s="37"/>
-      <c r="AW13" s="37"/>
-      <c r="AX13" s="37"/>
-      <c r="AY13" s="37"/>
-      <c r="AZ13" s="37"/>
-      <c r="BA13" s="37"/>
-      <c r="BB13" s="37"/>
-      <c r="BC13" s="37"/>
-      <c r="BD13" s="37"/>
-      <c r="BE13" s="37"/>
-      <c r="BF13" s="37"/>
-      <c r="BG13" s="37"/>
-      <c r="BH13" s="37"/>
-      <c r="BI13" s="37"/>
-      <c r="BJ13" s="37"/>
-      <c r="BK13" s="37"/>
-      <c r="BL13" s="37"/>
-      <c r="BM13" s="37"/>
-      <c r="BN13" s="37"/>
-      <c r="BO13" s="37"/>
-      <c r="BP13" s="37"/>
-      <c r="BQ13" s="37"/>
-      <c r="BR13" s="37"/>
-      <c r="BS13" s="37"/>
-      <c r="BT13" s="37"/>
-      <c r="BU13" s="37"/>
-      <c r="BV13" s="37"/>
-      <c r="BW13" s="37"/>
-      <c r="BX13" s="37"/>
-      <c r="BY13" s="37"/>
-      <c r="BZ13" s="37"/>
-      <c r="CA13" s="37"/>
-      <c r="CB13" s="37"/>
-      <c r="CC13" s="37"/>
-      <c r="CD13" s="37"/>
-      <c r="CE13" s="37"/>
-      <c r="CF13" s="37"/>
-      <c r="CG13" s="37"/>
-      <c r="CH13" s="37"/>
-      <c r="CI13" s="37"/>
-      <c r="CJ13" s="37"/>
-      <c r="CK13" s="37"/>
-      <c r="CL13" s="37"/>
-      <c r="CM13" s="37"/>
-      <c r="CN13" s="37"/>
-      <c r="CO13" s="37"/>
-      <c r="CP13" s="37"/>
-      <c r="CQ13" s="37"/>
-      <c r="CR13" s="37"/>
-      <c r="CS13" s="37"/>
-      <c r="CT13" s="37"/>
-      <c r="CU13" s="37"/>
-      <c r="CV13" s="37"/>
-      <c r="CW13" s="37"/>
-      <c r="CX13" s="37"/>
-      <c r="CY13" s="37"/>
-      <c r="CZ13" s="37"/>
-      <c r="DA13" s="37"/>
-      <c r="DB13" s="37"/>
-      <c r="DC13" s="37"/>
-      <c r="DD13" s="37"/>
-      <c r="DE13" s="37"/>
-      <c r="DF13" s="37"/>
-      <c r="DG13" s="37"/>
-      <c r="DH13" s="37"/>
-      <c r="DI13" s="37"/>
-      <c r="DJ13" s="37"/>
-      <c r="DK13" s="37"/>
-      <c r="DL13" s="37"/>
-      <c r="DM13" s="37"/>
-      <c r="DN13" s="37"/>
-      <c r="DO13" s="37"/>
-      <c r="DP13" s="37"/>
-      <c r="DQ13" s="37"/>
-      <c r="DR13" s="37"/>
-      <c r="DS13" s="37"/>
-      <c r="DT13" s="37"/>
-      <c r="DU13" s="37"/>
-      <c r="DV13" s="37"/>
-      <c r="DW13" s="37"/>
-      <c r="DX13" s="37"/>
-      <c r="DY13" s="37"/>
-      <c r="DZ13" s="37"/>
-      <c r="EA13" s="37"/>
-      <c r="EB13" s="37"/>
-      <c r="EC13" s="37"/>
-      <c r="ED13" s="37"/>
-      <c r="EE13" s="37"/>
-      <c r="EF13" s="37"/>
-      <c r="EG13" s="37"/>
-      <c r="EH13" s="37"/>
-      <c r="EI13" s="37"/>
-      <c r="EJ13" s="37"/>
-      <c r="EK13" s="37"/>
-      <c r="EL13" s="37"/>
-      <c r="EM13" s="37"/>
-      <c r="EN13" s="37"/>
-      <c r="EO13" s="37"/>
-      <c r="EP13" s="37"/>
-      <c r="EQ13" s="37"/>
-      <c r="ER13" s="37"/>
-      <c r="ES13" s="37"/>
-      <c r="ET13" s="37"/>
-      <c r="EU13" s="37"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="28"/>
+      <c r="U13" s="28"/>
+      <c r="V13" s="28"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="28"/>
+      <c r="Y13" s="28"/>
+      <c r="Z13" s="28"/>
+      <c r="AA13" s="28"/>
+      <c r="AB13" s="28"/>
+      <c r="AC13" s="28"/>
+      <c r="AD13" s="28"/>
+      <c r="AE13" s="28"/>
+      <c r="AF13" s="28"/>
+      <c r="AG13" s="28"/>
+      <c r="AH13" s="28"/>
+      <c r="AI13" s="28"/>
+      <c r="AJ13" s="28"/>
+      <c r="AK13" s="28"/>
+      <c r="AL13" s="28"/>
+      <c r="AM13" s="28"/>
+      <c r="AN13" s="28"/>
+      <c r="AO13" s="28"/>
+      <c r="AP13" s="28"/>
+      <c r="AQ13" s="28"/>
+      <c r="AR13" s="28"/>
+      <c r="AS13" s="28"/>
+      <c r="AT13" s="28"/>
+      <c r="AU13" s="28"/>
+      <c r="AV13" s="28"/>
+      <c r="AW13" s="28"/>
+      <c r="AX13" s="28"/>
+      <c r="AY13" s="28"/>
+      <c r="AZ13" s="28"/>
+      <c r="BA13" s="28"/>
+      <c r="BB13" s="28"/>
+      <c r="BC13" s="28"/>
+      <c r="BD13" s="28"/>
+      <c r="BE13" s="28"/>
+      <c r="BF13" s="28"/>
+      <c r="BG13" s="28"/>
+      <c r="BH13" s="28"/>
+      <c r="BI13" s="28"/>
+      <c r="BJ13" s="28"/>
+      <c r="BK13" s="28"/>
+      <c r="BL13" s="28"/>
+      <c r="BM13" s="28"/>
+      <c r="BN13" s="28"/>
+      <c r="BO13" s="28"/>
+      <c r="BP13" s="28"/>
+      <c r="BQ13" s="28"/>
+      <c r="BR13" s="28"/>
+      <c r="BS13" s="28"/>
+      <c r="BT13" s="28"/>
+      <c r="BU13" s="28"/>
+      <c r="BV13" s="28"/>
+      <c r="BW13" s="28"/>
+      <c r="BX13" s="28"/>
+      <c r="BY13" s="28"/>
+      <c r="BZ13" s="28"/>
+      <c r="CA13" s="28"/>
+      <c r="CB13" s="28"/>
+      <c r="CC13" s="28"/>
+      <c r="CD13" s="28"/>
+      <c r="CE13" s="28"/>
+      <c r="CF13" s="28"/>
+      <c r="CG13" s="28"/>
+      <c r="CH13" s="28"/>
+      <c r="CI13" s="28"/>
+      <c r="CJ13" s="28"/>
+      <c r="CK13" s="28"/>
+      <c r="CL13" s="28"/>
+      <c r="CM13" s="28"/>
+      <c r="CN13" s="28"/>
+      <c r="CO13" s="28"/>
+      <c r="CP13" s="28"/>
+      <c r="CQ13" s="28"/>
+      <c r="CR13" s="28"/>
+      <c r="CS13" s="28"/>
+      <c r="CT13" s="28"/>
+      <c r="CU13" s="28"/>
+      <c r="CV13" s="28"/>
+      <c r="CW13" s="28"/>
+      <c r="CX13" s="28"/>
+      <c r="CY13" s="28"/>
+      <c r="CZ13" s="28"/>
+      <c r="DA13" s="28"/>
+      <c r="DB13" s="28"/>
+      <c r="DC13" s="28"/>
+      <c r="DD13" s="28"/>
+      <c r="DE13" s="28"/>
+      <c r="DF13" s="28"/>
+      <c r="DG13" s="28"/>
+      <c r="DH13" s="28"/>
+      <c r="DI13" s="28"/>
+      <c r="DJ13" s="28"/>
+      <c r="DK13" s="28"/>
+      <c r="DL13" s="28"/>
+      <c r="DM13" s="28"/>
+      <c r="DN13" s="28"/>
+      <c r="DO13" s="28"/>
+      <c r="DP13" s="28"/>
+      <c r="DQ13" s="28"/>
+      <c r="DR13" s="28"/>
+      <c r="DS13" s="28"/>
+      <c r="DT13" s="28"/>
+      <c r="DU13" s="28"/>
+      <c r="DV13" s="28"/>
+      <c r="DW13" s="28"/>
+      <c r="DX13" s="28"/>
+      <c r="DY13" s="28"/>
+      <c r="DZ13" s="28"/>
+      <c r="EA13" s="28"/>
+      <c r="EB13" s="28"/>
+      <c r="EC13" s="28"/>
+      <c r="ED13" s="28"/>
+      <c r="EE13" s="28"/>
+      <c r="EF13" s="28"/>
+      <c r="EG13" s="28"/>
+      <c r="EH13" s="28"/>
+      <c r="EI13" s="28"/>
+      <c r="EJ13" s="28"/>
+      <c r="EK13" s="28"/>
+      <c r="EL13" s="28"/>
+      <c r="EM13" s="28"/>
+      <c r="EN13" s="28"/>
+      <c r="EO13" s="28"/>
+      <c r="EP13" s="28"/>
+      <c r="EQ13" s="28"/>
+      <c r="ER13" s="28"/>
+      <c r="ES13" s="28"/>
+      <c r="ET13" s="28"/>
+      <c r="EU13" s="28"/>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="31" t="s">
         <v>203</v>
       </c>
-      <c r="B14" s="41">
+      <c r="B14" s="31">
         <v>8.0</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="31">
         <v>10.0</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="31">
         <v>26.0</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="31">
         <v>4.0</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="31">
         <v>14.0</v>
       </c>
-      <c r="H14" s="41" t="s">
+      <c r="H14" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I14" s="41" t="s">
+      <c r="I14" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J14" s="41" t="s">
+      <c r="J14" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="K14" s="41" t="s">
+      <c r="K14" s="31" t="s">
         <v>296</v>
       </c>
-      <c r="L14" s="41" t="s">
+      <c r="L14" s="31" t="s">
         <v>297</v>
       </c>
-      <c r="M14" s="41" t="s">
+      <c r="M14" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="N14" s="37"/>
-      <c r="O14" s="37"/>
-      <c r="P14" s="37"/>
-      <c r="Q14" s="37"/>
-      <c r="R14" s="37"/>
-      <c r="S14" s="37"/>
-      <c r="T14" s="37"/>
-      <c r="U14" s="37"/>
-      <c r="V14" s="37"/>
-      <c r="W14" s="37"/>
-      <c r="X14" s="37"/>
-      <c r="Y14" s="37"/>
-      <c r="Z14" s="37"/>
-      <c r="AA14" s="37"/>
-      <c r="AB14" s="37"/>
-      <c r="AC14" s="37"/>
-      <c r="AD14" s="37"/>
-      <c r="AE14" s="37"/>
-      <c r="AF14" s="37"/>
-      <c r="AG14" s="37"/>
-      <c r="AH14" s="37"/>
-      <c r="AI14" s="37"/>
-      <c r="AJ14" s="37"/>
-      <c r="AK14" s="37"/>
-      <c r="AL14" s="37"/>
-      <c r="AM14" s="37"/>
-      <c r="AN14" s="37"/>
-      <c r="AO14" s="37"/>
-      <c r="AP14" s="37"/>
-      <c r="AQ14" s="37"/>
-      <c r="AR14" s="37"/>
-      <c r="AS14" s="37"/>
-      <c r="AT14" s="37"/>
-      <c r="AU14" s="37"/>
-      <c r="AV14" s="37"/>
-      <c r="AW14" s="37"/>
-      <c r="AX14" s="37"/>
-      <c r="AY14" s="37"/>
-      <c r="AZ14" s="37"/>
-      <c r="BA14" s="37"/>
-      <c r="BB14" s="37"/>
-      <c r="BC14" s="37"/>
-      <c r="BD14" s="37"/>
-      <c r="BE14" s="37"/>
-      <c r="BF14" s="37"/>
-      <c r="BG14" s="37"/>
-      <c r="BH14" s="37"/>
-      <c r="BI14" s="37"/>
-      <c r="BJ14" s="37"/>
-      <c r="BK14" s="37"/>
-      <c r="BL14" s="37"/>
-      <c r="BM14" s="37"/>
-      <c r="BN14" s="37"/>
-      <c r="BO14" s="37"/>
-      <c r="BP14" s="37"/>
-      <c r="BQ14" s="37"/>
-      <c r="BR14" s="37"/>
-      <c r="BS14" s="37"/>
-      <c r="BT14" s="37"/>
-      <c r="BU14" s="37"/>
-      <c r="BV14" s="37"/>
-      <c r="BW14" s="37"/>
-      <c r="BX14" s="37"/>
-      <c r="BY14" s="37"/>
-      <c r="BZ14" s="37"/>
-      <c r="CA14" s="37"/>
-      <c r="CB14" s="37"/>
-      <c r="CC14" s="37"/>
-      <c r="CD14" s="37"/>
-      <c r="CE14" s="37"/>
-      <c r="CF14" s="37"/>
-      <c r="CG14" s="37"/>
-      <c r="CH14" s="37"/>
-      <c r="CI14" s="37"/>
-      <c r="CJ14" s="37"/>
-      <c r="CK14" s="37"/>
-      <c r="CL14" s="37"/>
-      <c r="CM14" s="37"/>
-      <c r="CN14" s="37"/>
-      <c r="CO14" s="37"/>
-      <c r="CP14" s="37"/>
-      <c r="CQ14" s="37"/>
-      <c r="CR14" s="37"/>
-      <c r="CS14" s="37"/>
-      <c r="CT14" s="37"/>
-      <c r="CU14" s="37"/>
-      <c r="CV14" s="37"/>
-      <c r="CW14" s="37"/>
-      <c r="CX14" s="37"/>
-      <c r="CY14" s="37"/>
-      <c r="CZ14" s="37"/>
-      <c r="DA14" s="37"/>
-      <c r="DB14" s="37"/>
-      <c r="DC14" s="37"/>
-      <c r="DD14" s="37"/>
-      <c r="DE14" s="37"/>
-      <c r="DF14" s="37"/>
-      <c r="DG14" s="37"/>
-      <c r="DH14" s="37"/>
-      <c r="DI14" s="37"/>
-      <c r="DJ14" s="37"/>
-      <c r="DK14" s="37"/>
-      <c r="DL14" s="37"/>
-      <c r="DM14" s="37"/>
-      <c r="DN14" s="37"/>
-      <c r="DO14" s="37"/>
-      <c r="DP14" s="37"/>
-      <c r="DQ14" s="37"/>
-      <c r="DR14" s="37"/>
-      <c r="DS14" s="37"/>
-      <c r="DT14" s="37"/>
-      <c r="DU14" s="37"/>
-      <c r="DV14" s="37"/>
-      <c r="DW14" s="37"/>
-      <c r="DX14" s="37"/>
-      <c r="DY14" s="37"/>
-      <c r="DZ14" s="37"/>
-      <c r="EA14" s="37"/>
-      <c r="EB14" s="37"/>
-      <c r="EC14" s="37"/>
-      <c r="ED14" s="37"/>
-      <c r="EE14" s="37"/>
-      <c r="EF14" s="37"/>
-      <c r="EG14" s="37"/>
-      <c r="EH14" s="37"/>
-      <c r="EI14" s="37"/>
-      <c r="EJ14" s="37"/>
-      <c r="EK14" s="37"/>
-      <c r="EL14" s="37"/>
-      <c r="EM14" s="37"/>
-      <c r="EN14" s="37"/>
-      <c r="EO14" s="37"/>
-      <c r="EP14" s="37"/>
-      <c r="EQ14" s="37"/>
-      <c r="ER14" s="37"/>
-      <c r="ES14" s="37"/>
-      <c r="ET14" s="37"/>
-      <c r="EU14" s="37"/>
+      <c r="N14" s="28"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="28"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="28"/>
+      <c r="T14" s="28"/>
+      <c r="U14" s="28"/>
+      <c r="V14" s="28"/>
+      <c r="W14" s="28"/>
+      <c r="X14" s="28"/>
+      <c r="Y14" s="28"/>
+      <c r="Z14" s="28"/>
+      <c r="AA14" s="28"/>
+      <c r="AB14" s="28"/>
+      <c r="AC14" s="28"/>
+      <c r="AD14" s="28"/>
+      <c r="AE14" s="28"/>
+      <c r="AF14" s="28"/>
+      <c r="AG14" s="28"/>
+      <c r="AH14" s="28"/>
+      <c r="AI14" s="28"/>
+      <c r="AJ14" s="28"/>
+      <c r="AK14" s="28"/>
+      <c r="AL14" s="28"/>
+      <c r="AM14" s="28"/>
+      <c r="AN14" s="28"/>
+      <c r="AO14" s="28"/>
+      <c r="AP14" s="28"/>
+      <c r="AQ14" s="28"/>
+      <c r="AR14" s="28"/>
+      <c r="AS14" s="28"/>
+      <c r="AT14" s="28"/>
+      <c r="AU14" s="28"/>
+      <c r="AV14" s="28"/>
+      <c r="AW14" s="28"/>
+      <c r="AX14" s="28"/>
+      <c r="AY14" s="28"/>
+      <c r="AZ14" s="28"/>
+      <c r="BA14" s="28"/>
+      <c r="BB14" s="28"/>
+      <c r="BC14" s="28"/>
+      <c r="BD14" s="28"/>
+      <c r="BE14" s="28"/>
+      <c r="BF14" s="28"/>
+      <c r="BG14" s="28"/>
+      <c r="BH14" s="28"/>
+      <c r="BI14" s="28"/>
+      <c r="BJ14" s="28"/>
+      <c r="BK14" s="28"/>
+      <c r="BL14" s="28"/>
+      <c r="BM14" s="28"/>
+      <c r="BN14" s="28"/>
+      <c r="BO14" s="28"/>
+      <c r="BP14" s="28"/>
+      <c r="BQ14" s="28"/>
+      <c r="BR14" s="28"/>
+      <c r="BS14" s="28"/>
+      <c r="BT14" s="28"/>
+      <c r="BU14" s="28"/>
+      <c r="BV14" s="28"/>
+      <c r="BW14" s="28"/>
+      <c r="BX14" s="28"/>
+      <c r="BY14" s="28"/>
+      <c r="BZ14" s="28"/>
+      <c r="CA14" s="28"/>
+      <c r="CB14" s="28"/>
+      <c r="CC14" s="28"/>
+      <c r="CD14" s="28"/>
+      <c r="CE14" s="28"/>
+      <c r="CF14" s="28"/>
+      <c r="CG14" s="28"/>
+      <c r="CH14" s="28"/>
+      <c r="CI14" s="28"/>
+      <c r="CJ14" s="28"/>
+      <c r="CK14" s="28"/>
+      <c r="CL14" s="28"/>
+      <c r="CM14" s="28"/>
+      <c r="CN14" s="28"/>
+      <c r="CO14" s="28"/>
+      <c r="CP14" s="28"/>
+      <c r="CQ14" s="28"/>
+      <c r="CR14" s="28"/>
+      <c r="CS14" s="28"/>
+      <c r="CT14" s="28"/>
+      <c r="CU14" s="28"/>
+      <c r="CV14" s="28"/>
+      <c r="CW14" s="28"/>
+      <c r="CX14" s="28"/>
+      <c r="CY14" s="28"/>
+      <c r="CZ14" s="28"/>
+      <c r="DA14" s="28"/>
+      <c r="DB14" s="28"/>
+      <c r="DC14" s="28"/>
+      <c r="DD14" s="28"/>
+      <c r="DE14" s="28"/>
+      <c r="DF14" s="28"/>
+      <c r="DG14" s="28"/>
+      <c r="DH14" s="28"/>
+      <c r="DI14" s="28"/>
+      <c r="DJ14" s="28"/>
+      <c r="DK14" s="28"/>
+      <c r="DL14" s="28"/>
+      <c r="DM14" s="28"/>
+      <c r="DN14" s="28"/>
+      <c r="DO14" s="28"/>
+      <c r="DP14" s="28"/>
+      <c r="DQ14" s="28"/>
+      <c r="DR14" s="28"/>
+      <c r="DS14" s="28"/>
+      <c r="DT14" s="28"/>
+      <c r="DU14" s="28"/>
+      <c r="DV14" s="28"/>
+      <c r="DW14" s="28"/>
+      <c r="DX14" s="28"/>
+      <c r="DY14" s="28"/>
+      <c r="DZ14" s="28"/>
+      <c r="EA14" s="28"/>
+      <c r="EB14" s="28"/>
+      <c r="EC14" s="28"/>
+      <c r="ED14" s="28"/>
+      <c r="EE14" s="28"/>
+      <c r="EF14" s="28"/>
+      <c r="EG14" s="28"/>
+      <c r="EH14" s="28"/>
+      <c r="EI14" s="28"/>
+      <c r="EJ14" s="28"/>
+      <c r="EK14" s="28"/>
+      <c r="EL14" s="28"/>
+      <c r="EM14" s="28"/>
+      <c r="EN14" s="28"/>
+      <c r="EO14" s="28"/>
+      <c r="EP14" s="28"/>
+      <c r="EQ14" s="28"/>
+      <c r="ER14" s="28"/>
+      <c r="ES14" s="28"/>
+      <c r="ET14" s="28"/>
+      <c r="EU14" s="28"/>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="B15" s="41">
+      <c r="B15" s="31">
         <v>5.0</v>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="31">
         <v>7.0</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="31">
         <v>27.0</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="31">
         <v>4.0</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="31">
         <v>14.0</v>
       </c>
-      <c r="H15" s="41" t="s">
+      <c r="H15" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I15" s="41" t="s">
+      <c r="I15" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J15" s="41" t="s">
+      <c r="J15" s="31" t="s">
         <v>299</v>
       </c>
-      <c r="K15" s="41" t="s">
+      <c r="K15" s="31" t="s">
         <v>300</v>
       </c>
-      <c r="L15" s="41" t="s">
+      <c r="L15" s="31" t="s">
         <v>301</v>
       </c>
-      <c r="M15" s="41" t="s">
+      <c r="M15" s="31" t="s">
         <v>302</v>
       </c>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="37"/>
-      <c r="S15" s="37"/>
-      <c r="T15" s="37"/>
-      <c r="U15" s="37"/>
-      <c r="V15" s="37"/>
-      <c r="W15" s="37"/>
-      <c r="X15" s="37"/>
-      <c r="Y15" s="37"/>
-      <c r="Z15" s="37"/>
-      <c r="AA15" s="37"/>
-      <c r="AB15" s="37"/>
-      <c r="AC15" s="37"/>
-      <c r="AD15" s="37"/>
-      <c r="AE15" s="37"/>
-      <c r="AF15" s="37"/>
-      <c r="AG15" s="37"/>
-      <c r="AH15" s="37"/>
-      <c r="AI15" s="37"/>
-      <c r="AJ15" s="37"/>
-      <c r="AK15" s="37"/>
-      <c r="AL15" s="37"/>
-      <c r="AM15" s="37"/>
-      <c r="AN15" s="37"/>
-      <c r="AO15" s="37"/>
-      <c r="AP15" s="37"/>
-      <c r="AQ15" s="37"/>
-      <c r="AR15" s="37"/>
-      <c r="AS15" s="37"/>
-      <c r="AT15" s="37"/>
-      <c r="AU15" s="37"/>
-      <c r="AV15" s="37"/>
-      <c r="AW15" s="37"/>
-      <c r="AX15" s="37"/>
-      <c r="AY15" s="37"/>
-      <c r="AZ15" s="37"/>
-      <c r="BA15" s="37"/>
-      <c r="BB15" s="37"/>
-      <c r="BC15" s="37"/>
-      <c r="BD15" s="37"/>
-      <c r="BE15" s="37"/>
-      <c r="BF15" s="37"/>
-      <c r="BG15" s="37"/>
-      <c r="BH15" s="37"/>
-      <c r="BI15" s="37"/>
-      <c r="BJ15" s="37"/>
-      <c r="BK15" s="37"/>
-      <c r="BL15" s="37"/>
-      <c r="BM15" s="37"/>
-      <c r="BN15" s="37"/>
-      <c r="BO15" s="37"/>
-      <c r="BP15" s="37"/>
-      <c r="BQ15" s="37"/>
-      <c r="BR15" s="37"/>
-      <c r="BS15" s="37"/>
-      <c r="BT15" s="37"/>
-      <c r="BU15" s="37"/>
-      <c r="BV15" s="37"/>
-      <c r="BW15" s="37"/>
-      <c r="BX15" s="37"/>
-      <c r="BY15" s="37"/>
-      <c r="BZ15" s="37"/>
-      <c r="CA15" s="37"/>
-      <c r="CB15" s="37"/>
-      <c r="CC15" s="37"/>
-      <c r="CD15" s="37"/>
-      <c r="CE15" s="37"/>
-      <c r="CF15" s="37"/>
-      <c r="CG15" s="37"/>
-      <c r="CH15" s="37"/>
-      <c r="CI15" s="37"/>
-      <c r="CJ15" s="37"/>
-      <c r="CK15" s="37"/>
-      <c r="CL15" s="37"/>
-      <c r="CM15" s="37"/>
-      <c r="CN15" s="37"/>
-      <c r="CO15" s="37"/>
-      <c r="CP15" s="37"/>
-      <c r="CQ15" s="37"/>
-      <c r="CR15" s="37"/>
-      <c r="CS15" s="37"/>
-      <c r="CT15" s="37"/>
-      <c r="CU15" s="37"/>
-      <c r="CV15" s="37"/>
-      <c r="CW15" s="37"/>
-      <c r="CX15" s="37"/>
-      <c r="CY15" s="37"/>
-      <c r="CZ15" s="37"/>
-      <c r="DA15" s="37"/>
-      <c r="DB15" s="37"/>
-      <c r="DC15" s="37"/>
-      <c r="DD15" s="37"/>
-      <c r="DE15" s="37"/>
-      <c r="DF15" s="37"/>
-      <c r="DG15" s="37"/>
-      <c r="DH15" s="37"/>
-      <c r="DI15" s="37"/>
-      <c r="DJ15" s="37"/>
-      <c r="DK15" s="37"/>
-      <c r="DL15" s="37"/>
-      <c r="DM15" s="37"/>
-      <c r="DN15" s="37"/>
-      <c r="DO15" s="37"/>
-      <c r="DP15" s="37"/>
-      <c r="DQ15" s="37"/>
-      <c r="DR15" s="37"/>
-      <c r="DS15" s="37"/>
-      <c r="DT15" s="37"/>
-      <c r="DU15" s="37"/>
-      <c r="DV15" s="37"/>
-      <c r="DW15" s="37"/>
-      <c r="DX15" s="37"/>
-      <c r="DY15" s="37"/>
-      <c r="DZ15" s="37"/>
-      <c r="EA15" s="37"/>
-      <c r="EB15" s="37"/>
-      <c r="EC15" s="37"/>
-      <c r="ED15" s="37"/>
-      <c r="EE15" s="37"/>
-      <c r="EF15" s="37"/>
-      <c r="EG15" s="37"/>
-      <c r="EH15" s="37"/>
-      <c r="EI15" s="37"/>
-      <c r="EJ15" s="37"/>
-      <c r="EK15" s="37"/>
-      <c r="EL15" s="37"/>
-      <c r="EM15" s="37"/>
-      <c r="EN15" s="37"/>
-      <c r="EO15" s="37"/>
-      <c r="EP15" s="37"/>
-      <c r="EQ15" s="37"/>
-      <c r="ER15" s="37"/>
-      <c r="ES15" s="37"/>
-      <c r="ET15" s="37"/>
-      <c r="EU15" s="37"/>
+      <c r="N15" s="28"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="28"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="28"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="28"/>
+      <c r="X15" s="28"/>
+      <c r="Y15" s="28"/>
+      <c r="Z15" s="28"/>
+      <c r="AA15" s="28"/>
+      <c r="AB15" s="28"/>
+      <c r="AC15" s="28"/>
+      <c r="AD15" s="28"/>
+      <c r="AE15" s="28"/>
+      <c r="AF15" s="28"/>
+      <c r="AG15" s="28"/>
+      <c r="AH15" s="28"/>
+      <c r="AI15" s="28"/>
+      <c r="AJ15" s="28"/>
+      <c r="AK15" s="28"/>
+      <c r="AL15" s="28"/>
+      <c r="AM15" s="28"/>
+      <c r="AN15" s="28"/>
+      <c r="AO15" s="28"/>
+      <c r="AP15" s="28"/>
+      <c r="AQ15" s="28"/>
+      <c r="AR15" s="28"/>
+      <c r="AS15" s="28"/>
+      <c r="AT15" s="28"/>
+      <c r="AU15" s="28"/>
+      <c r="AV15" s="28"/>
+      <c r="AW15" s="28"/>
+      <c r="AX15" s="28"/>
+      <c r="AY15" s="28"/>
+      <c r="AZ15" s="28"/>
+      <c r="BA15" s="28"/>
+      <c r="BB15" s="28"/>
+      <c r="BC15" s="28"/>
+      <c r="BD15" s="28"/>
+      <c r="BE15" s="28"/>
+      <c r="BF15" s="28"/>
+      <c r="BG15" s="28"/>
+      <c r="BH15" s="28"/>
+      <c r="BI15" s="28"/>
+      <c r="BJ15" s="28"/>
+      <c r="BK15" s="28"/>
+      <c r="BL15" s="28"/>
+      <c r="BM15" s="28"/>
+      <c r="BN15" s="28"/>
+      <c r="BO15" s="28"/>
+      <c r="BP15" s="28"/>
+      <c r="BQ15" s="28"/>
+      <c r="BR15" s="28"/>
+      <c r="BS15" s="28"/>
+      <c r="BT15" s="28"/>
+      <c r="BU15" s="28"/>
+      <c r="BV15" s="28"/>
+      <c r="BW15" s="28"/>
+      <c r="BX15" s="28"/>
+      <c r="BY15" s="28"/>
+      <c r="BZ15" s="28"/>
+      <c r="CA15" s="28"/>
+      <c r="CB15" s="28"/>
+      <c r="CC15" s="28"/>
+      <c r="CD15" s="28"/>
+      <c r="CE15" s="28"/>
+      <c r="CF15" s="28"/>
+      <c r="CG15" s="28"/>
+      <c r="CH15" s="28"/>
+      <c r="CI15" s="28"/>
+      <c r="CJ15" s="28"/>
+      <c r="CK15" s="28"/>
+      <c r="CL15" s="28"/>
+      <c r="CM15" s="28"/>
+      <c r="CN15" s="28"/>
+      <c r="CO15" s="28"/>
+      <c r="CP15" s="28"/>
+      <c r="CQ15" s="28"/>
+      <c r="CR15" s="28"/>
+      <c r="CS15" s="28"/>
+      <c r="CT15" s="28"/>
+      <c r="CU15" s="28"/>
+      <c r="CV15" s="28"/>
+      <c r="CW15" s="28"/>
+      <c r="CX15" s="28"/>
+      <c r="CY15" s="28"/>
+      <c r="CZ15" s="28"/>
+      <c r="DA15" s="28"/>
+      <c r="DB15" s="28"/>
+      <c r="DC15" s="28"/>
+      <c r="DD15" s="28"/>
+      <c r="DE15" s="28"/>
+      <c r="DF15" s="28"/>
+      <c r="DG15" s="28"/>
+      <c r="DH15" s="28"/>
+      <c r="DI15" s="28"/>
+      <c r="DJ15" s="28"/>
+      <c r="DK15" s="28"/>
+      <c r="DL15" s="28"/>
+      <c r="DM15" s="28"/>
+      <c r="DN15" s="28"/>
+      <c r="DO15" s="28"/>
+      <c r="DP15" s="28"/>
+      <c r="DQ15" s="28"/>
+      <c r="DR15" s="28"/>
+      <c r="DS15" s="28"/>
+      <c r="DT15" s="28"/>
+      <c r="DU15" s="28"/>
+      <c r="DV15" s="28"/>
+      <c r="DW15" s="28"/>
+      <c r="DX15" s="28"/>
+      <c r="DY15" s="28"/>
+      <c r="DZ15" s="28"/>
+      <c r="EA15" s="28"/>
+      <c r="EB15" s="28"/>
+      <c r="EC15" s="28"/>
+      <c r="ED15" s="28"/>
+      <c r="EE15" s="28"/>
+      <c r="EF15" s="28"/>
+      <c r="EG15" s="28"/>
+      <c r="EH15" s="28"/>
+      <c r="EI15" s="28"/>
+      <c r="EJ15" s="28"/>
+      <c r="EK15" s="28"/>
+      <c r="EL15" s="28"/>
+      <c r="EM15" s="28"/>
+      <c r="EN15" s="28"/>
+      <c r="EO15" s="28"/>
+      <c r="EP15" s="28"/>
+      <c r="EQ15" s="28"/>
+      <c r="ER15" s="28"/>
+      <c r="ES15" s="28"/>
+      <c r="ET15" s="28"/>
+      <c r="EU15" s="28"/>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="B16" s="42">
+      <c r="B16" s="32">
         <v>190.0</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="32">
         <v>240.0</v>
       </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="42">
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="32">
         <v>318.0</v>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
-      <c r="S16" s="37"/>
-      <c r="T16" s="37"/>
-      <c r="U16" s="37"/>
-      <c r="V16" s="37"/>
-      <c r="W16" s="37"/>
-      <c r="X16" s="37"/>
-      <c r="Y16" s="37"/>
-      <c r="Z16" s="37"/>
-      <c r="AA16" s="37"/>
-      <c r="AB16" s="37"/>
-      <c r="AC16" s="37"/>
-      <c r="AD16" s="37"/>
-      <c r="AE16" s="37"/>
-      <c r="AF16" s="37"/>
-      <c r="AG16" s="37"/>
-      <c r="AH16" s="37"/>
-      <c r="AI16" s="37"/>
-      <c r="AJ16" s="37"/>
-      <c r="AK16" s="37"/>
-      <c r="AL16" s="37"/>
-      <c r="AM16" s="37"/>
-      <c r="AN16" s="37"/>
-      <c r="AO16" s="37"/>
-      <c r="AP16" s="37"/>
-      <c r="AQ16" s="37"/>
-      <c r="AR16" s="37"/>
-      <c r="AS16" s="37"/>
-      <c r="AT16" s="37"/>
-      <c r="AU16" s="37"/>
-      <c r="AV16" s="37"/>
-      <c r="AW16" s="37"/>
-      <c r="AX16" s="37"/>
-      <c r="AY16" s="37"/>
-      <c r="AZ16" s="37"/>
-      <c r="BA16" s="37"/>
-      <c r="BB16" s="37"/>
-      <c r="BC16" s="37"/>
-      <c r="BD16" s="37"/>
-      <c r="BE16" s="37"/>
-      <c r="BF16" s="37"/>
-      <c r="BG16" s="37"/>
-      <c r="BH16" s="37"/>
-      <c r="BI16" s="37"/>
-      <c r="BJ16" s="37"/>
-      <c r="BK16" s="37"/>
-      <c r="BL16" s="37"/>
-      <c r="BM16" s="37"/>
-      <c r="BN16" s="37"/>
-      <c r="BO16" s="37"/>
-      <c r="BP16" s="37"/>
-      <c r="BQ16" s="37"/>
-      <c r="BR16" s="37"/>
-      <c r="BS16" s="37"/>
-      <c r="BT16" s="37"/>
-      <c r="BU16" s="37"/>
-      <c r="BV16" s="37"/>
-      <c r="BW16" s="37"/>
-      <c r="BX16" s="37"/>
-      <c r="BY16" s="37"/>
-      <c r="BZ16" s="37"/>
-      <c r="CA16" s="37"/>
-      <c r="CB16" s="37"/>
-      <c r="CC16" s="37"/>
-      <c r="CD16" s="37"/>
-      <c r="CE16" s="37"/>
-      <c r="CF16" s="37"/>
-      <c r="CG16" s="37"/>
-      <c r="CH16" s="37"/>
-      <c r="CI16" s="37"/>
-      <c r="CJ16" s="37"/>
-      <c r="CK16" s="37"/>
-      <c r="CL16" s="37"/>
-      <c r="CM16" s="37"/>
-      <c r="CN16" s="37"/>
-      <c r="CO16" s="37"/>
-      <c r="CP16" s="37"/>
-      <c r="CQ16" s="37"/>
-      <c r="CR16" s="37"/>
-      <c r="CS16" s="37"/>
-      <c r="CT16" s="37"/>
-      <c r="CU16" s="37"/>
-      <c r="CV16" s="37"/>
-      <c r="CW16" s="37"/>
-      <c r="CX16" s="37"/>
-      <c r="CY16" s="37"/>
-      <c r="CZ16" s="37"/>
-      <c r="DA16" s="37"/>
-      <c r="DB16" s="37"/>
-      <c r="DC16" s="37"/>
-      <c r="DD16" s="37"/>
-      <c r="DE16" s="37"/>
-      <c r="DF16" s="37"/>
-      <c r="DG16" s="37"/>
-      <c r="DH16" s="37"/>
-      <c r="DI16" s="37"/>
-      <c r="DJ16" s="37"/>
-      <c r="DK16" s="37"/>
-      <c r="DL16" s="37"/>
-      <c r="DM16" s="37"/>
-      <c r="DN16" s="37"/>
-      <c r="DO16" s="37"/>
-      <c r="DP16" s="37"/>
-      <c r="DQ16" s="37"/>
-      <c r="DR16" s="37"/>
-      <c r="DS16" s="37"/>
-      <c r="DT16" s="37"/>
-      <c r="DU16" s="37"/>
-      <c r="DV16" s="37"/>
-      <c r="DW16" s="37"/>
-      <c r="DX16" s="37"/>
-      <c r="DY16" s="37"/>
-      <c r="DZ16" s="37"/>
-      <c r="EA16" s="37"/>
-      <c r="EB16" s="37"/>
-      <c r="EC16" s="37"/>
-      <c r="ED16" s="37"/>
-      <c r="EE16" s="37"/>
-      <c r="EF16" s="37"/>
-      <c r="EG16" s="37"/>
-      <c r="EH16" s="37"/>
-      <c r="EI16" s="37"/>
-      <c r="EJ16" s="37"/>
-      <c r="EK16" s="37"/>
-      <c r="EL16" s="37"/>
-      <c r="EM16" s="37"/>
-      <c r="EN16" s="37"/>
-      <c r="EO16" s="37"/>
-      <c r="EP16" s="37"/>
-      <c r="EQ16" s="37"/>
-      <c r="ER16" s="37"/>
-      <c r="ES16" s="37"/>
-      <c r="ET16" s="37"/>
-      <c r="EU16" s="37"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
+      <c r="O16" s="28"/>
+      <c r="P16" s="28"/>
+      <c r="Q16" s="28"/>
+      <c r="R16" s="28"/>
+      <c r="S16" s="28"/>
+      <c r="T16" s="28"/>
+      <c r="U16" s="28"/>
+      <c r="V16" s="28"/>
+      <c r="W16" s="28"/>
+      <c r="X16" s="28"/>
+      <c r="Y16" s="28"/>
+      <c r="Z16" s="28"/>
+      <c r="AA16" s="28"/>
+      <c r="AB16" s="28"/>
+      <c r="AC16" s="28"/>
+      <c r="AD16" s="28"/>
+      <c r="AE16" s="28"/>
+      <c r="AF16" s="28"/>
+      <c r="AG16" s="28"/>
+      <c r="AH16" s="28"/>
+      <c r="AI16" s="28"/>
+      <c r="AJ16" s="28"/>
+      <c r="AK16" s="28"/>
+      <c r="AL16" s="28"/>
+      <c r="AM16" s="28"/>
+      <c r="AN16" s="28"/>
+      <c r="AO16" s="28"/>
+      <c r="AP16" s="28"/>
+      <c r="AQ16" s="28"/>
+      <c r="AR16" s="28"/>
+      <c r="AS16" s="28"/>
+      <c r="AT16" s="28"/>
+      <c r="AU16" s="28"/>
+      <c r="AV16" s="28"/>
+      <c r="AW16" s="28"/>
+      <c r="AX16" s="28"/>
+      <c r="AY16" s="28"/>
+      <c r="AZ16" s="28"/>
+      <c r="BA16" s="28"/>
+      <c r="BB16" s="28"/>
+      <c r="BC16" s="28"/>
+      <c r="BD16" s="28"/>
+      <c r="BE16" s="28"/>
+      <c r="BF16" s="28"/>
+      <c r="BG16" s="28"/>
+      <c r="BH16" s="28"/>
+      <c r="BI16" s="28"/>
+      <c r="BJ16" s="28"/>
+      <c r="BK16" s="28"/>
+      <c r="BL16" s="28"/>
+      <c r="BM16" s="28"/>
+      <c r="BN16" s="28"/>
+      <c r="BO16" s="28"/>
+      <c r="BP16" s="28"/>
+      <c r="BQ16" s="28"/>
+      <c r="BR16" s="28"/>
+      <c r="BS16" s="28"/>
+      <c r="BT16" s="28"/>
+      <c r="BU16" s="28"/>
+      <c r="BV16" s="28"/>
+      <c r="BW16" s="28"/>
+      <c r="BX16" s="28"/>
+      <c r="BY16" s="28"/>
+      <c r="BZ16" s="28"/>
+      <c r="CA16" s="28"/>
+      <c r="CB16" s="28"/>
+      <c r="CC16" s="28"/>
+      <c r="CD16" s="28"/>
+      <c r="CE16" s="28"/>
+      <c r="CF16" s="28"/>
+      <c r="CG16" s="28"/>
+      <c r="CH16" s="28"/>
+      <c r="CI16" s="28"/>
+      <c r="CJ16" s="28"/>
+      <c r="CK16" s="28"/>
+      <c r="CL16" s="28"/>
+      <c r="CM16" s="28"/>
+      <c r="CN16" s="28"/>
+      <c r="CO16" s="28"/>
+      <c r="CP16" s="28"/>
+      <c r="CQ16" s="28"/>
+      <c r="CR16" s="28"/>
+      <c r="CS16" s="28"/>
+      <c r="CT16" s="28"/>
+      <c r="CU16" s="28"/>
+      <c r="CV16" s="28"/>
+      <c r="CW16" s="28"/>
+      <c r="CX16" s="28"/>
+      <c r="CY16" s="28"/>
+      <c r="CZ16" s="28"/>
+      <c r="DA16" s="28"/>
+      <c r="DB16" s="28"/>
+      <c r="DC16" s="28"/>
+      <c r="DD16" s="28"/>
+      <c r="DE16" s="28"/>
+      <c r="DF16" s="28"/>
+      <c r="DG16" s="28"/>
+      <c r="DH16" s="28"/>
+      <c r="DI16" s="28"/>
+      <c r="DJ16" s="28"/>
+      <c r="DK16" s="28"/>
+      <c r="DL16" s="28"/>
+      <c r="DM16" s="28"/>
+      <c r="DN16" s="28"/>
+      <c r="DO16" s="28"/>
+      <c r="DP16" s="28"/>
+      <c r="DQ16" s="28"/>
+      <c r="DR16" s="28"/>
+      <c r="DS16" s="28"/>
+      <c r="DT16" s="28"/>
+      <c r="DU16" s="28"/>
+      <c r="DV16" s="28"/>
+      <c r="DW16" s="28"/>
+      <c r="DX16" s="28"/>
+      <c r="DY16" s="28"/>
+      <c r="DZ16" s="28"/>
+      <c r="EA16" s="28"/>
+      <c r="EB16" s="28"/>
+      <c r="EC16" s="28"/>
+      <c r="ED16" s="28"/>
+      <c r="EE16" s="28"/>
+      <c r="EF16" s="28"/>
+      <c r="EG16" s="28"/>
+      <c r="EH16" s="28"/>
+      <c r="EI16" s="28"/>
+      <c r="EJ16" s="28"/>
+      <c r="EK16" s="28"/>
+      <c r="EL16" s="28"/>
+      <c r="EM16" s="28"/>
+      <c r="EN16" s="28"/>
+      <c r="EO16" s="28"/>
+      <c r="EP16" s="28"/>
+      <c r="EQ16" s="28"/>
+      <c r="ER16" s="28"/>
+      <c r="ES16" s="28"/>
+      <c r="ET16" s="28"/>
+      <c r="EU16" s="28"/>
     </row>
     <row r="17">
-      <c r="A17" s="39"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="37"/>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
-      <c r="S17" s="37"/>
-      <c r="T17" s="37"/>
-      <c r="U17" s="37"/>
-      <c r="V17" s="37"/>
-      <c r="W17" s="37"/>
-      <c r="X17" s="37"/>
-      <c r="Y17" s="37"/>
-      <c r="Z17" s="37"/>
-      <c r="AA17" s="37"/>
-      <c r="AB17" s="37"/>
-      <c r="AC17" s="37"/>
-      <c r="AD17" s="37"/>
-      <c r="AE17" s="37"/>
-      <c r="AF17" s="37"/>
-      <c r="AG17" s="37"/>
-      <c r="AH17" s="37"/>
-      <c r="AI17" s="37"/>
-      <c r="AJ17" s="37"/>
-      <c r="AK17" s="37"/>
-      <c r="AL17" s="37"/>
-      <c r="AM17" s="37"/>
-      <c r="AN17" s="37"/>
-      <c r="AO17" s="37"/>
-      <c r="AP17" s="37"/>
-      <c r="AQ17" s="37"/>
-      <c r="AR17" s="37"/>
-      <c r="AS17" s="37"/>
-      <c r="AT17" s="37"/>
-      <c r="AU17" s="37"/>
-      <c r="AV17" s="37"/>
-      <c r="AW17" s="37"/>
-      <c r="AX17" s="37"/>
-      <c r="AY17" s="37"/>
-      <c r="AZ17" s="37"/>
-      <c r="BA17" s="37"/>
-      <c r="BB17" s="37"/>
-      <c r="BC17" s="37"/>
-      <c r="BD17" s="37"/>
-      <c r="BE17" s="37"/>
-      <c r="BF17" s="37"/>
-      <c r="BG17" s="37"/>
-      <c r="BH17" s="37"/>
-      <c r="BI17" s="37"/>
-      <c r="BJ17" s="37"/>
-      <c r="BK17" s="37"/>
-      <c r="BL17" s="37"/>
-      <c r="BM17" s="37"/>
-      <c r="BN17" s="37"/>
-      <c r="BO17" s="37"/>
-      <c r="BP17" s="37"/>
-      <c r="BQ17" s="37"/>
-      <c r="BR17" s="37"/>
-      <c r="BS17" s="37"/>
-      <c r="BT17" s="37"/>
-      <c r="BU17" s="37"/>
-      <c r="BV17" s="37"/>
-      <c r="BW17" s="37"/>
-      <c r="BX17" s="37"/>
-      <c r="BY17" s="37"/>
-      <c r="BZ17" s="37"/>
-      <c r="CA17" s="37"/>
-      <c r="CB17" s="37"/>
-      <c r="CC17" s="37"/>
-      <c r="CD17" s="37"/>
-      <c r="CE17" s="37"/>
-      <c r="CF17" s="37"/>
-      <c r="CG17" s="37"/>
-      <c r="CH17" s="37"/>
-      <c r="CI17" s="37"/>
-      <c r="CJ17" s="37"/>
-      <c r="CK17" s="37"/>
-      <c r="CL17" s="37"/>
-      <c r="CM17" s="37"/>
-      <c r="CN17" s="37"/>
-      <c r="CO17" s="37"/>
-      <c r="CP17" s="37"/>
-      <c r="CQ17" s="37"/>
-      <c r="CR17" s="37"/>
-      <c r="CS17" s="37"/>
-      <c r="CT17" s="37"/>
-      <c r="CU17" s="37"/>
-      <c r="CV17" s="37"/>
-      <c r="CW17" s="37"/>
-      <c r="CX17" s="37"/>
-      <c r="CY17" s="37"/>
-      <c r="CZ17" s="37"/>
-      <c r="DA17" s="37"/>
-      <c r="DB17" s="37"/>
-      <c r="DC17" s="37"/>
-      <c r="DD17" s="37"/>
-      <c r="DE17" s="37"/>
-      <c r="DF17" s="37"/>
-      <c r="DG17" s="37"/>
-      <c r="DH17" s="37"/>
-      <c r="DI17" s="37"/>
-      <c r="DJ17" s="37"/>
-      <c r="DK17" s="37"/>
-      <c r="DL17" s="37"/>
-      <c r="DM17" s="37"/>
-      <c r="DN17" s="37"/>
-      <c r="DO17" s="37"/>
-      <c r="DP17" s="37"/>
-      <c r="DQ17" s="37"/>
-      <c r="DR17" s="37"/>
-      <c r="DS17" s="37"/>
-      <c r="DT17" s="37"/>
-      <c r="DU17" s="37"/>
-      <c r="DV17" s="37"/>
-      <c r="DW17" s="37"/>
-      <c r="DX17" s="37"/>
-      <c r="DY17" s="37"/>
-      <c r="DZ17" s="37"/>
-      <c r="EA17" s="37"/>
-      <c r="EB17" s="37"/>
-      <c r="EC17" s="37"/>
-      <c r="ED17" s="37"/>
-      <c r="EE17" s="37"/>
-      <c r="EF17" s="37"/>
-      <c r="EG17" s="37"/>
-      <c r="EH17" s="37"/>
-      <c r="EI17" s="37"/>
-      <c r="EJ17" s="37"/>
-      <c r="EK17" s="37"/>
-      <c r="EL17" s="37"/>
-      <c r="EM17" s="37"/>
-      <c r="EN17" s="37"/>
-      <c r="EO17" s="37"/>
-      <c r="EP17" s="37"/>
-      <c r="EQ17" s="37"/>
-      <c r="ER17" s="37"/>
-      <c r="ES17" s="37"/>
-      <c r="ET17" s="37"/>
-      <c r="EU17" s="37"/>
+      <c r="A17" s="33"/>
+      <c r="B17" s="33"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
+      <c r="O17" s="28"/>
+      <c r="P17" s="28"/>
+      <c r="Q17" s="28"/>
+      <c r="R17" s="28"/>
+      <c r="S17" s="28"/>
+      <c r="T17" s="28"/>
+      <c r="U17" s="28"/>
+      <c r="V17" s="28"/>
+      <c r="W17" s="28"/>
+      <c r="X17" s="28"/>
+      <c r="Y17" s="28"/>
+      <c r="Z17" s="28"/>
+      <c r="AA17" s="28"/>
+      <c r="AB17" s="28"/>
+      <c r="AC17" s="28"/>
+      <c r="AD17" s="28"/>
+      <c r="AE17" s="28"/>
+      <c r="AF17" s="28"/>
+      <c r="AG17" s="28"/>
+      <c r="AH17" s="28"/>
+      <c r="AI17" s="28"/>
+      <c r="AJ17" s="28"/>
+      <c r="AK17" s="28"/>
+      <c r="AL17" s="28"/>
+      <c r="AM17" s="28"/>
+      <c r="AN17" s="28"/>
+      <c r="AO17" s="28"/>
+      <c r="AP17" s="28"/>
+      <c r="AQ17" s="28"/>
+      <c r="AR17" s="28"/>
+      <c r="AS17" s="28"/>
+      <c r="AT17" s="28"/>
+      <c r="AU17" s="28"/>
+      <c r="AV17" s="28"/>
+      <c r="AW17" s="28"/>
+      <c r="AX17" s="28"/>
+      <c r="AY17" s="28"/>
+      <c r="AZ17" s="28"/>
+      <c r="BA17" s="28"/>
+      <c r="BB17" s="28"/>
+      <c r="BC17" s="28"/>
+      <c r="BD17" s="28"/>
+      <c r="BE17" s="28"/>
+      <c r="BF17" s="28"/>
+      <c r="BG17" s="28"/>
+      <c r="BH17" s="28"/>
+      <c r="BI17" s="28"/>
+      <c r="BJ17" s="28"/>
+      <c r="BK17" s="28"/>
+      <c r="BL17" s="28"/>
+      <c r="BM17" s="28"/>
+      <c r="BN17" s="28"/>
+      <c r="BO17" s="28"/>
+      <c r="BP17" s="28"/>
+      <c r="BQ17" s="28"/>
+      <c r="BR17" s="28"/>
+      <c r="BS17" s="28"/>
+      <c r="BT17" s="28"/>
+      <c r="BU17" s="28"/>
+      <c r="BV17" s="28"/>
+      <c r="BW17" s="28"/>
+      <c r="BX17" s="28"/>
+      <c r="BY17" s="28"/>
+      <c r="BZ17" s="28"/>
+      <c r="CA17" s="28"/>
+      <c r="CB17" s="28"/>
+      <c r="CC17" s="28"/>
+      <c r="CD17" s="28"/>
+      <c r="CE17" s="28"/>
+      <c r="CF17" s="28"/>
+      <c r="CG17" s="28"/>
+      <c r="CH17" s="28"/>
+      <c r="CI17" s="28"/>
+      <c r="CJ17" s="28"/>
+      <c r="CK17" s="28"/>
+      <c r="CL17" s="28"/>
+      <c r="CM17" s="28"/>
+      <c r="CN17" s="28"/>
+      <c r="CO17" s="28"/>
+      <c r="CP17" s="28"/>
+      <c r="CQ17" s="28"/>
+      <c r="CR17" s="28"/>
+      <c r="CS17" s="28"/>
+      <c r="CT17" s="28"/>
+      <c r="CU17" s="28"/>
+      <c r="CV17" s="28"/>
+      <c r="CW17" s="28"/>
+      <c r="CX17" s="28"/>
+      <c r="CY17" s="28"/>
+      <c r="CZ17" s="28"/>
+      <c r="DA17" s="28"/>
+      <c r="DB17" s="28"/>
+      <c r="DC17" s="28"/>
+      <c r="DD17" s="28"/>
+      <c r="DE17" s="28"/>
+      <c r="DF17" s="28"/>
+      <c r="DG17" s="28"/>
+      <c r="DH17" s="28"/>
+      <c r="DI17" s="28"/>
+      <c r="DJ17" s="28"/>
+      <c r="DK17" s="28"/>
+      <c r="DL17" s="28"/>
+      <c r="DM17" s="28"/>
+      <c r="DN17" s="28"/>
+      <c r="DO17" s="28"/>
+      <c r="DP17" s="28"/>
+      <c r="DQ17" s="28"/>
+      <c r="DR17" s="28"/>
+      <c r="DS17" s="28"/>
+      <c r="DT17" s="28"/>
+      <c r="DU17" s="28"/>
+      <c r="DV17" s="28"/>
+      <c r="DW17" s="28"/>
+      <c r="DX17" s="28"/>
+      <c r="DY17" s="28"/>
+      <c r="DZ17" s="28"/>
+      <c r="EA17" s="28"/>
+      <c r="EB17" s="28"/>
+      <c r="EC17" s="28"/>
+      <c r="ED17" s="28"/>
+      <c r="EE17" s="28"/>
+      <c r="EF17" s="28"/>
+      <c r="EG17" s="28"/>
+      <c r="EH17" s="28"/>
+      <c r="EI17" s="28"/>
+      <c r="EJ17" s="28"/>
+      <c r="EK17" s="28"/>
+      <c r="EL17" s="28"/>
+      <c r="EM17" s="28"/>
+      <c r="EN17" s="28"/>
+      <c r="EO17" s="28"/>
+      <c r="EP17" s="28"/>
+      <c r="EQ17" s="28"/>
+      <c r="ER17" s="28"/>
+      <c r="ES17" s="28"/>
+      <c r="ET17" s="28"/>
+      <c r="EU17" s="28"/>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="29" t="s">
         <v>303</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
-      <c r="S18" s="37"/>
-      <c r="T18" s="37"/>
-      <c r="U18" s="37"/>
-      <c r="V18" s="37"/>
-      <c r="W18" s="37"/>
-      <c r="X18" s="37"/>
-      <c r="Y18" s="37"/>
-      <c r="Z18" s="37"/>
-      <c r="AA18" s="37"/>
-      <c r="AB18" s="37"/>
-      <c r="AC18" s="37"/>
-      <c r="AD18" s="37"/>
-      <c r="AE18" s="37"/>
-      <c r="AF18" s="37"/>
-      <c r="AG18" s="37"/>
-      <c r="AH18" s="37"/>
-      <c r="AI18" s="37"/>
-      <c r="AJ18" s="37"/>
-      <c r="AK18" s="37"/>
-      <c r="AL18" s="37"/>
-      <c r="AM18" s="37"/>
-      <c r="AN18" s="37"/>
-      <c r="AO18" s="37"/>
-      <c r="AP18" s="37"/>
-      <c r="AQ18" s="37"/>
-      <c r="AR18" s="37"/>
-      <c r="AS18" s="37"/>
-      <c r="AT18" s="37"/>
-      <c r="AU18" s="37"/>
-      <c r="AV18" s="37"/>
-      <c r="AW18" s="37"/>
-      <c r="AX18" s="37"/>
-      <c r="AY18" s="37"/>
-      <c r="AZ18" s="37"/>
-      <c r="BA18" s="37"/>
-      <c r="BB18" s="37"/>
-      <c r="BC18" s="37"/>
-      <c r="BD18" s="37"/>
-      <c r="BE18" s="37"/>
-      <c r="BF18" s="37"/>
-      <c r="BG18" s="37"/>
-      <c r="BH18" s="37"/>
-      <c r="BI18" s="37"/>
-      <c r="BJ18" s="37"/>
-      <c r="BK18" s="37"/>
-      <c r="BL18" s="37"/>
-      <c r="BM18" s="37"/>
-      <c r="BN18" s="37"/>
-      <c r="BO18" s="37"/>
-      <c r="BP18" s="37"/>
-      <c r="BQ18" s="37"/>
-      <c r="BR18" s="37"/>
-      <c r="BS18" s="37"/>
-      <c r="BT18" s="37"/>
-      <c r="BU18" s="37"/>
-      <c r="BV18" s="37"/>
-      <c r="BW18" s="37"/>
-      <c r="BX18" s="37"/>
-      <c r="BY18" s="37"/>
-      <c r="BZ18" s="37"/>
-      <c r="CA18" s="37"/>
-      <c r="CB18" s="37"/>
-      <c r="CC18" s="37"/>
-      <c r="CD18" s="37"/>
-      <c r="CE18" s="37"/>
-      <c r="CF18" s="37"/>
-      <c r="CG18" s="37"/>
-      <c r="CH18" s="37"/>
-      <c r="CI18" s="37"/>
-      <c r="CJ18" s="37"/>
-      <c r="CK18" s="37"/>
-      <c r="CL18" s="37"/>
-      <c r="CM18" s="37"/>
-      <c r="CN18" s="37"/>
-      <c r="CO18" s="37"/>
-      <c r="CP18" s="37"/>
-      <c r="CQ18" s="37"/>
-      <c r="CR18" s="37"/>
-      <c r="CS18" s="37"/>
-      <c r="CT18" s="37"/>
-      <c r="CU18" s="37"/>
-      <c r="CV18" s="37"/>
-      <c r="CW18" s="37"/>
-      <c r="CX18" s="37"/>
-      <c r="CY18" s="37"/>
-      <c r="CZ18" s="37"/>
-      <c r="DA18" s="37"/>
-      <c r="DB18" s="37"/>
-      <c r="DC18" s="37"/>
-      <c r="DD18" s="37"/>
-      <c r="DE18" s="37"/>
-      <c r="DF18" s="37"/>
-      <c r="DG18" s="37"/>
-      <c r="DH18" s="37"/>
-      <c r="DI18" s="37"/>
-      <c r="DJ18" s="37"/>
-      <c r="DK18" s="37"/>
-      <c r="DL18" s="37"/>
-      <c r="DM18" s="37"/>
-      <c r="DN18" s="37"/>
-      <c r="DO18" s="37"/>
-      <c r="DP18" s="37"/>
-      <c r="DQ18" s="37"/>
-      <c r="DR18" s="37"/>
-      <c r="DS18" s="37"/>
-      <c r="DT18" s="37"/>
-      <c r="DU18" s="37"/>
-      <c r="DV18" s="37"/>
-      <c r="DW18" s="37"/>
-      <c r="DX18" s="37"/>
-      <c r="DY18" s="37"/>
-      <c r="DZ18" s="37"/>
-      <c r="EA18" s="37"/>
-      <c r="EB18" s="37"/>
-      <c r="EC18" s="37"/>
-      <c r="ED18" s="37"/>
-      <c r="EE18" s="37"/>
-      <c r="EF18" s="37"/>
-      <c r="EG18" s="37"/>
-      <c r="EH18" s="37"/>
-      <c r="EI18" s="37"/>
-      <c r="EJ18" s="37"/>
-      <c r="EK18" s="37"/>
-      <c r="EL18" s="37"/>
-      <c r="EM18" s="37"/>
-      <c r="EN18" s="37"/>
-      <c r="EO18" s="37"/>
-      <c r="EP18" s="37"/>
-      <c r="EQ18" s="37"/>
-      <c r="ER18" s="37"/>
-      <c r="ES18" s="37"/>
-      <c r="ET18" s="37"/>
-      <c r="EU18" s="37"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
+      <c r="O18" s="28"/>
+      <c r="P18" s="28"/>
+      <c r="Q18" s="28"/>
+      <c r="R18" s="28"/>
+      <c r="S18" s="28"/>
+      <c r="T18" s="28"/>
+      <c r="U18" s="28"/>
+      <c r="V18" s="28"/>
+      <c r="W18" s="28"/>
+      <c r="X18" s="28"/>
+      <c r="Y18" s="28"/>
+      <c r="Z18" s="28"/>
+      <c r="AA18" s="28"/>
+      <c r="AB18" s="28"/>
+      <c r="AC18" s="28"/>
+      <c r="AD18" s="28"/>
+      <c r="AE18" s="28"/>
+      <c r="AF18" s="28"/>
+      <c r="AG18" s="28"/>
+      <c r="AH18" s="28"/>
+      <c r="AI18" s="28"/>
+      <c r="AJ18" s="28"/>
+      <c r="AK18" s="28"/>
+      <c r="AL18" s="28"/>
+      <c r="AM18" s="28"/>
+      <c r="AN18" s="28"/>
+      <c r="AO18" s="28"/>
+      <c r="AP18" s="28"/>
+      <c r="AQ18" s="28"/>
+      <c r="AR18" s="28"/>
+      <c r="AS18" s="28"/>
+      <c r="AT18" s="28"/>
+      <c r="AU18" s="28"/>
+      <c r="AV18" s="28"/>
+      <c r="AW18" s="28"/>
+      <c r="AX18" s="28"/>
+      <c r="AY18" s="28"/>
+      <c r="AZ18" s="28"/>
+      <c r="BA18" s="28"/>
+      <c r="BB18" s="28"/>
+      <c r="BC18" s="28"/>
+      <c r="BD18" s="28"/>
+      <c r="BE18" s="28"/>
+      <c r="BF18" s="28"/>
+      <c r="BG18" s="28"/>
+      <c r="BH18" s="28"/>
+      <c r="BI18" s="28"/>
+      <c r="BJ18" s="28"/>
+      <c r="BK18" s="28"/>
+      <c r="BL18" s="28"/>
+      <c r="BM18" s="28"/>
+      <c r="BN18" s="28"/>
+      <c r="BO18" s="28"/>
+      <c r="BP18" s="28"/>
+      <c r="BQ18" s="28"/>
+      <c r="BR18" s="28"/>
+      <c r="BS18" s="28"/>
+      <c r="BT18" s="28"/>
+      <c r="BU18" s="28"/>
+      <c r="BV18" s="28"/>
+      <c r="BW18" s="28"/>
+      <c r="BX18" s="28"/>
+      <c r="BY18" s="28"/>
+      <c r="BZ18" s="28"/>
+      <c r="CA18" s="28"/>
+      <c r="CB18" s="28"/>
+      <c r="CC18" s="28"/>
+      <c r="CD18" s="28"/>
+      <c r="CE18" s="28"/>
+      <c r="CF18" s="28"/>
+      <c r="CG18" s="28"/>
+      <c r="CH18" s="28"/>
+      <c r="CI18" s="28"/>
+      <c r="CJ18" s="28"/>
+      <c r="CK18" s="28"/>
+      <c r="CL18" s="28"/>
+      <c r="CM18" s="28"/>
+      <c r="CN18" s="28"/>
+      <c r="CO18" s="28"/>
+      <c r="CP18" s="28"/>
+      <c r="CQ18" s="28"/>
+      <c r="CR18" s="28"/>
+      <c r="CS18" s="28"/>
+      <c r="CT18" s="28"/>
+      <c r="CU18" s="28"/>
+      <c r="CV18" s="28"/>
+      <c r="CW18" s="28"/>
+      <c r="CX18" s="28"/>
+      <c r="CY18" s="28"/>
+      <c r="CZ18" s="28"/>
+      <c r="DA18" s="28"/>
+      <c r="DB18" s="28"/>
+      <c r="DC18" s="28"/>
+      <c r="DD18" s="28"/>
+      <c r="DE18" s="28"/>
+      <c r="DF18" s="28"/>
+      <c r="DG18" s="28"/>
+      <c r="DH18" s="28"/>
+      <c r="DI18" s="28"/>
+      <c r="DJ18" s="28"/>
+      <c r="DK18" s="28"/>
+      <c r="DL18" s="28"/>
+      <c r="DM18" s="28"/>
+      <c r="DN18" s="28"/>
+      <c r="DO18" s="28"/>
+      <c r="DP18" s="28"/>
+      <c r="DQ18" s="28"/>
+      <c r="DR18" s="28"/>
+      <c r="DS18" s="28"/>
+      <c r="DT18" s="28"/>
+      <c r="DU18" s="28"/>
+      <c r="DV18" s="28"/>
+      <c r="DW18" s="28"/>
+      <c r="DX18" s="28"/>
+      <c r="DY18" s="28"/>
+      <c r="DZ18" s="28"/>
+      <c r="EA18" s="28"/>
+      <c r="EB18" s="28"/>
+      <c r="EC18" s="28"/>
+      <c r="ED18" s="28"/>
+      <c r="EE18" s="28"/>
+      <c r="EF18" s="28"/>
+      <c r="EG18" s="28"/>
+      <c r="EH18" s="28"/>
+      <c r="EI18" s="28"/>
+      <c r="EJ18" s="28"/>
+      <c r="EK18" s="28"/>
+      <c r="EL18" s="28"/>
+      <c r="EM18" s="28"/>
+      <c r="EN18" s="28"/>
+      <c r="EO18" s="28"/>
+      <c r="EP18" s="28"/>
+      <c r="EQ18" s="28"/>
+      <c r="ER18" s="28"/>
+      <c r="ES18" s="28"/>
+      <c r="ET18" s="28"/>
+      <c r="EU18" s="28"/>
     </row>
     <row r="19">
-      <c r="J19" s="43"/>
+      <c r="J19" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6756,573 +6749,573 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="26" t="s">
         <v>304</v>
       </c>
-      <c r="C1" s="36"/>
+      <c r="C1" s="27"/>
       <c r="D1" s="18"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
     </row>
     <row r="2">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
     </row>
     <row r="3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="C3" s="39"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
+      <c r="C3" s="33"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
     </row>
     <row r="4">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
     </row>
     <row r="5">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="J6" s="40" t="s">
+      <c r="J6" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="40" t="s">
+      <c r="K6" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="40" t="s">
+      <c r="L6" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="40" t="s">
+      <c r="M6" s="30" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="B7" s="41">
+      <c r="B7" s="31">
         <v>35.0</v>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="31">
         <v>44.0</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="31">
         <v>40.0</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="31">
         <v>6.0</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="31">
         <v>62.0</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="I7" s="41" t="s">
+      <c r="I7" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="J7" s="41" t="s">
+      <c r="J7" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="K7" s="41" t="s">
+      <c r="K7" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="L7" s="41" t="s">
+      <c r="L7" s="31" t="s">
         <v>306</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="31" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="B8" s="41">
+      <c r="B8" s="31">
         <v>18.0</v>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="31">
         <v>23.0</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="31">
         <v>41.0</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="31">
         <v>5.0</v>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="31">
         <v>30.0</v>
       </c>
-      <c r="H8" s="41" t="s">
+      <c r="H8" s="31" t="s">
         <v>205</v>
       </c>
-      <c r="I8" s="41" t="s">
+      <c r="I8" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="J8" s="41" t="s">
+      <c r="J8" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="K8" s="41" t="s">
+      <c r="K8" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="L8" s="41" t="s">
+      <c r="L8" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="M8" s="41" t="s">
+      <c r="M8" s="31" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="B9" s="41">
+      <c r="B9" s="31">
         <v>10.0</v>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="31">
         <v>13.0</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="31">
         <v>42.0</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="31">
         <v>4.0</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="31">
         <v>14.0</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="H9" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="31" t="s">
         <v>312</v>
       </c>
-      <c r="K9" s="41" t="s">
+      <c r="K9" s="31" t="s">
         <v>313</v>
       </c>
-      <c r="L9" s="41" t="s">
+      <c r="L9" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="M9" s="41" t="s">
+      <c r="M9" s="31" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="41">
+      <c r="B10" s="31">
         <v>8.0</v>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="31">
         <v>10.0</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="31">
         <v>43.0</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="31">
         <v>4.0</v>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="31">
         <v>14.0</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="H10" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I10" s="41" t="s">
+      <c r="I10" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J10" s="41" t="s">
+      <c r="J10" s="31" t="s">
         <v>316</v>
       </c>
-      <c r="K10" s="41" t="s">
+      <c r="K10" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="L10" s="41" t="s">
+      <c r="L10" s="31" t="s">
         <v>318</v>
       </c>
-      <c r="M10" s="41" t="s">
+      <c r="M10" s="31" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="31" t="s">
         <v>191</v>
       </c>
-      <c r="B11" s="41">
+      <c r="B11" s="31">
         <v>7.0</v>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="31">
         <v>9.0</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="D11" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="31">
         <v>44.0</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="31">
         <v>4.0</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="31">
         <v>14.0</v>
       </c>
-      <c r="H11" s="41" t="s">
+      <c r="H11" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I11" s="41" t="s">
+      <c r="I11" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J11" s="41" t="s">
+      <c r="J11" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="K11" s="41" t="s">
+      <c r="K11" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="L11" s="41" t="s">
+      <c r="L11" s="31" t="s">
         <v>322</v>
       </c>
-      <c r="M11" s="41" t="s">
+      <c r="M11" s="31" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="31">
         <v>6.0</v>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="31">
         <v>8.0</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="D12" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="31">
         <v>45.0</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="31">
         <v>4.0</v>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="31">
         <v>14.0</v>
       </c>
-      <c r="H12" s="41" t="s">
+      <c r="H12" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I12" s="41" t="s">
+      <c r="I12" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J12" s="41" t="s">
+      <c r="J12" s="31" t="s">
         <v>324</v>
       </c>
-      <c r="K12" s="41" t="s">
+      <c r="K12" s="31" t="s">
         <v>325</v>
       </c>
-      <c r="L12" s="41" t="s">
+      <c r="L12" s="31" t="s">
         <v>326</v>
       </c>
-      <c r="M12" s="41" t="s">
+      <c r="M12" s="31" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="31" t="s">
         <v>203</v>
       </c>
-      <c r="B13" s="41">
+      <c r="B13" s="31">
         <v>5.0</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="31">
         <v>7.0</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="D13" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="31">
         <v>46.0</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="31">
         <v>4.0</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="31">
         <v>14.0</v>
       </c>
-      <c r="H13" s="41" t="s">
+      <c r="H13" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J13" s="41" t="s">
+      <c r="J13" s="31" t="s">
         <v>328</v>
       </c>
-      <c r="K13" s="41" t="s">
+      <c r="K13" s="31" t="s">
         <v>329</v>
       </c>
-      <c r="L13" s="41" t="s">
+      <c r="L13" s="31" t="s">
         <v>330</v>
       </c>
-      <c r="M13" s="41" t="s">
+      <c r="M13" s="31" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="B14" s="41">
+      <c r="B14" s="31">
         <v>4.0</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="31">
         <v>5.0</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="31">
         <v>99.0</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="31">
         <v>3.0</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="31">
         <v>6.0</v>
       </c>
-      <c r="H14" s="41" t="s">
-        <v>259</v>
-      </c>
-      <c r="I14" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="J14" s="41" t="s">
+      <c r="H14" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="I14" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="J14" s="31" t="s">
         <v>332</v>
       </c>
-      <c r="K14" s="41" t="s">
+      <c r="K14" s="31" t="s">
         <v>333</v>
       </c>
-      <c r="L14" s="41" t="s">
+      <c r="L14" s="31" t="s">
         <v>334</v>
       </c>
-      <c r="M14" s="41" t="s">
+      <c r="M14" s="31" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="B15" s="41">
+      <c r="B15" s="31">
         <v>3.0</v>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="31">
         <v>4.0</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="31">
         <v>47.0</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="31">
         <v>3.0</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="31">
         <v>6.0</v>
       </c>
-      <c r="H15" s="41" t="s">
-        <v>259</v>
-      </c>
-      <c r="I15" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="J15" s="41" t="s">
+      <c r="H15" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="I15" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="J15" s="31" t="s">
         <v>336</v>
       </c>
-      <c r="K15" s="41" t="s">
+      <c r="K15" s="31" t="s">
         <v>337</v>
       </c>
-      <c r="L15" s="41" t="s">
+      <c r="L15" s="31" t="s">
         <v>338</v>
       </c>
-      <c r="M15" s="41" t="s">
+      <c r="M15" s="31" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="B16" s="42">
+      <c r="B16" s="32">
         <v>96.0</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="32">
         <v>123.0</v>
       </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="42">
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="32">
         <v>174.0</v>
       </c>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
     </row>
     <row r="17">
-      <c r="A17" s="37"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="37"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="29" t="s">
         <v>340</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
     </row>
     <row r="19">
-      <c r="A19" s="37"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="37"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7349,688 +7342,688 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="26" t="s">
         <v>341</v>
       </c>
-      <c r="C1" s="36"/>
+      <c r="C1" s="27"/>
       <c r="D1" s="18"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
     </row>
     <row r="2">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="37"/>
-      <c r="N2" s="37"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
     </row>
     <row r="3">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="38" t="s">
+      <c r="B3" s="29" t="s">
         <v>342</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-      <c r="K3" s="37"/>
-      <c r="L3" s="37"/>
-      <c r="M3" s="37"/>
-      <c r="N3" s="37"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
     </row>
     <row r="4">
-      <c r="A4" s="37"/>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="37"/>
-      <c r="K4" s="37"/>
-      <c r="L4" s="37"/>
-      <c r="M4" s="37"/>
-      <c r="N4" s="37"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
     </row>
     <row r="5">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="37"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="37"/>
-      <c r="I5" s="37"/>
-      <c r="J5" s="37"/>
-      <c r="K5" s="37"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
     </row>
     <row r="6">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="40" t="s">
+      <c r="C6" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="D6" s="40" t="s">
+      <c r="D6" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="G6" s="40" t="s">
+      <c r="G6" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="H6" s="40" t="s">
+      <c r="H6" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="40" t="s">
+      <c r="I6" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="J6" s="40" t="s">
+      <c r="J6" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="40" t="s">
+      <c r="K6" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="40" t="s">
+      <c r="L6" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="40" t="s">
+      <c r="M6" s="30" t="s">
         <v>228</v>
       </c>
-      <c r="N6" s="37"/>
+      <c r="N6" s="28"/>
     </row>
     <row r="7">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="B7" s="41">
+      <c r="B7" s="31">
         <v>36.0</v>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="31">
         <v>45.0</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="31">
         <v>30.0</v>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="31">
         <v>6.0</v>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="31">
         <v>62.0</v>
       </c>
-      <c r="H7" s="41" t="s">
+      <c r="H7" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="I7" s="41" t="s">
+      <c r="I7" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="J7" s="41" t="s">
+      <c r="J7" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="K7" s="41" t="s">
+      <c r="K7" s="31" t="s">
         <v>119</v>
       </c>
-      <c r="L7" s="41" t="s">
+      <c r="L7" s="31" t="s">
         <v>343</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="31" t="s">
         <v>344</v>
       </c>
-      <c r="N7" s="37"/>
+      <c r="N7" s="28"/>
     </row>
     <row r="8">
-      <c r="A8" s="41" t="s">
+      <c r="A8" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="B8" s="41">
+      <c r="B8" s="31">
         <v>20.0</v>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="31">
         <v>25.0</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="D8" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="31">
         <v>10.0</v>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="31">
         <v>5.0</v>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="31">
         <v>30.0</v>
       </c>
-      <c r="H8" s="41" t="s">
+      <c r="H8" s="31" t="s">
         <v>205</v>
       </c>
-      <c r="I8" s="41" t="s">
+      <c r="I8" s="31" t="s">
         <v>206</v>
       </c>
-      <c r="J8" s="41" t="s">
+      <c r="J8" s="31" t="s">
         <v>345</v>
       </c>
-      <c r="K8" s="41" t="s">
+      <c r="K8" s="31" t="s">
         <v>346</v>
       </c>
-      <c r="L8" s="41" t="s">
+      <c r="L8" s="31" t="s">
         <v>347</v>
       </c>
-      <c r="M8" s="41" t="s">
+      <c r="M8" s="31" t="s">
         <v>348</v>
       </c>
-      <c r="N8" s="37"/>
+      <c r="N8" s="28"/>
     </row>
     <row r="9">
-      <c r="A9" s="41" t="s">
+      <c r="A9" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="B9" s="41">
+      <c r="B9" s="31">
         <v>11.0</v>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="31">
         <v>14.0</v>
       </c>
-      <c r="D9" s="41" t="s">
+      <c r="D9" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="31">
         <v>40.0</v>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="31">
         <v>4.0</v>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="31">
         <v>14.0</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="H9" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I9" s="41" t="s">
+      <c r="I9" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J9" s="41" t="s">
+      <c r="J9" s="31" t="s">
         <v>349</v>
       </c>
-      <c r="K9" s="41" t="s">
+      <c r="K9" s="31" t="s">
         <v>350</v>
       </c>
-      <c r="L9" s="41" t="s">
+      <c r="L9" s="31" t="s">
         <v>351</v>
       </c>
-      <c r="M9" s="41" t="s">
+      <c r="M9" s="31" t="s">
         <v>352</v>
       </c>
-      <c r="N9" s="37"/>
+      <c r="N9" s="28"/>
     </row>
     <row r="10">
-      <c r="A10" s="41" t="s">
+      <c r="A10" s="31" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="41">
+      <c r="B10" s="31">
         <v>9.0</v>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="31">
         <v>12.0</v>
       </c>
-      <c r="D10" s="41" t="s">
+      <c r="D10" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="31">
         <v>80.0</v>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="31">
         <v>4.0</v>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="31">
         <v>14.0</v>
       </c>
-      <c r="H10" s="41" t="s">
+      <c r="H10" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I10" s="41" t="s">
+      <c r="I10" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J10" s="41" t="s">
+      <c r="J10" s="31" t="s">
         <v>353</v>
       </c>
-      <c r="K10" s="41" t="s">
+      <c r="K10" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="L10" s="41" t="s">
+      <c r="L10" s="31" t="s">
         <v>355</v>
       </c>
-      <c r="M10" s="41" t="s">
+      <c r="M10" s="31" t="s">
         <v>356</v>
       </c>
-      <c r="N10" s="37"/>
+      <c r="N10" s="28"/>
     </row>
     <row r="11">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="31" t="s">
         <v>191</v>
       </c>
-      <c r="B11" s="41">
+      <c r="B11" s="31">
         <v>8.0</v>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="31">
         <v>10.0</v>
       </c>
-      <c r="D11" s="41" t="s">
+      <c r="D11" s="31" t="s">
         <v>192</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="31">
         <v>50.0</v>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="31">
         <v>4.0</v>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="31">
         <v>14.0</v>
       </c>
-      <c r="H11" s="41" t="s">
+      <c r="H11" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I11" s="41" t="s">
+      <c r="I11" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J11" s="41" t="s">
+      <c r="J11" s="31" t="s">
         <v>357</v>
       </c>
-      <c r="K11" s="41" t="s">
+      <c r="K11" s="31" t="s">
         <v>358</v>
       </c>
-      <c r="L11" s="41" t="s">
+      <c r="L11" s="31" t="s">
         <v>359</v>
       </c>
-      <c r="M11" s="41" t="s">
+      <c r="M11" s="31" t="s">
         <v>360</v>
       </c>
-      <c r="N11" s="37"/>
+      <c r="N11" s="28"/>
     </row>
     <row r="12">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="31" t="s">
         <v>197</v>
       </c>
-      <c r="B12" s="41">
+      <c r="B12" s="31">
         <v>7.0</v>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="31">
         <v>9.0</v>
       </c>
-      <c r="D12" s="41" t="s">
+      <c r="D12" s="31" t="s">
         <v>198</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="31">
         <v>20.0</v>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="31">
         <v>4.0</v>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="31">
         <v>14.0</v>
       </c>
-      <c r="H12" s="41" t="s">
+      <c r="H12" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I12" s="41" t="s">
+      <c r="I12" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J12" s="41" t="s">
+      <c r="J12" s="31" t="s">
         <v>361</v>
       </c>
-      <c r="K12" s="41" t="s">
+      <c r="K12" s="31" t="s">
         <v>362</v>
       </c>
-      <c r="L12" s="41" t="s">
+      <c r="L12" s="31" t="s">
         <v>363</v>
       </c>
-      <c r="M12" s="41" t="s">
+      <c r="M12" s="31" t="s">
         <v>364</v>
       </c>
-      <c r="N12" s="37"/>
+      <c r="N12" s="28"/>
     </row>
     <row r="13">
-      <c r="A13" s="41" t="s">
+      <c r="A13" s="31" t="s">
         <v>203</v>
       </c>
-      <c r="B13" s="41">
+      <c r="B13" s="31">
         <v>5.0</v>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="31">
         <v>7.0</v>
       </c>
-      <c r="D13" s="41" t="s">
+      <c r="D13" s="31" t="s">
         <v>204</v>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="31">
         <v>70.0</v>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="31">
         <v>4.0</v>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="31">
         <v>14.0</v>
       </c>
-      <c r="H13" s="41" t="s">
+      <c r="H13" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J13" s="41" t="s">
+      <c r="J13" s="31" t="s">
         <v>365</v>
       </c>
-      <c r="K13" s="41" t="s">
+      <c r="K13" s="31" t="s">
         <v>366</v>
       </c>
-      <c r="L13" s="41" t="s">
+      <c r="L13" s="31" t="s">
         <v>367</v>
       </c>
-      <c r="M13" s="41" t="s">
+      <c r="M13" s="31" t="s">
         <v>368</v>
       </c>
-      <c r="N13" s="37"/>
+      <c r="N13" s="28"/>
     </row>
     <row r="14">
-      <c r="A14" s="41" t="s">
+      <c r="A14" s="31" t="s">
         <v>217</v>
       </c>
-      <c r="B14" s="41">
+      <c r="B14" s="31">
         <v>5.0</v>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="31">
         <v>7.0</v>
       </c>
-      <c r="D14" s="41" t="s">
+      <c r="D14" s="31" t="s">
         <v>218</v>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="31">
         <v>60.0</v>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="31">
         <v>4.0</v>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="31">
         <v>14.0</v>
       </c>
-      <c r="H14" s="41" t="s">
+      <c r="H14" s="31" t="s">
         <v>219</v>
       </c>
-      <c r="I14" s="41" t="s">
+      <c r="I14" s="31" t="s">
         <v>220</v>
       </c>
-      <c r="J14" s="41" t="s">
+      <c r="J14" s="31" t="s">
         <v>369</v>
       </c>
-      <c r="K14" s="41" t="s">
+      <c r="K14" s="31" t="s">
         <v>370</v>
       </c>
-      <c r="L14" s="41" t="s">
+      <c r="L14" s="31" t="s">
         <v>371</v>
       </c>
-      <c r="M14" s="41" t="s">
+      <c r="M14" s="31" t="s">
         <v>372</v>
       </c>
-      <c r="N14" s="37"/>
+      <c r="N14" s="28"/>
     </row>
     <row r="15">
-      <c r="A15" s="41" t="s">
+      <c r="A15" s="31" t="s">
         <v>211</v>
       </c>
-      <c r="B15" s="41">
+      <c r="B15" s="31">
         <v>4.0</v>
       </c>
-      <c r="C15" s="41">
+      <c r="C15" s="31">
         <v>5.0</v>
       </c>
-      <c r="D15" s="41" t="s">
+      <c r="D15" s="31" t="s">
         <v>212</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="31">
         <v>99.0</v>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="31">
         <v>3.0</v>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="31">
         <v>6.0</v>
       </c>
-      <c r="H15" s="41" t="s">
-        <v>259</v>
-      </c>
-      <c r="I15" s="41" t="s">
-        <v>260</v>
-      </c>
-      <c r="J15" s="41" t="s">
+      <c r="H15" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="I15" s="31" t="s">
+        <v>256</v>
+      </c>
+      <c r="J15" s="31" t="s">
         <v>373</v>
       </c>
-      <c r="K15" s="41" t="s">
+      <c r="K15" s="31" t="s">
         <v>374</v>
       </c>
-      <c r="L15" s="41" t="s">
+      <c r="L15" s="31" t="s">
         <v>375</v>
       </c>
-      <c r="M15" s="41" t="s">
+      <c r="M15" s="31" t="s">
         <v>376</v>
       </c>
-      <c r="N15" s="37"/>
+      <c r="N15" s="28"/>
     </row>
     <row r="16">
-      <c r="A16" s="34" t="s">
+      <c r="A16" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="B16" s="42">
+      <c r="B16" s="32">
         <v>105.0</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="32">
         <v>134.0</v>
       </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="42">
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="32">
         <v>182.0</v>
       </c>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="37"/>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="28"/>
+      <c r="N16" s="28"/>
     </row>
     <row r="17">
-      <c r="A17" s="37"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="37"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
-      <c r="L17" s="37"/>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="28"/>
+      <c r="N17" s="28"/>
     </row>
     <row r="18">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="29" t="s">
         <v>377</v>
       </c>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="37"/>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="28"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="28"/>
+      <c r="N18" s="28"/>
     </row>
     <row r="19">
-      <c r="A19" s="37"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="37"/>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+      <c r="J19" s="28"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="28"/>
+      <c r="N19" s="28"/>
     </row>
     <row r="20">
-      <c r="A20" s="37"/>
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="37"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
     </row>
     <row r="21">
-      <c r="A21" s="37"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="37"/>
-      <c r="L21" s="37"/>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="28"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="28"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="28"/>
+      <c r="N21" s="28"/>
     </row>
     <row r="22">
-      <c r="A22" s="37"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
     </row>
     <row r="23">
-      <c r="A23" s="37"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="37"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="37"/>
-      <c r="N23" s="37"/>
+      <c r="A23" s="28"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
     </row>
     <row r="24">
-      <c r="A24" s="37"/>
-      <c r="B24" s="37"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="37"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
-      <c r="K24" s="37"/>
-      <c r="L24" s="37"/>
-      <c r="M24" s="37"/>
-      <c r="N24" s="37"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="28"/>
+      <c r="N24" s="28"/>
     </row>
     <row r="25">
-      <c r="A25" s="37"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="37"/>
-      <c r="L25" s="37"/>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/excel-final/Esquema de Direccionamiento IP.xlsx
+++ b/excel-final/Esquema de Direccionamiento IP.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="728" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="734" uniqueCount="384">
   <si>
     <t>Caso Estudio:</t>
   </si>
@@ -508,6 +508,9 @@
     <t>Mascara de Subred</t>
   </si>
   <si>
+    <t>Direccion de Broadcast</t>
+  </si>
+  <si>
     <t>Ventas</t>
   </si>
   <si>
@@ -652,171 +655,180 @@
     <t>10.192.42.159</t>
   </si>
   <si>
+    <t>Nativa</t>
+  </si>
+  <si>
+    <t>VLNAT</t>
+  </si>
+  <si>
+    <t>10.192.42.160</t>
+  </si>
+  <si>
+    <t>10.192.42.161</t>
+  </si>
+  <si>
+    <t>10.192.42.190</t>
+  </si>
+  <si>
+    <t>10.192.42.191</t>
+  </si>
+  <si>
+    <t>Servidores</t>
+  </si>
+  <si>
+    <t>VLSER</t>
+  </si>
+  <si>
+    <t>/28</t>
+  </si>
+  <si>
+    <t>255.255.255.240</t>
+  </si>
+  <si>
+    <t>10.192.42.192</t>
+  </si>
+  <si>
+    <t>10.192.42.193</t>
+  </si>
+  <si>
+    <t>10.192.42.206</t>
+  </si>
+  <si>
+    <t>10.192.42.207</t>
+  </si>
+  <si>
+    <t>Nota:</t>
+  </si>
+  <si>
+    <t>Nativa se calculo con 15 equipos actuales asumidos para gestion; ajustar si tu Packet Tracer usa otra cantidad. XYZW queda reservado.</t>
+  </si>
+  <si>
+    <t>Validacion:</t>
+  </si>
+  <si>
+    <t>Todas las VLAN quedan dentro de 10.192.40.0/22 y no se solapan.</t>
+  </si>
+  <si>
+    <t>Yeremi Tanner Villavicencio Rios</t>
+  </si>
+  <si>
+    <t>10.192.44.0/22</t>
+  </si>
+  <si>
+    <t>10.192.44.126</t>
+  </si>
+  <si>
+    <t>10.192.44.127</t>
+  </si>
+  <si>
+    <t>10.192.44.128</t>
+  </si>
+  <si>
+    <t>10.192.44.129</t>
+  </si>
+  <si>
+    <t>10.192.44.190</t>
+  </si>
+  <si>
+    <t>10.192.44.191</t>
+  </si>
+  <si>
+    <t>10.192.44.192</t>
+  </si>
+  <si>
+    <t>10.192.44.193</t>
+  </si>
+  <si>
+    <t>10.192.44.222</t>
+  </si>
+  <si>
+    <t>10.192.44.223</t>
+  </si>
+  <si>
+    <t>10.192.44.224</t>
+  </si>
+  <si>
+    <t>10.192.44.225</t>
+  </si>
+  <si>
+    <t>10.192.44.238</t>
+  </si>
+  <si>
+    <t>10.192.44.239</t>
+  </si>
+  <si>
+    <t>10.192.44.240</t>
+  </si>
+  <si>
+    <t>10.192.44.241</t>
+  </si>
+  <si>
+    <t>10.192.44.254</t>
+  </si>
+  <si>
+    <t>10.192.44.255</t>
+  </si>
+  <si>
+    <t>10.192.45.0</t>
+  </si>
+  <si>
+    <t>10.192.45.1</t>
+  </si>
+  <si>
+    <t>10.192.45.14</t>
+  </si>
+  <si>
+    <t>10.192.45.15</t>
+  </si>
+  <si>
+    <t>10.192.45.16</t>
+  </si>
+  <si>
+    <t>10.192.45.17</t>
+  </si>
+  <si>
+    <t>10.192.45.30</t>
+  </si>
+  <si>
+    <t>10.192.45.31</t>
+  </si>
+  <si>
     <t>Nativa/Gestion</t>
   </si>
   <si>
-    <t>VLNAT</t>
-  </si>
-  <si>
-    <t>10.192.42.160</t>
-  </si>
-  <si>
-    <t>10.192.42.161</t>
-  </si>
-  <si>
-    <t>10.192.42.190</t>
-  </si>
-  <si>
-    <t>10.192.42.191</t>
-  </si>
-  <si>
-    <t>Servidores</t>
-  </si>
-  <si>
-    <t>VLSER</t>
-  </si>
-  <si>
-    <t>/28</t>
-  </si>
-  <si>
-    <t>255.255.255.240</t>
-  </si>
-  <si>
-    <t>10.192.42.192</t>
-  </si>
-  <si>
-    <t>10.192.42.193</t>
-  </si>
-  <si>
-    <t>10.192.42.206</t>
-  </si>
-  <si>
-    <t>10.192.42.207</t>
+    <t>/29</t>
+  </si>
+  <si>
+    <t>255.255.255.248</t>
+  </si>
+  <si>
+    <t>10.192.45.32</t>
+  </si>
+  <si>
+    <t>10.192.45.33</t>
+  </si>
+  <si>
+    <t>10.192.45.38</t>
+  </si>
+  <si>
+    <t>10.192.45.39</t>
+  </si>
+  <si>
+    <t>10.192.45.40</t>
+  </si>
+  <si>
+    <t>10.192.45.41</t>
+  </si>
+  <si>
+    <t>10.192.45.46</t>
+  </si>
+  <si>
+    <t>10.192.45.47</t>
   </si>
   <si>
     <t>Total Host</t>
   </si>
   <si>
-    <t>Yeremi Tanner Villavicencio Rios</t>
-  </si>
-  <si>
-    <t>10.192.44.0/22</t>
-  </si>
-  <si>
-    <t>Direccion de Broadcast</t>
-  </si>
-  <si>
-    <t>10.192.44.126</t>
-  </si>
-  <si>
-    <t>10.192.44.127</t>
-  </si>
-  <si>
-    <t>10.192.44.128</t>
-  </si>
-  <si>
-    <t>10.192.44.129</t>
-  </si>
-  <si>
-    <t>10.192.44.190</t>
-  </si>
-  <si>
-    <t>10.192.44.191</t>
-  </si>
-  <si>
-    <t>10.192.44.192</t>
-  </si>
-  <si>
-    <t>10.192.44.193</t>
-  </si>
-  <si>
-    <t>10.192.44.222</t>
-  </si>
-  <si>
-    <t>10.192.44.223</t>
-  </si>
-  <si>
-    <t>10.192.44.224</t>
-  </si>
-  <si>
-    <t>10.192.44.225</t>
-  </si>
-  <si>
-    <t>10.192.44.238</t>
-  </si>
-  <si>
-    <t>10.192.44.239</t>
-  </si>
-  <si>
-    <t>10.192.44.240</t>
-  </si>
-  <si>
-    <t>10.192.44.241</t>
-  </si>
-  <si>
-    <t>10.192.44.254</t>
-  </si>
-  <si>
-    <t>10.192.44.255</t>
-  </si>
-  <si>
-    <t>10.192.45.0</t>
-  </si>
-  <si>
-    <t>10.192.45.1</t>
-  </si>
-  <si>
-    <t>10.192.45.14</t>
-  </si>
-  <si>
-    <t>10.192.45.15</t>
-  </si>
-  <si>
-    <t>10.192.45.16</t>
-  </si>
-  <si>
-    <t>10.192.45.17</t>
-  </si>
-  <si>
-    <t>10.192.45.30</t>
-  </si>
-  <si>
-    <t>10.192.45.31</t>
-  </si>
-  <si>
-    <t>/29</t>
-  </si>
-  <si>
-    <t>255.255.255.248</t>
-  </si>
-  <si>
-    <t>10.192.45.32</t>
-  </si>
-  <si>
-    <t>10.192.45.33</t>
-  </si>
-  <si>
-    <t>10.192.45.38</t>
-  </si>
-  <si>
-    <t>10.192.45.39</t>
-  </si>
-  <si>
-    <t>10.192.45.40</t>
-  </si>
-  <si>
-    <t>10.192.45.41</t>
-  </si>
-  <si>
-    <t>10.192.45.46</t>
-  </si>
-  <si>
-    <t>10.192.45.47</t>
-  </si>
-  <si>
-    <t>Validacion:</t>
-  </si>
-  <si>
     <t>Todas las VLAN quedan dentro de 10.192.44.0/22 y no se solapan.</t>
   </si>
   <si>
@@ -937,6 +949,18 @@
     <t>10.192.52.0/22</t>
   </si>
   <si>
+    <t>10.192.52.30</t>
+  </si>
+  <si>
+    <t>10.192.52.31</t>
+  </si>
+  <si>
+    <t>10.192.52.32</t>
+  </si>
+  <si>
+    <t>10.192.52.33</t>
+  </si>
+  <si>
     <t>10.192.52.62</t>
   </si>
   <si>
@@ -1021,18 +1045,6 @@
     <t>10.192.52.177</t>
   </si>
   <si>
-    <t>10.192.52.182</t>
-  </si>
-  <si>
-    <t>10.192.52.183</t>
-  </si>
-  <si>
-    <t>10.192.52.184</t>
-  </si>
-  <si>
-    <t>10.192.52.185</t>
-  </si>
-  <si>
     <t>10.192.52.190</t>
   </si>
   <si>
@@ -1151,6 +1163,12 @@
   </si>
   <si>
     <t>Todas las VLAN quedan dentro de 10.192.56.0/22 y no se solapan.</t>
+  </si>
+  <si>
+    <t>10.192.56.114</t>
+  </si>
+  <si>
+    <t>10.192.56.115</t>
   </si>
 </sst>
 </file>
@@ -1195,7 +1213,7 @@
     <font>
       <b/>
       <sz val="11.0"/>
-      <color rgb="FF000000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1206,7 +1224,7 @@
     <font>
       <b/>
       <sz val="11.0"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1286,7 +1304,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1351,33 +1369,28 @@
     <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1385,6 +1398,19 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="1" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2664,7 +2690,7 @@
         <v>162</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>12</v>
+        <v>127</v>
       </c>
       <c r="K6" s="22" t="s">
         <v>15</v>
@@ -2673,389 +2699,392 @@
         <v>16</v>
       </c>
       <c r="M6" s="22" t="s">
-        <v>17</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="A7" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="23">
         <v>198.0</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="23">
         <v>248.0</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="D7" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="23">
         <v>10.0</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="23">
         <v>8.0</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="23">
         <v>254.0</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="H7" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="I7" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="J7" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="M7" s="2" t="s">
+      <c r="L7" s="23" t="s">
         <v>168</v>
       </c>
+      <c r="M7" s="23" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B8" s="2">
+      <c r="A8" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="23">
         <v>100.0</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="23">
         <v>125.0</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="D8" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="23">
         <v>11.0</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="23">
         <v>7.0</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="23">
         <v>126.0</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="H8" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="I8" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="J8" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="K8" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="L8" s="23" t="s">
         <v>176</v>
       </c>
+      <c r="M8" s="23" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="B9" s="2">
+      <c r="A9" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="23">
         <v>41.0</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9" s="23">
         <v>52.0</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E9" s="2">
+      <c r="D9" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="23">
         <v>12.0</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="23">
         <v>6.0</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="23">
         <v>62.0</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I9" s="2" t="s">
+      <c r="H9" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="I9" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="J9" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="L9" s="2" t="s">
+      <c r="K9" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="L9" s="23" t="s">
         <v>184</v>
       </c>
+      <c r="M9" s="23" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="2">
+      <c r="A10" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="23">
         <v>31.0</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10" s="23">
         <v>39.0</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="D10" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" s="23">
         <v>13.0</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="23">
         <v>6.0</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="23">
         <v>62.0</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I10" s="2" t="s">
+      <c r="H10" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K10" s="2" t="s">
+      <c r="I10" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="J10" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="K10" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="L10" s="23" t="s">
         <v>190</v>
       </c>
+      <c r="M10" s="23" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B11" s="2">
+      <c r="A11" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="23">
         <v>29.0</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11" s="23">
         <v>37.0</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" s="2">
+      <c r="D11" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="23">
         <v>14.0</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="23">
         <v>6.0</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="23">
         <v>62.0</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I11" s="2" t="s">
+      <c r="H11" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="K11" s="2" t="s">
+      <c r="I11" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="J11" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="L11" s="2" t="s">
+      <c r="K11" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="L11" s="23" t="s">
         <v>196</v>
       </c>
+      <c r="M11" s="23" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B12" s="2">
+      <c r="A12" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="23">
         <v>25.0</v>
       </c>
-      <c r="C12" s="2">
+      <c r="C12" s="23">
         <v>32.0</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E12" s="2">
+      <c r="D12" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" s="23">
         <v>15.0</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="23">
         <v>6.0</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="23">
         <v>62.0</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="I12" s="2" t="s">
+      <c r="H12" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="K12" s="2" t="s">
+      <c r="I12" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="J12" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="L12" s="2" t="s">
+      <c r="K12" s="23" t="s">
         <v>201</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="L12" s="23" t="s">
         <v>202</v>
       </c>
+      <c r="M12" s="23" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13" s="2">
+      <c r="A13" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" s="23">
         <v>18.0</v>
       </c>
-      <c r="C13" s="2">
+      <c r="C13" s="23">
         <v>23.0</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="E13" s="2">
+      <c r="D13" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="E13" s="23">
         <v>16.0</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="23">
         <v>5.0</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="23">
         <v>30.0</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I13" s="2" t="s">
+      <c r="H13" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="I13" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="J13" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="L13" s="2" t="s">
+      <c r="K13" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="L13" s="23" t="s">
         <v>210</v>
       </c>
+      <c r="M13" s="23" t="s">
+        <v>211</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B14" s="2">
+      <c r="A14" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14" s="23">
         <v>15.0</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14" s="23">
         <v>19.0</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E14" s="2">
+      <c r="D14" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E14" s="23">
         <v>99.0</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="23">
         <v>5.0</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="23">
         <v>30.0</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="I14" s="2" t="s">
+      <c r="H14" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="J14" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="K14" s="2" t="s">
+      <c r="I14" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="J14" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="L14" s="2" t="s">
+      <c r="K14" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="M14" s="2" t="s">
+      <c r="L14" s="23" t="s">
         <v>216</v>
       </c>
+      <c r="M14" s="23" t="s">
+        <v>217</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B15" s="2">
+      <c r="A15" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" s="23">
         <v>10.0</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15" s="23">
         <v>13.0</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E15" s="2">
+      <c r="D15" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="E15" s="23">
         <v>17.0</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="23">
         <v>4.0</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="23">
         <v>14.0</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="I15" s="2" t="s">
+      <c r="H15" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="I15" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="J15" s="23" t="s">
         <v>222</v>
       </c>
-      <c r="L15" s="2" t="s">
+      <c r="K15" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="L15" s="23" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="s">
+      <c r="M15" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="B16" s="24">
-        <f t="shared" ref="B16:C16" si="1">SUM(B7:B15)</f>
-        <v>467</v>
-      </c>
-      <c r="C16" s="24">
-        <f t="shared" si="1"/>
-        <v>588</v>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>229</v>
       </c>
     </row>
   </sheetData>
@@ -3077,7 +3106,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="33.0"/>
     <col customWidth="1" min="2" max="2" width="25.88"/>
-    <col customWidth="1" min="3" max="3" width="51.63"/>
+    <col customWidth="1" min="3" max="3" width="41.75"/>
     <col customWidth="1" min="4" max="4" width="23.25"/>
     <col customWidth="1" min="5" max="5" width="13.13"/>
     <col customWidth="1" min="7" max="7" width="18.25"/>
@@ -3090,14 +3119,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="26" t="s">
-        <v>226</v>
-      </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="18"/>
+      <c r="B1" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="C1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="28"/>
       <c r="F1" s="28"/>
       <c r="G1" s="28"/>
@@ -3109,10 +3138,10 @@
       <c r="M1" s="28"/>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="25" t="s">
         <v>104</v>
       </c>
       <c r="C2" s="28"/>
@@ -3128,11 +3157,11 @@
       <c r="M2" s="28"/>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="29" t="s">
-        <v>227</v>
+      <c r="B3" s="25" t="s">
+        <v>231</v>
       </c>
       <c r="C3" s="28"/>
       <c r="D3" s="28"/>
@@ -3177,430 +3206,430 @@
       <c r="M5" s="28"/>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="30" t="s">
+      <c r="I6" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="J6" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="30" t="s">
+      <c r="K6" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="30" t="s">
+      <c r="L6" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="30" t="s">
-        <v>228</v>
+      <c r="M6" s="22" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="B7" s="31">
+      <c r="A7" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="23">
         <v>70.0</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="23">
         <v>88.0</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="E7" s="31">
+      <c r="D7" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="23">
         <v>30.0</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="23">
         <v>7.0</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="23">
         <v>126.0</v>
       </c>
-      <c r="H7" s="31" t="s">
+      <c r="H7" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>232</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="23">
+        <v>35.0</v>
+      </c>
+      <c r="C8" s="23">
+        <v>44.0</v>
+      </c>
+      <c r="D8" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="I7" s="31" t="s">
-        <v>172</v>
-      </c>
-      <c r="J7" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="K7" s="31" t="s">
-        <v>101</v>
-      </c>
-      <c r="L7" s="31" t="s">
-        <v>229</v>
-      </c>
-      <c r="M7" s="31" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="B8" s="31">
+      <c r="E8" s="23">
+        <v>31.0</v>
+      </c>
+      <c r="F8" s="23">
+        <v>6.0</v>
+      </c>
+      <c r="G8" s="23">
+        <v>62.0</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="L8" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="23">
+        <v>15.0</v>
+      </c>
+      <c r="C9" s="23">
+        <v>19.0</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="23">
+        <v>32.0</v>
+      </c>
+      <c r="F9" s="23">
+        <v>5.0</v>
+      </c>
+      <c r="G9" s="23">
+        <v>30.0</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="L9" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="23">
+        <v>11.0</v>
+      </c>
+      <c r="C10" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" s="23">
+        <v>33.0</v>
+      </c>
+      <c r="F10" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="G10" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="L10" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="23">
+        <v>10.0</v>
+      </c>
+      <c r="C11" s="23">
+        <v>13.0</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="23">
+        <v>34.0</v>
+      </c>
+      <c r="F11" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="G11" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="L11" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="M11" s="23" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="23">
+        <v>9.0</v>
+      </c>
+      <c r="C12" s="23">
+        <v>12.0</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" s="23">
         <v>35.0</v>
       </c>
-      <c r="C8" s="31">
-        <v>44.0</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="E8" s="31">
-        <v>31.0</v>
-      </c>
-      <c r="F8" s="31">
+      <c r="F12" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="G12" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="L12" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="M12" s="23" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" s="23">
         <v>6.0</v>
       </c>
-      <c r="G8" s="31">
-        <v>62.0</v>
-      </c>
-      <c r="H8" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="I8" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="J8" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="K8" s="31" t="s">
-        <v>232</v>
-      </c>
-      <c r="L8" s="31" t="s">
-        <v>233</v>
-      </c>
-      <c r="M8" s="31" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="B9" s="31">
-        <v>15.0</v>
-      </c>
-      <c r="C9" s="31">
-        <v>19.0</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="E9" s="31">
-        <v>32.0</v>
-      </c>
-      <c r="F9" s="31">
-        <v>5.0</v>
-      </c>
-      <c r="G9" s="31">
-        <v>30.0</v>
-      </c>
-      <c r="H9" s="31" t="s">
+      <c r="C13" s="23">
+        <v>8.0</v>
+      </c>
+      <c r="D13" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="I9" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="J9" s="31" t="s">
-        <v>235</v>
-      </c>
-      <c r="K9" s="31" t="s">
-        <v>236</v>
-      </c>
-      <c r="L9" s="31" t="s">
-        <v>237</v>
-      </c>
-      <c r="M9" s="31" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="31">
-        <v>11.0</v>
-      </c>
-      <c r="C10" s="31">
+      <c r="E13" s="23">
+        <v>36.0</v>
+      </c>
+      <c r="F13" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="G13" s="23">
         <v>14.0</v>
       </c>
-      <c r="D10" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="31">
-        <v>33.0</v>
-      </c>
-      <c r="F10" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="G10" s="31">
-        <v>14.0</v>
-      </c>
-      <c r="H10" s="31" t="s">
+      <c r="H13" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="B14" s="23">
+        <v>2.0</v>
+      </c>
+      <c r="C14" s="23">
+        <v>3.0</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E14" s="23">
+        <v>99.0</v>
+      </c>
+      <c r="F14" s="23">
+        <v>3.0</v>
+      </c>
+      <c r="G14" s="23">
+        <v>6.0</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>261</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="L14" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" s="23">
+        <v>2.0</v>
+      </c>
+      <c r="C15" s="23">
+        <v>3.0</v>
+      </c>
+      <c r="D15" s="23" t="s">
         <v>219</v>
       </c>
-      <c r="I10" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="J10" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="K10" s="31" t="s">
-        <v>240</v>
-      </c>
-      <c r="L10" s="31" t="s">
-        <v>241</v>
-      </c>
-      <c r="M10" s="31" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="B11" s="31">
-        <v>10.0</v>
-      </c>
-      <c r="C11" s="31">
-        <v>13.0</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" s="31">
-        <v>34.0</v>
-      </c>
-      <c r="F11" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="G11" s="31">
-        <v>14.0</v>
-      </c>
-      <c r="H11" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="J11" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="K11" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="L11" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="M11" s="31" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="B12" s="31">
-        <v>9.0</v>
-      </c>
-      <c r="C12" s="31">
-        <v>12.0</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="E12" s="31">
-        <v>35.0</v>
-      </c>
-      <c r="F12" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="G12" s="31">
-        <v>14.0</v>
-      </c>
-      <c r="H12" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I12" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="J12" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="K12" s="31" t="s">
-        <v>248</v>
-      </c>
-      <c r="L12" s="31" t="s">
-        <v>249</v>
-      </c>
-      <c r="M12" s="31" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13" s="31">
+      <c r="E15" s="23">
+        <v>37.0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>3.0</v>
+      </c>
+      <c r="G15" s="23">
         <v>6.0</v>
       </c>
-      <c r="C13" s="31">
-        <v>8.0</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="E13" s="31">
-        <v>36.0</v>
-      </c>
-      <c r="F13" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="G13" s="31">
-        <v>14.0</v>
-      </c>
-      <c r="H13" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I13" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="J13" s="31" t="s">
-        <v>251</v>
-      </c>
-      <c r="K13" s="31" t="s">
-        <v>252</v>
-      </c>
-      <c r="L13" s="31" t="s">
-        <v>253</v>
-      </c>
-      <c r="M13" s="31" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="B14" s="31">
-        <v>2.0</v>
-      </c>
-      <c r="C14" s="31">
-        <v>3.0</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="E14" s="31">
-        <v>99.0</v>
-      </c>
-      <c r="F14" s="31">
-        <v>3.0</v>
-      </c>
-      <c r="G14" s="31">
-        <v>6.0</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="I14" s="31" t="s">
-        <v>256</v>
-      </c>
-      <c r="J14" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="K14" s="31" t="s">
-        <v>258</v>
-      </c>
-      <c r="L14" s="31" t="s">
+      <c r="H15" s="23" t="s">
         <v>259</v>
       </c>
-      <c r="M14" s="31" t="s">
+      <c r="I15" s="23" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="31" t="s">
-        <v>217</v>
-      </c>
-      <c r="B15" s="31">
-        <v>2.0</v>
-      </c>
-      <c r="C15" s="31">
-        <v>3.0</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="E15" s="31">
-        <v>37.0</v>
-      </c>
-      <c r="F15" s="31">
-        <v>3.0</v>
-      </c>
-      <c r="G15" s="31">
-        <v>6.0</v>
-      </c>
-      <c r="H15" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="I15" s="31" t="s">
-        <v>256</v>
-      </c>
-      <c r="J15" s="31" t="s">
-        <v>261</v>
-      </c>
-      <c r="K15" s="31" t="s">
-        <v>262</v>
-      </c>
-      <c r="L15" s="31" t="s">
-        <v>263</v>
-      </c>
-      <c r="M15" s="31" t="s">
-        <v>264</v>
+      <c r="J15" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="L15" s="23" t="s">
+        <v>267</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="B16" s="32">
+      <c r="A16" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="B16" s="29">
         <f>SUM(B7:B15)</f>
         <v>160</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="29">
         <v>204.0</v>
       </c>
       <c r="D16" s="28"/>
       <c r="E16" s="28"/>
       <c r="F16" s="28"/>
-      <c r="G16" s="32">
+      <c r="G16" s="29">
         <v>286.0</v>
       </c>
       <c r="H16" s="28"/>
@@ -3626,11 +3655,11 @@
       <c r="M17" s="28"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>266</v>
+      <c r="A18" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>270</v>
       </c>
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
@@ -3660,9 +3689,6 @@
       <c r="M19" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:D1"/>
-  </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3688,14 +3714,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="26" t="s">
-        <v>267</v>
-      </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="18"/>
+      <c r="B1" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="C1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="28"/>
       <c r="F1" s="28"/>
       <c r="G1" s="28"/>
@@ -3845,13 +3871,13 @@
       <c r="EU1" s="28"/>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="33"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="28"/>
       <c r="E2" s="28"/>
       <c r="F2" s="28"/>
@@ -4002,13 +4028,13 @@
       <c r="EU2" s="28"/>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="29" t="s">
-        <v>268</v>
-      </c>
-      <c r="C3" s="33"/>
+      <c r="B3" s="25" t="s">
+        <v>272</v>
+      </c>
+      <c r="C3" s="30"/>
       <c r="D3" s="28"/>
       <c r="E3" s="28"/>
       <c r="F3" s="28"/>
@@ -4465,44 +4491,44 @@
       <c r="EU5" s="28"/>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="22" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="22" t="s">
         <v>157</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="22" t="s">
         <v>158</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="22" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="30" t="s">
+      <c r="I6" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="J6" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="30" t="s">
+      <c r="K6" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="30" t="s">
+      <c r="L6" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="30" t="s">
-        <v>228</v>
+      <c r="M6" s="22" t="s">
+        <v>163</v>
       </c>
       <c r="N6" s="28"/>
       <c r="O6" s="28"/>
@@ -4644,44 +4670,44 @@
       <c r="EU6" s="28"/>
     </row>
     <row r="7" ht="24.75" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="B7" s="31">
+      <c r="A7" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="23">
         <v>78.0</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="23">
         <v>98.0</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="E7" s="31">
+      <c r="D7" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="23">
         <v>20.0</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="23">
         <v>7.0</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="23">
         <v>126.0</v>
       </c>
-      <c r="H7" s="31" t="s">
-        <v>171</v>
-      </c>
-      <c r="I7" s="31" t="s">
+      <c r="H7" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="J7" s="31" t="s">
+      <c r="I7" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="J7" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="K7" s="31" t="s">
+      <c r="K7" s="23" t="s">
         <v>107</v>
       </c>
-      <c r="L7" s="31" t="s">
-        <v>269</v>
-      </c>
-      <c r="M7" s="31" t="s">
-        <v>270</v>
+      <c r="L7" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>274</v>
       </c>
       <c r="N7" s="28"/>
       <c r="O7" s="28"/>
@@ -4823,44 +4849,44 @@
       <c r="EU7" s="28"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="B8" s="31">
+      <c r="A8" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="23">
         <v>40.0</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="23">
         <v>50.0</v>
       </c>
-      <c r="D8" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="E8" s="31">
+      <c r="D8" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="23">
         <v>21.0</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="23">
         <v>6.0</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="23">
         <v>62.0</v>
       </c>
-      <c r="H8" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="I8" s="31" t="s">
+      <c r="H8" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="J8" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="K8" s="31" t="s">
-        <v>272</v>
-      </c>
-      <c r="L8" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="M8" s="31" t="s">
-        <v>274</v>
+      <c r="I8" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>275</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="L8" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>278</v>
       </c>
       <c r="N8" s="28"/>
       <c r="O8" s="28"/>
@@ -5002,44 +5028,44 @@
       <c r="EU8" s="28"/>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="B9" s="31">
+      <c r="A9" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="23">
         <v>16.0</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="23">
         <v>20.0</v>
       </c>
-      <c r="D9" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="E9" s="31">
+      <c r="D9" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="23">
         <v>22.0</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="23">
         <v>5.0</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="23">
         <v>30.0</v>
       </c>
-      <c r="H9" s="31" t="s">
-        <v>205</v>
-      </c>
-      <c r="I9" s="31" t="s">
+      <c r="H9" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="J9" s="31" t="s">
-        <v>275</v>
-      </c>
-      <c r="K9" s="31" t="s">
-        <v>276</v>
-      </c>
-      <c r="L9" s="31" t="s">
-        <v>277</v>
-      </c>
-      <c r="M9" s="31" t="s">
-        <v>278</v>
+      <c r="I9" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="L9" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>282</v>
       </c>
       <c r="N9" s="28"/>
       <c r="O9" s="28"/>
@@ -5181,44 +5207,44 @@
       <c r="EU9" s="28"/>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="31">
+      <c r="A10" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="23">
         <v>12.0</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="23">
         <v>15.0</v>
       </c>
-      <c r="D10" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="31">
+      <c r="D10" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" s="23">
         <v>23.0</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="23">
         <v>5.0</v>
       </c>
-      <c r="G10" s="31">
+      <c r="G10" s="23">
         <v>30.0</v>
       </c>
-      <c r="H10" s="31" t="s">
-        <v>205</v>
-      </c>
-      <c r="I10" s="31" t="s">
+      <c r="H10" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="J10" s="31" t="s">
-        <v>279</v>
-      </c>
-      <c r="K10" s="31" t="s">
-        <v>280</v>
-      </c>
-      <c r="L10" s="31" t="s">
-        <v>281</v>
-      </c>
-      <c r="M10" s="31" t="s">
-        <v>282</v>
+      <c r="I10" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="L10" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>286</v>
       </c>
       <c r="N10" s="28"/>
       <c r="O10" s="28"/>
@@ -5360,44 +5386,44 @@
       <c r="EU10" s="28"/>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="B11" s="31">
+      <c r="A11" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="23">
         <v>11.0</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="23">
         <v>14.0</v>
       </c>
-      <c r="D11" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" s="31">
+      <c r="D11" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="23">
         <v>24.0</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="23">
         <v>4.0</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="23">
         <v>14.0</v>
       </c>
-      <c r="H11" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I11" s="31" t="s">
+      <c r="H11" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="J11" s="31" t="s">
-        <v>283</v>
-      </c>
-      <c r="K11" s="31" t="s">
-        <v>284</v>
-      </c>
-      <c r="L11" s="31" t="s">
-        <v>285</v>
-      </c>
-      <c r="M11" s="31" t="s">
-        <v>286</v>
+      <c r="I11" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="L11" s="23" t="s">
+        <v>289</v>
+      </c>
+      <c r="M11" s="23" t="s">
+        <v>290</v>
       </c>
       <c r="N11" s="28"/>
       <c r="O11" s="28"/>
@@ -5539,44 +5565,44 @@
       <c r="EU11" s="28"/>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="B12" s="31">
+      <c r="A12" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="23">
         <v>10.0</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="23">
         <v>13.0</v>
       </c>
-      <c r="D12" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="E12" s="31">
+      <c r="D12" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" s="23">
         <v>25.0</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="23">
         <v>4.0</v>
       </c>
-      <c r="G12" s="31">
+      <c r="G12" s="23">
         <v>14.0</v>
       </c>
-      <c r="H12" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I12" s="31" t="s">
+      <c r="H12" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="J12" s="31" t="s">
-        <v>287</v>
-      </c>
-      <c r="K12" s="31" t="s">
-        <v>288</v>
-      </c>
-      <c r="L12" s="31" t="s">
-        <v>289</v>
-      </c>
-      <c r="M12" s="31" t="s">
-        <v>290</v>
+      <c r="I12" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="L12" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="M12" s="23" t="s">
+        <v>294</v>
       </c>
       <c r="N12" s="28"/>
       <c r="O12" s="28"/>
@@ -5718,44 +5744,44 @@
       <c r="EU12" s="28"/>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="B13" s="31">
+      <c r="A13" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="B13" s="23">
         <v>10.0</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="23">
         <v>13.0</v>
       </c>
-      <c r="D13" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="E13" s="31">
+      <c r="D13" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E13" s="23">
         <v>99.0</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="23">
         <v>4.0</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="23">
         <v>14.0</v>
       </c>
-      <c r="H13" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I13" s="31" t="s">
+      <c r="H13" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="J13" s="31" t="s">
-        <v>291</v>
-      </c>
-      <c r="K13" s="31" t="s">
-        <v>292</v>
-      </c>
-      <c r="L13" s="31" t="s">
-        <v>293</v>
-      </c>
-      <c r="M13" s="31" t="s">
-        <v>294</v>
+      <c r="I13" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>298</v>
       </c>
       <c r="N13" s="28"/>
       <c r="O13" s="28"/>
@@ -5897,44 +5923,44 @@
       <c r="EU13" s="28"/>
     </row>
     <row r="14">
-      <c r="A14" s="31" t="s">
-        <v>203</v>
-      </c>
-      <c r="B14" s="31">
+      <c r="A14" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="B14" s="23">
         <v>8.0</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="23">
         <v>10.0</v>
       </c>
-      <c r="D14" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="E14" s="31">
+      <c r="D14" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="E14" s="23">
         <v>26.0</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="23">
         <v>4.0</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="23">
         <v>14.0</v>
       </c>
-      <c r="H14" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I14" s="31" t="s">
+      <c r="H14" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="J14" s="31" t="s">
-        <v>295</v>
-      </c>
-      <c r="K14" s="31" t="s">
-        <v>296</v>
-      </c>
-      <c r="L14" s="31" t="s">
-        <v>297</v>
-      </c>
-      <c r="M14" s="31" t="s">
-        <v>298</v>
+      <c r="I14" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>300</v>
+      </c>
+      <c r="L14" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>302</v>
       </c>
       <c r="N14" s="28"/>
       <c r="O14" s="28"/>
@@ -6076,44 +6102,44 @@
       <c r="EU14" s="28"/>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="s">
-        <v>217</v>
-      </c>
-      <c r="B15" s="31">
+      <c r="A15" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" s="23">
         <v>5.0</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="23">
         <v>7.0</v>
       </c>
-      <c r="D15" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="E15" s="31">
+      <c r="D15" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="E15" s="23">
         <v>27.0</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="23">
         <v>4.0</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="23">
         <v>14.0</v>
       </c>
-      <c r="H15" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I15" s="31" t="s">
+      <c r="H15" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="J15" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="K15" s="31" t="s">
-        <v>300</v>
-      </c>
-      <c r="L15" s="31" t="s">
-        <v>301</v>
-      </c>
-      <c r="M15" s="31" t="s">
-        <v>302</v>
+      <c r="I15" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="L15" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>306</v>
       </c>
       <c r="N15" s="28"/>
       <c r="O15" s="28"/>
@@ -6255,25 +6281,25 @@
       <c r="EU15" s="28"/>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="B16" s="32">
+      <c r="A16" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="B16" s="29">
         <v>190.0</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="29">
         <v>240.0</v>
       </c>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="32">
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="29">
         <v>318.0</v>
       </c>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
       <c r="L16" s="28"/>
       <c r="M16" s="28"/>
       <c r="N16" s="28"/>
@@ -6416,17 +6442,17 @@
       <c r="EU16" s="28"/>
     </row>
     <row r="17">
-      <c r="A17" s="33"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
+      <c r="A17" s="30"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
       <c r="L17" s="28"/>
       <c r="M17" s="28"/>
       <c r="N17" s="28"/>
@@ -6569,13 +6595,13 @@
       <c r="EU17" s="28"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>303</v>
-      </c>
-      <c r="C18" s="33"/>
+      <c r="A18" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="C18" s="30"/>
       <c r="D18" s="28"/>
       <c r="E18" s="28"/>
       <c r="F18" s="28"/>
@@ -6726,12 +6752,9 @@
       <c r="EU18" s="28"/>
     </row>
     <row r="19">
-      <c r="J19" s="34"/>
+      <c r="J19" s="31"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:D1"/>
-  </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -6749,14 +6772,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="26" t="s">
-        <v>304</v>
-      </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="18"/>
+      <c r="B1" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="28"/>
       <c r="F1" s="28"/>
       <c r="G1" s="28"/>
@@ -6768,13 +6791,13 @@
       <c r="M1" s="28"/>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="C2" s="33"/>
+      <c r="C2" s="30"/>
       <c r="D2" s="28"/>
       <c r="E2" s="28"/>
       <c r="F2" s="28"/>
@@ -6787,13 +6810,13 @@
       <c r="M2" s="28"/>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="29" t="s">
-        <v>305</v>
-      </c>
-      <c r="C3" s="33"/>
+      <c r="B3" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="C3" s="30"/>
       <c r="D3" s="28"/>
       <c r="E3" s="28"/>
       <c r="F3" s="28"/>
@@ -6835,430 +6858,439 @@
       <c r="L5" s="28"/>
       <c r="M5" s="28"/>
     </row>
-    <row r="6">
-      <c r="A6" s="30" t="s">
+    <row r="6" ht="51.75" customHeight="1">
+      <c r="A6" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="32" t="s">
         <v>161</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="30" t="s">
+      <c r="I6" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="J6" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="30" t="s">
+      <c r="K6" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="30" t="s">
+      <c r="L6" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="30" t="s">
-        <v>228</v>
+      <c r="M6" s="32" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="B7" s="31">
-        <v>35.0</v>
-      </c>
-      <c r="C7" s="31">
+      <c r="A7" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="23">
+        <v>20.0</v>
+      </c>
+      <c r="C7" s="33">
+        <f t="shared" ref="C7:C15" si="1">B7*1.25</f>
+        <v>25</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="23">
+        <v>40.0</v>
+      </c>
+      <c r="F7" s="23">
+        <v>5.0</v>
+      </c>
+      <c r="G7" s="23">
+        <v>30.0</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="23">
+        <v>13.0</v>
+      </c>
+      <c r="C8" s="33">
+        <f t="shared" si="1"/>
+        <v>16.25</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="23">
+        <v>41.0</v>
+      </c>
+      <c r="F8" s="23">
+        <v>5.0</v>
+      </c>
+      <c r="G8" s="23">
+        <v>30.0</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>313</v>
+      </c>
+      <c r="L8" s="23" t="s">
+        <v>314</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="23">
+        <v>12.0</v>
+      </c>
+      <c r="C9" s="33">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="23">
+        <v>42.0</v>
+      </c>
+      <c r="F9" s="23">
+        <v>5.0</v>
+      </c>
+      <c r="G9" s="23">
+        <v>30.0</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>316</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>317</v>
+      </c>
+      <c r="L9" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="23">
+        <v>11.0</v>
+      </c>
+      <c r="C10" s="33">
+        <f t="shared" si="1"/>
+        <v>13.75</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" s="23">
+        <v>43.0</v>
+      </c>
+      <c r="F10" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="G10" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="L10" s="23" t="s">
+        <v>322</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="23">
+        <v>10.0</v>
+      </c>
+      <c r="C11" s="33">
+        <f t="shared" si="1"/>
+        <v>12.5</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="23">
         <v>44.0</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="E7" s="31">
-        <v>40.0</v>
-      </c>
-      <c r="F7" s="31">
+      <c r="F11" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="G11" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>324</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>325</v>
+      </c>
+      <c r="L11" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="M11" s="23" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="23">
+        <v>9.0</v>
+      </c>
+      <c r="C12" s="33">
+        <f t="shared" si="1"/>
+        <v>11.25</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" s="23">
+        <v>45.0</v>
+      </c>
+      <c r="F12" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="G12" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>328</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>329</v>
+      </c>
+      <c r="L12" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="M12" s="23" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" s="23">
+        <v>8.0</v>
+      </c>
+      <c r="C13" s="33">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="E13" s="23">
+        <v>46.0</v>
+      </c>
+      <c r="F13" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="G13" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="B14" s="23">
+        <v>7.0</v>
+      </c>
+      <c r="C14" s="33">
+        <f t="shared" si="1"/>
+        <v>8.75</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E14" s="23">
+        <v>99.0</v>
+      </c>
+      <c r="F14" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="G14" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>336</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="L14" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B15" s="23">
         <v>6.0</v>
       </c>
-      <c r="G7" s="31">
-        <v>62.0</v>
-      </c>
-      <c r="H7" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="I7" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="J7" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="K7" s="31" t="s">
-        <v>113</v>
-      </c>
-      <c r="L7" s="31" t="s">
-        <v>306</v>
-      </c>
-      <c r="M7" s="31" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="B8" s="31">
-        <v>18.0</v>
-      </c>
-      <c r="C8" s="31">
-        <v>23.0</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="E8" s="31">
-        <v>41.0</v>
-      </c>
-      <c r="F8" s="31">
-        <v>5.0</v>
-      </c>
-      <c r="G8" s="31">
-        <v>30.0</v>
-      </c>
-      <c r="H8" s="31" t="s">
-        <v>205</v>
-      </c>
-      <c r="I8" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="J8" s="31" t="s">
-        <v>308</v>
-      </c>
-      <c r="K8" s="31" t="s">
-        <v>309</v>
-      </c>
-      <c r="L8" s="31" t="s">
-        <v>310</v>
-      </c>
-      <c r="M8" s="31" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="B9" s="31">
-        <v>10.0</v>
-      </c>
-      <c r="C9" s="31">
-        <v>13.0</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="E9" s="31">
-        <v>42.0</v>
-      </c>
-      <c r="F9" s="31">
+      <c r="C15" s="33">
+        <f t="shared" si="1"/>
+        <v>7.5</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="E15" s="23">
+        <v>47.0</v>
+      </c>
+      <c r="F15" s="23">
         <v>4.0</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G15" s="23">
         <v>14.0</v>
       </c>
-      <c r="H9" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I9" s="31" t="s">
+      <c r="H15" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="J9" s="31" t="s">
-        <v>312</v>
-      </c>
-      <c r="K9" s="31" t="s">
-        <v>313</v>
-      </c>
-      <c r="L9" s="31" t="s">
-        <v>314</v>
-      </c>
-      <c r="M9" s="31" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="31">
-        <v>8.0</v>
-      </c>
-      <c r="C10" s="31">
-        <v>10.0</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="31">
-        <v>43.0</v>
-      </c>
-      <c r="F10" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="G10" s="31">
-        <v>14.0</v>
-      </c>
-      <c r="H10" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I10" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="J10" s="31" t="s">
-        <v>316</v>
-      </c>
-      <c r="K10" s="31" t="s">
-        <v>317</v>
-      </c>
-      <c r="L10" s="31" t="s">
-        <v>318</v>
-      </c>
-      <c r="M10" s="31" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="B11" s="31">
-        <v>7.0</v>
-      </c>
-      <c r="C11" s="31">
-        <v>9.0</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" s="31">
-        <v>44.0</v>
-      </c>
-      <c r="F11" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="G11" s="31">
-        <v>14.0</v>
-      </c>
-      <c r="H11" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="J11" s="31" t="s">
-        <v>320</v>
-      </c>
-      <c r="K11" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="L11" s="31" t="s">
-        <v>322</v>
-      </c>
-      <c r="M11" s="31" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="B12" s="31">
-        <v>6.0</v>
-      </c>
-      <c r="C12" s="31">
-        <v>8.0</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="E12" s="31">
-        <v>45.0</v>
-      </c>
-      <c r="F12" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="G12" s="31">
-        <v>14.0</v>
-      </c>
-      <c r="H12" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I12" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="J12" s="31" t="s">
-        <v>324</v>
-      </c>
-      <c r="K12" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="L12" s="31" t="s">
-        <v>326</v>
-      </c>
-      <c r="M12" s="31" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13" s="31">
-        <v>5.0</v>
-      </c>
-      <c r="C13" s="31">
-        <v>7.0</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="E13" s="31">
-        <v>46.0</v>
-      </c>
-      <c r="F13" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="G13" s="31">
-        <v>14.0</v>
-      </c>
-      <c r="H13" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I13" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="J13" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="K13" s="31" t="s">
-        <v>329</v>
-      </c>
-      <c r="L13" s="31" t="s">
-        <v>330</v>
-      </c>
-      <c r="M13" s="31" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="B14" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="C14" s="31">
-        <v>5.0</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="E14" s="31">
-        <v>99.0</v>
-      </c>
-      <c r="F14" s="31">
-        <v>3.0</v>
-      </c>
-      <c r="G14" s="31">
-        <v>6.0</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="I14" s="31" t="s">
-        <v>256</v>
-      </c>
-      <c r="J14" s="31" t="s">
-        <v>332</v>
-      </c>
-      <c r="K14" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="L14" s="31" t="s">
-        <v>334</v>
-      </c>
-      <c r="M14" s="31" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="31" t="s">
-        <v>217</v>
-      </c>
-      <c r="B15" s="31">
-        <v>3.0</v>
-      </c>
-      <c r="C15" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="E15" s="31">
-        <v>47.0</v>
-      </c>
-      <c r="F15" s="31">
-        <v>3.0</v>
-      </c>
-      <c r="G15" s="31">
-        <v>6.0</v>
-      </c>
-      <c r="H15" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="I15" s="31" t="s">
-        <v>256</v>
-      </c>
-      <c r="J15" s="31" t="s">
-        <v>336</v>
-      </c>
-      <c r="K15" s="31" t="s">
-        <v>337</v>
-      </c>
-      <c r="L15" s="31" t="s">
-        <v>338</v>
-      </c>
-      <c r="M15" s="31" t="s">
-        <v>339</v>
+      <c r="I15" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="L15" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="B16" s="32">
+      <c r="A16" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="B16" s="29">
         <v>96.0</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="29">
         <v>123.0</v>
       </c>
       <c r="D16" s="28"/>
       <c r="E16" s="28"/>
       <c r="F16" s="28"/>
-      <c r="G16" s="32">
+      <c r="G16" s="29">
         <v>174.0</v>
       </c>
       <c r="H16" s="28"/>
@@ -7284,15 +7316,15 @@
       <c r="M17" s="28"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>340</v>
-      </c>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
+      <c r="A18" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="18"/>
       <c r="F18" s="28"/>
       <c r="G18" s="28"/>
       <c r="H18" s="28"/>
@@ -7319,7 +7351,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B18:E18"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -7334,7 +7366,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="28.88"/>
     <col customWidth="1" min="6" max="6" width="14.25"/>
-    <col customWidth="1" min="7" max="7" width="15.5"/>
+    <col customWidth="1" min="7" max="7" width="17.13"/>
     <col customWidth="1" min="9" max="10" width="16.88"/>
     <col customWidth="1" min="11" max="11" width="17.13"/>
     <col customWidth="1" min="12" max="12" width="16.88"/>
@@ -7342,14 +7374,14 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="B1" s="26" t="s">
-        <v>341</v>
-      </c>
-      <c r="C1" s="27"/>
-      <c r="D1" s="18"/>
+      <c r="B1" s="25" t="s">
+        <v>345</v>
+      </c>
+      <c r="C1" s="26"/>
+      <c r="D1" s="27"/>
       <c r="E1" s="28"/>
       <c r="F1" s="28"/>
       <c r="G1" s="28"/>
@@ -7362,10 +7394,10 @@
       <c r="N1" s="28"/>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="25" t="s">
         <v>122</v>
       </c>
       <c r="C2" s="28"/>
@@ -7382,11 +7414,11 @@
       <c r="N2" s="28"/>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="s">
+      <c r="A3" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="B3" s="29" t="s">
-        <v>342</v>
+      <c r="B3" s="25" t="s">
+        <v>346</v>
       </c>
       <c r="C3" s="28"/>
       <c r="D3" s="28"/>
@@ -7434,439 +7466,439 @@
       <c r="N5" s="28"/>
     </row>
     <row r="6">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="36" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="36" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="36" t="s">
         <v>157</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="36" t="s">
         <v>158</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="36" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="36" t="s">
         <v>160</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="36" t="s">
         <v>161</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="30" t="s">
+      <c r="I6" s="36" t="s">
         <v>162</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="J6" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="30" t="s">
+      <c r="K6" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="30" t="s">
+      <c r="L6" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="30" t="s">
-        <v>228</v>
+      <c r="M6" s="36" t="s">
+        <v>163</v>
       </c>
       <c r="N6" s="28"/>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="B7" s="31">
+      <c r="A7" s="23" t="s">
+        <v>164</v>
+      </c>
+      <c r="B7" s="23">
         <v>36.0</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="23">
         <v>45.0</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>164</v>
-      </c>
-      <c r="E7" s="31">
+      <c r="D7" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="23">
         <v>30.0</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="23">
         <v>6.0</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="23">
         <v>62.0</v>
       </c>
-      <c r="H7" s="31" t="s">
+      <c r="H7" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="K7" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="L7" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="M7" s="23" t="s">
+        <v>348</v>
+      </c>
+      <c r="N7" s="28"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="23">
+        <v>20.0</v>
+      </c>
+      <c r="C8" s="23">
+        <v>25.0</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="23">
+        <v>10.0</v>
+      </c>
+      <c r="F8" s="23">
+        <v>5.0</v>
+      </c>
+      <c r="G8" s="23">
+        <v>30.0</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>349</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>350</v>
+      </c>
+      <c r="L8" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="N8" s="28"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="23">
+        <v>11.0</v>
+      </c>
+      <c r="C9" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="D9" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="I7" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="J7" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="K7" s="31" t="s">
-        <v>119</v>
-      </c>
-      <c r="L7" s="31" t="s">
-        <v>343</v>
-      </c>
-      <c r="M7" s="31" t="s">
-        <v>344</v>
-      </c>
-      <c r="N7" s="28"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="B8" s="31">
+      <c r="E9" s="23">
+        <v>40.0</v>
+      </c>
+      <c r="F9" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="G9" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>353</v>
+      </c>
+      <c r="K9" s="23" t="s">
+        <v>354</v>
+      </c>
+      <c r="L9" s="23" t="s">
+        <v>355</v>
+      </c>
+      <c r="M9" s="23" t="s">
+        <v>356</v>
+      </c>
+      <c r="N9" s="28"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="23">
+        <v>9.0</v>
+      </c>
+      <c r="C10" s="23">
+        <v>12.0</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" s="23">
+        <v>80.0</v>
+      </c>
+      <c r="F10" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="G10" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>357</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="L10" s="23" t="s">
+        <v>359</v>
+      </c>
+      <c r="M10" s="23" t="s">
+        <v>360</v>
+      </c>
+      <c r="N10" s="28"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="23">
+        <v>8.0</v>
+      </c>
+      <c r="C11" s="23">
+        <v>10.0</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="23">
+        <v>50.0</v>
+      </c>
+      <c r="F11" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="G11" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>361</v>
+      </c>
+      <c r="K11" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="L11" s="23" t="s">
+        <v>363</v>
+      </c>
+      <c r="M11" s="23" t="s">
+        <v>364</v>
+      </c>
+      <c r="N11" s="28"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="23">
+        <v>7.0</v>
+      </c>
+      <c r="C12" s="23">
+        <v>9.0</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" s="23">
         <v>20.0</v>
       </c>
-      <c r="C8" s="31">
-        <v>25.0</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>170</v>
-      </c>
-      <c r="E8" s="31">
-        <v>10.0</v>
-      </c>
-      <c r="F8" s="31">
+      <c r="F12" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="G12" s="23">
+        <v>14.0</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="K12" s="23" t="s">
+        <v>366</v>
+      </c>
+      <c r="L12" s="23" t="s">
+        <v>367</v>
+      </c>
+      <c r="M12" s="23" t="s">
+        <v>368</v>
+      </c>
+      <c r="N12" s="28"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" s="23">
         <v>5.0</v>
       </c>
-      <c r="G8" s="31">
-        <v>30.0</v>
-      </c>
-      <c r="H8" s="31" t="s">
+      <c r="C13" s="23">
+        <v>7.0</v>
+      </c>
+      <c r="D13" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="I8" s="31" t="s">
-        <v>206</v>
-      </c>
-      <c r="J8" s="31" t="s">
-        <v>345</v>
-      </c>
-      <c r="K8" s="31" t="s">
-        <v>346</v>
-      </c>
-      <c r="L8" s="31" t="s">
-        <v>347</v>
-      </c>
-      <c r="M8" s="31" t="s">
-        <v>348</v>
-      </c>
-      <c r="N8" s="28"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="31" t="s">
-        <v>177</v>
-      </c>
-      <c r="B9" s="31">
-        <v>11.0</v>
-      </c>
-      <c r="C9" s="31">
+      <c r="E13" s="23">
+        <v>70.0</v>
+      </c>
+      <c r="F13" s="23">
+        <v>4.0</v>
+      </c>
+      <c r="G13" s="23">
         <v>14.0</v>
       </c>
-      <c r="D9" s="31" t="s">
-        <v>178</v>
-      </c>
-      <c r="E9" s="31">
-        <v>40.0</v>
-      </c>
-      <c r="F9" s="31">
+      <c r="H13" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>369</v>
+      </c>
+      <c r="K13" s="23" t="s">
+        <v>370</v>
+      </c>
+      <c r="L13" s="23" t="s">
+        <v>371</v>
+      </c>
+      <c r="M13" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="N13" s="28"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="B14" s="23">
+        <v>5.0</v>
+      </c>
+      <c r="C14" s="23">
+        <v>7.0</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="E14" s="23">
+        <v>60.0</v>
+      </c>
+      <c r="F14" s="23">
         <v>4.0</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G14" s="23">
         <v>14.0</v>
       </c>
-      <c r="H9" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I9" s="31" t="s">
+      <c r="H14" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="J9" s="31" t="s">
-        <v>349</v>
-      </c>
-      <c r="K9" s="31" t="s">
-        <v>350</v>
-      </c>
-      <c r="L9" s="31" t="s">
-        <v>351</v>
-      </c>
-      <c r="M9" s="31" t="s">
-        <v>352</v>
-      </c>
-      <c r="N9" s="28"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="31" t="s">
-        <v>185</v>
-      </c>
-      <c r="B10" s="31">
-        <v>9.0</v>
-      </c>
-      <c r="C10" s="31">
-        <v>12.0</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="E10" s="31">
-        <v>80.0</v>
-      </c>
-      <c r="F10" s="31">
+      <c r="I14" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>373</v>
+      </c>
+      <c r="K14" s="23" t="s">
+        <v>374</v>
+      </c>
+      <c r="L14" s="23" t="s">
+        <v>375</v>
+      </c>
+      <c r="M14" s="23" t="s">
+        <v>376</v>
+      </c>
+      <c r="N14" s="28"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="B15" s="23">
         <v>4.0</v>
       </c>
-      <c r="G10" s="31">
-        <v>14.0</v>
-      </c>
-      <c r="H10" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I10" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="J10" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="K10" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="L10" s="31" t="s">
-        <v>355</v>
-      </c>
-      <c r="M10" s="31" t="s">
-        <v>356</v>
-      </c>
-      <c r="N10" s="28"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="31" t="s">
-        <v>191</v>
-      </c>
-      <c r="B11" s="31">
-        <v>8.0</v>
-      </c>
-      <c r="C11" s="31">
-        <v>10.0</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="E11" s="31">
-        <v>50.0</v>
-      </c>
-      <c r="F11" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="G11" s="31">
-        <v>14.0</v>
-      </c>
-      <c r="H11" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I11" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="J11" s="31" t="s">
-        <v>357</v>
-      </c>
-      <c r="K11" s="31" t="s">
-        <v>358</v>
-      </c>
-      <c r="L11" s="31" t="s">
-        <v>359</v>
-      </c>
-      <c r="M11" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="N11" s="28"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="B12" s="31">
-        <v>7.0</v>
-      </c>
-      <c r="C12" s="31">
-        <v>9.0</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>198</v>
-      </c>
-      <c r="E12" s="31">
-        <v>20.0</v>
-      </c>
-      <c r="F12" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="G12" s="31">
-        <v>14.0</v>
-      </c>
-      <c r="H12" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I12" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="J12" s="31" t="s">
-        <v>361</v>
-      </c>
-      <c r="K12" s="31" t="s">
-        <v>362</v>
-      </c>
-      <c r="L12" s="31" t="s">
-        <v>363</v>
-      </c>
-      <c r="M12" s="31" t="s">
-        <v>364</v>
-      </c>
-      <c r="N12" s="28"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="31" t="s">
-        <v>203</v>
-      </c>
-      <c r="B13" s="31">
+      <c r="C15" s="23">
         <v>5.0</v>
       </c>
-      <c r="C13" s="31">
-        <v>7.0</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>204</v>
-      </c>
-      <c r="E13" s="31">
-        <v>70.0</v>
-      </c>
-      <c r="F13" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="G13" s="31">
-        <v>14.0</v>
-      </c>
-      <c r="H13" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I13" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="J13" s="31" t="s">
-        <v>365</v>
-      </c>
-      <c r="K13" s="31" t="s">
-        <v>366</v>
-      </c>
-      <c r="L13" s="31" t="s">
-        <v>367</v>
-      </c>
-      <c r="M13" s="31" t="s">
-        <v>368</v>
-      </c>
-      <c r="N13" s="28"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="31" t="s">
-        <v>217</v>
-      </c>
-      <c r="B14" s="31">
-        <v>5.0</v>
-      </c>
-      <c r="C14" s="31">
-        <v>7.0</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="E14" s="31">
-        <v>60.0</v>
-      </c>
-      <c r="F14" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="G14" s="31">
-        <v>14.0</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>219</v>
-      </c>
-      <c r="I14" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="J14" s="31" t="s">
-        <v>369</v>
-      </c>
-      <c r="K14" s="31" t="s">
-        <v>370</v>
-      </c>
-      <c r="L14" s="31" t="s">
-        <v>371</v>
-      </c>
-      <c r="M14" s="31" t="s">
-        <v>372</v>
-      </c>
-      <c r="N14" s="28"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="B15" s="31">
-        <v>4.0</v>
-      </c>
-      <c r="C15" s="31">
-        <v>5.0</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="E15" s="31">
+      <c r="D15" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="E15" s="23">
         <v>99.0</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="23">
         <v>3.0</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="23">
         <v>6.0</v>
       </c>
-      <c r="H15" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="I15" s="31" t="s">
-        <v>256</v>
-      </c>
-      <c r="J15" s="31" t="s">
-        <v>373</v>
-      </c>
-      <c r="K15" s="31" t="s">
-        <v>374</v>
-      </c>
-      <c r="L15" s="31" t="s">
-        <v>375</v>
-      </c>
-      <c r="M15" s="31" t="s">
-        <v>376</v>
+      <c r="H15" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>377</v>
+      </c>
+      <c r="K15" s="23" t="s">
+        <v>378</v>
+      </c>
+      <c r="L15" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="M15" s="23" t="s">
+        <v>380</v>
       </c>
       <c r="N15" s="28"/>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="B16" s="32">
+      <c r="A16" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="B16" s="29">
         <v>105.0</v>
       </c>
-      <c r="C16" s="32">
+      <c r="C16" s="29">
         <v>134.0</v>
       </c>
       <c r="D16" s="28"/>
       <c r="E16" s="28"/>
       <c r="F16" s="28"/>
-      <c r="G16" s="32">
+      <c r="G16" s="29">
         <v>182.0</v>
       </c>
       <c r="H16" s="28"/>
@@ -7894,11 +7926,11 @@
       <c r="N17" s="28"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="s">
-        <v>265</v>
-      </c>
-      <c r="B18" s="29" t="s">
-        <v>377</v>
+      <c r="A18" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>381</v>
       </c>
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
@@ -7925,7 +7957,9 @@
       <c r="I19" s="28"/>
       <c r="J19" s="28"/>
       <c r="K19" s="28"/>
-      <c r="L19" s="28"/>
+      <c r="L19" s="23" t="s">
+        <v>382</v>
+      </c>
       <c r="M19" s="28"/>
       <c r="N19" s="28"/>
     </row>
@@ -7939,9 +7973,13 @@
       <c r="G20" s="28"/>
       <c r="H20" s="28"/>
       <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
+      <c r="J20" s="23" t="s">
+        <v>358</v>
+      </c>
       <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
+      <c r="L20" s="23" t="s">
+        <v>383</v>
+      </c>
       <c r="M20" s="28"/>
       <c r="N20" s="28"/>
     </row>
@@ -8026,9 +8064,6 @@
       <c r="N25" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B1:D1"/>
-  </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/excel-final/Esquema de Direccionamiento IP.xlsx
+++ b/excel-final/Esquema de Direccionamiento IP.xlsx
@@ -655,16 +655,40 @@
     <t>10.192.42.159</t>
   </si>
   <si>
+    <t>Servidores</t>
+  </si>
+  <si>
+    <t>VLSER</t>
+  </si>
+  <si>
+    <t>/28</t>
+  </si>
+  <si>
+    <t>255.255.255.240</t>
+  </si>
+  <si>
+    <t>10.192.42.160</t>
+  </si>
+  <si>
+    <t>10.192.42.161</t>
+  </si>
+  <si>
+    <t>10.192.42.174</t>
+  </si>
+  <si>
+    <t>10.192.42.175</t>
+  </si>
+  <si>
     <t>Nativa</t>
   </si>
   <si>
     <t>VLNAT</t>
   </si>
   <si>
-    <t>10.192.42.160</t>
-  </si>
-  <si>
-    <t>10.192.42.161</t>
+    <t>10.192.42.176</t>
+  </si>
+  <si>
+    <t>10.192.42.177</t>
   </si>
   <si>
     <t>10.192.42.190</t>
@@ -673,34 +697,10 @@
     <t>10.192.42.191</t>
   </si>
   <si>
-    <t>Servidores</t>
-  </si>
-  <si>
-    <t>VLSER</t>
-  </si>
-  <si>
-    <t>/28</t>
-  </si>
-  <si>
-    <t>255.255.255.240</t>
-  </si>
-  <si>
-    <t>10.192.42.192</t>
-  </si>
-  <si>
-    <t>10.192.42.193</t>
-  </si>
-  <si>
-    <t>10.192.42.206</t>
-  </si>
-  <si>
-    <t>10.192.42.207</t>
-  </si>
-  <si>
     <t>Nota:</t>
   </si>
   <si>
-    <t>Los 452 hosts corresponden a los requerimientos indicados en el caso para Lima. Adicionalmente, se dimensionan 15 hosts para la VLAN Nativa/Gestión, de acuerdo con la cantidad de dispositivos de red considerados en la solución, obteniendo un total de 467 hosts dimensionados.</t>
+    <t>Los 452 hosts corresponden a los requerimientos indicados en el caso para Lima. Adicionalmente, se dimensionan 9 hosts actuales para la VLAN Nativa/Gestión según los dispositivos de red usados; con crecimiento del 25% se consideran 12 hosts. Total actual dimensionado: 461 hosts.</t>
   </si>
   <si>
     <t>Validacion:</t>
@@ -904,130 +904,130 @@
     <t>10.192.49.31</t>
   </si>
   <si>
+    <t>10.192.49.32</t>
+  </si>
+  <si>
+    <t>10.192.49.33</t>
+  </si>
+  <si>
+    <t>10.192.49.46</t>
+  </si>
+  <si>
+    <t>10.192.49.47</t>
+  </si>
+  <si>
+    <t>10.192.49.48</t>
+  </si>
+  <si>
+    <t>10.192.49.49</t>
+  </si>
+  <si>
+    <t>10.192.49.62</t>
+  </si>
+  <si>
+    <t>10.192.49.63</t>
+  </si>
+  <si>
+    <t>10.192.49.64</t>
+  </si>
+  <si>
+    <t>10.192.49.65</t>
+  </si>
+  <si>
+    <t>10.192.49.78</t>
+  </si>
+  <si>
+    <t>10.192.49.79</t>
+  </si>
+  <si>
+    <t>Todas las VLAN quedan dentro de 10.192.48.0/22 y no se solapan.</t>
+  </si>
+  <si>
+    <t>Portalanza Romero, Aurora de Libertad</t>
+  </si>
+  <si>
+    <t>10.192.52.0/22</t>
+  </si>
+  <si>
+    <t>10.192.52.30</t>
+  </si>
+  <si>
+    <t>10.192.52.31</t>
+  </si>
+  <si>
+    <t>10.192.52.32</t>
+  </si>
+  <si>
+    <t>10.192.52.33</t>
+  </si>
+  <si>
+    <t>10.192.52.62</t>
+  </si>
+  <si>
+    <t>10.192.52.63</t>
+  </si>
+  <si>
+    <t>10.192.52.64</t>
+  </si>
+  <si>
+    <t>10.192.52.65</t>
+  </si>
+  <si>
+    <t>10.192.52.94</t>
+  </si>
+  <si>
+    <t>10.192.52.95</t>
+  </si>
+  <si>
+    <t>10.192.52.96</t>
+  </si>
+  <si>
+    <t>10.192.52.97</t>
+  </si>
+  <si>
+    <t>10.192.52.110</t>
+  </si>
+  <si>
+    <t>10.192.52.111</t>
+  </si>
+  <si>
+    <t>10.192.52.112</t>
+  </si>
+  <si>
+    <t>10.192.52.113</t>
+  </si>
+  <si>
+    <t>10.192.52.126</t>
+  </si>
+  <si>
+    <t>10.192.52.127</t>
+  </si>
+  <si>
+    <t>10.192.52.128</t>
+  </si>
+  <si>
+    <t>10.192.52.129</t>
+  </si>
+  <si>
+    <t>10.192.52.142</t>
+  </si>
+  <si>
+    <t>10.192.52.143</t>
+  </si>
+  <si>
+    <t>10.192.52.144</t>
+  </si>
+  <si>
+    <t>10.192.52.145</t>
+  </si>
+  <si>
+    <t>10.192.52.158</t>
+  </si>
+  <si>
+    <t>10.192.52.159</t>
+  </si>
+  <si>
     <t>Nativa/Gestion</t>
-  </si>
-  <si>
-    <t>10.192.49.32</t>
-  </si>
-  <si>
-    <t>10.192.49.33</t>
-  </si>
-  <si>
-    <t>10.192.49.46</t>
-  </si>
-  <si>
-    <t>10.192.49.47</t>
-  </si>
-  <si>
-    <t>10.192.49.48</t>
-  </si>
-  <si>
-    <t>10.192.49.49</t>
-  </si>
-  <si>
-    <t>10.192.49.62</t>
-  </si>
-  <si>
-    <t>10.192.49.63</t>
-  </si>
-  <si>
-    <t>10.192.49.64</t>
-  </si>
-  <si>
-    <t>10.192.49.65</t>
-  </si>
-  <si>
-    <t>10.192.49.78</t>
-  </si>
-  <si>
-    <t>10.192.49.79</t>
-  </si>
-  <si>
-    <t>Todas las VLAN quedan dentro de 10.192.48.0/22 y no se solapan.</t>
-  </si>
-  <si>
-    <t>Portalanza Romero, Aurora de Libertad</t>
-  </si>
-  <si>
-    <t>10.192.52.0/22</t>
-  </si>
-  <si>
-    <t>10.192.52.30</t>
-  </si>
-  <si>
-    <t>10.192.52.31</t>
-  </si>
-  <si>
-    <t>10.192.52.32</t>
-  </si>
-  <si>
-    <t>10.192.52.33</t>
-  </si>
-  <si>
-    <t>10.192.52.62</t>
-  </si>
-  <si>
-    <t>10.192.52.63</t>
-  </si>
-  <si>
-    <t>10.192.52.64</t>
-  </si>
-  <si>
-    <t>10.192.52.65</t>
-  </si>
-  <si>
-    <t>10.192.52.94</t>
-  </si>
-  <si>
-    <t>10.192.52.95</t>
-  </si>
-  <si>
-    <t>10.192.52.96</t>
-  </si>
-  <si>
-    <t>10.192.52.97</t>
-  </si>
-  <si>
-    <t>10.192.52.110</t>
-  </si>
-  <si>
-    <t>10.192.52.111</t>
-  </si>
-  <si>
-    <t>10.192.52.112</t>
-  </si>
-  <si>
-    <t>10.192.52.113</t>
-  </si>
-  <si>
-    <t>10.192.52.126</t>
-  </si>
-  <si>
-    <t>10.192.52.127</t>
-  </si>
-  <si>
-    <t>10.192.52.128</t>
-  </si>
-  <si>
-    <t>10.192.52.129</t>
-  </si>
-  <si>
-    <t>10.192.52.142</t>
-  </si>
-  <si>
-    <t>10.192.52.143</t>
-  </si>
-  <si>
-    <t>10.192.52.144</t>
-  </si>
-  <si>
-    <t>10.192.52.145</t>
-  </si>
-  <si>
-    <t>10.192.52.158</t>
-  </si>
-  <si>
-    <t>10.192.52.159</t>
   </si>
   <si>
     <t>10.192.52.160</t>
@@ -1251,7 +1251,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="15">
     <border/>
     <border>
       <left style="thin">
@@ -1367,14 +1367,6 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -1452,7 +1444,7 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1520,20 +1512,20 @@
     <xf borderId="1" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    </xf>
     <xf borderId="2" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="13" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf borderId="14" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="14" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="15" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf borderId="14" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3117,57 +3109,57 @@
         <v>212</v>
       </c>
       <c r="B14" s="23">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="C14" s="23">
-        <v>19.0</v>
+        <v>13.0</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>213</v>
       </c>
       <c r="E14" s="23">
-        <v>99.0</v>
+        <v>17.0</v>
       </c>
       <c r="F14" s="23">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G14" s="23">
-        <v>30.0</v>
+        <v>14.0</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K14" s="23" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="M14" s="23" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="23" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B15" s="23">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="C15" s="23">
-        <v>13.0</v>
+        <v>12.0</v>
       </c>
       <c r="D15" s="23" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E15" s="23">
-        <v>17.0</v>
+        <v>99.0</v>
       </c>
       <c r="F15" s="23">
         <v>4.0</v>
@@ -3176,10 +3168,10 @@
         <v>14.0</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J15" s="23" t="s">
         <v>222</v>
@@ -3197,12 +3189,12 @@
     <row r="16">
       <c r="B16" s="24">
         <f>SUM(B7:B15)</f>
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="24">
-        <f>B16-15</f>
+        <f>B16-9</f>
         <v>452</v>
       </c>
     </row>
@@ -3541,10 +3533,10 @@
         <v>14.0</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J10" s="38" t="s">
         <v>243</v>
@@ -3582,10 +3574,10 @@
         <v>14.0</v>
       </c>
       <c r="H11" s="38" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I11" s="38" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J11" s="38" t="s">
         <v>247</v>
@@ -3623,10 +3615,10 @@
         <v>14.0</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J12" s="38" t="s">
         <v>252</v>
@@ -3652,7 +3644,7 @@
         <v>12.0</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="E13" s="38">
         <v>99.0</v>
@@ -3664,10 +3656,10 @@
         <v>14.0</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I13" s="38" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J13" s="38" t="s">
         <v>257</v>
@@ -3705,10 +3697,10 @@
         <v>14.0</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J14" s="38" t="s">
         <v>261</v>
@@ -3725,7 +3717,7 @@
     </row>
     <row r="15">
       <c r="A15" s="40" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B15" s="41">
         <v>5.0</v>
@@ -3734,7 +3726,7 @@
         <v>7.0</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="E15" s="41">
         <v>37.0</v>
@@ -3746,10 +3738,10 @@
         <v>14.0</v>
       </c>
       <c r="H15" s="41" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I15" s="41" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J15" s="41" t="s">
         <v>265</v>
@@ -4821,43 +4813,43 @@
       <c r="EU6" s="33"/>
     </row>
     <row r="7" ht="24.75" customHeight="1">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="B7" s="23">
-        <v>78.0</v>
-      </c>
-      <c r="C7" s="23">
-        <v>98.0</v>
-      </c>
-      <c r="D7" s="23" t="s">
+      <c r="B7" s="35">
+        <v>79.0</v>
+      </c>
+      <c r="C7" s="35">
+        <v>99.0</v>
+      </c>
+      <c r="D7" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="35">
         <v>20.0</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="35">
         <v>7.0</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="35">
         <v>126.0</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="35" t="s">
         <v>172</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="I7" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="J7" s="23" t="s">
+      <c r="J7" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="K7" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="L7" s="23" t="s">
+      <c r="L7" s="35" t="s">
         <v>273</v>
       </c>
-      <c r="M7" s="23" t="s">
+      <c r="M7" s="36" t="s">
         <v>274</v>
       </c>
       <c r="N7" s="33"/>
@@ -5000,43 +4992,43 @@
       <c r="EU7" s="33"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
-      <c r="A8" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="B8" s="23">
+      <c r="A8" s="37" t="s">
+        <v>234</v>
+      </c>
+      <c r="B8" s="38">
         <v>40.0</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="38">
         <v>50.0</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="38">
         <v>21.0</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="38">
         <v>6.0</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="38">
         <v>62.0</v>
       </c>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="I8" s="23" t="s">
+      <c r="I8" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="J8" s="23" t="s">
+      <c r="J8" s="38" t="s">
         <v>275</v>
       </c>
-      <c r="K8" s="23" t="s">
+      <c r="K8" s="38" t="s">
         <v>276</v>
       </c>
-      <c r="L8" s="23" t="s">
+      <c r="L8" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="M8" s="23" t="s">
+      <c r="M8" s="39" t="s">
         <v>278</v>
       </c>
       <c r="N8" s="33"/>
@@ -5179,43 +5171,43 @@
       <c r="EU8" s="33"/>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="37" t="s">
         <v>178</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="38">
         <v>16.0</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="38">
         <v>20.0</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="38">
         <v>22.0</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="38">
         <v>5.0</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="38">
         <v>30.0</v>
       </c>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="I9" s="23" t="s">
+      <c r="I9" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="J9" s="23" t="s">
+      <c r="J9" s="38" t="s">
         <v>279</v>
       </c>
-      <c r="K9" s="23" t="s">
+      <c r="K9" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="L9" s="23" t="s">
+      <c r="L9" s="38" t="s">
         <v>281</v>
       </c>
-      <c r="M9" s="23" t="s">
+      <c r="M9" s="39" t="s">
         <v>282</v>
       </c>
       <c r="N9" s="33"/>
@@ -5358,43 +5350,43 @@
       <c r="EU9" s="33"/>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="37" t="s">
         <v>186</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="38">
         <v>12.0</v>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="38">
         <v>15.0</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="E10" s="23">
+      <c r="E10" s="38">
         <v>23.0</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="38">
         <v>5.0</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="38">
         <v>30.0</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="38" t="s">
         <v>206</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="J10" s="23" t="s">
+      <c r="J10" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="K10" s="23" t="s">
+      <c r="K10" s="38" t="s">
         <v>284</v>
       </c>
-      <c r="L10" s="23" t="s">
+      <c r="L10" s="38" t="s">
         <v>285</v>
       </c>
-      <c r="M10" s="23" t="s">
+      <c r="M10" s="39" t="s">
         <v>286</v>
       </c>
       <c r="N10" s="33"/>
@@ -5537,43 +5529,43 @@
       <c r="EU10" s="33"/>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="38">
         <v>11.0</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="38">
         <v>14.0</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="38">
         <v>24.0</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="38">
         <v>4.0</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="38">
         <v>14.0</v>
       </c>
-      <c r="H11" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="J11" s="23" t="s">
+      <c r="H11" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="I11" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="J11" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="K11" s="23" t="s">
+      <c r="K11" s="38" t="s">
         <v>288</v>
       </c>
-      <c r="L11" s="23" t="s">
+      <c r="L11" s="38" t="s">
         <v>289</v>
       </c>
-      <c r="M11" s="23" t="s">
+      <c r="M11" s="39" t="s">
         <v>290</v>
       </c>
       <c r="N11" s="33"/>
@@ -5716,43 +5708,43 @@
       <c r="EU11" s="33"/>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="B12" s="23">
+      <c r="A12" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="B12" s="38">
         <v>10.0</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="38">
         <v>13.0</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="E12" s="23">
+      <c r="E12" s="38">
         <v>25.0</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="38">
         <v>4.0</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="38">
         <v>14.0</v>
       </c>
-      <c r="H12" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="I12" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="J12" s="23" t="s">
+      <c r="H12" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="I12" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="J12" s="38" t="s">
         <v>291</v>
       </c>
-      <c r="K12" s="23" t="s">
+      <c r="K12" s="38" t="s">
         <v>292</v>
       </c>
-      <c r="L12" s="23" t="s">
+      <c r="L12" s="38" t="s">
         <v>293</v>
       </c>
-      <c r="M12" s="23" t="s">
+      <c r="M12" s="39" t="s">
         <v>294</v>
       </c>
       <c r="N12" s="33"/>
@@ -5895,44 +5887,44 @@
       <c r="EU12" s="33"/>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="B13" s="38">
+        <v>9.0</v>
+      </c>
+      <c r="C13" s="38">
+        <v>12.0</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="E13" s="38">
+        <v>99.0</v>
+      </c>
+      <c r="F13" s="38">
+        <v>4.0</v>
+      </c>
+      <c r="G13" s="38">
+        <v>14.0</v>
+      </c>
+      <c r="H13" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="I13" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="J13" s="38" t="s">
         <v>295</v>
       </c>
-      <c r="B13" s="23">
-        <v>10.0</v>
-      </c>
-      <c r="C13" s="23">
-        <v>13.0</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="E13" s="23">
-        <v>99.0</v>
-      </c>
-      <c r="F13" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G13" s="23">
-        <v>14.0</v>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="I13" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="J13" s="23" t="s">
+      <c r="K13" s="38" t="s">
         <v>296</v>
       </c>
-      <c r="K13" s="23" t="s">
+      <c r="L13" s="38" t="s">
         <v>297</v>
       </c>
-      <c r="L13" s="23" t="s">
+      <c r="M13" s="39" t="s">
         <v>298</v>
-      </c>
-      <c r="M13" s="23" t="s">
-        <v>299</v>
       </c>
       <c r="N13" s="33"/>
       <c r="O13" s="33"/>
@@ -6074,44 +6066,44 @@
       <c r="EU13" s="33"/>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="B14" s="23">
+      <c r="B14" s="38">
         <v>8.0</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="38">
         <v>10.0</v>
       </c>
-      <c r="D14" s="23" t="s">
+      <c r="D14" s="38" t="s">
         <v>205</v>
       </c>
-      <c r="E14" s="23">
+      <c r="E14" s="38">
         <v>26.0</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="38">
         <v>4.0</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="38">
         <v>14.0</v>
       </c>
-      <c r="H14" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="I14" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="J14" s="23" t="s">
+      <c r="H14" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="I14" s="38" t="s">
+        <v>215</v>
+      </c>
+      <c r="J14" s="38" t="s">
+        <v>299</v>
+      </c>
+      <c r="K14" s="38" t="s">
         <v>300</v>
       </c>
-      <c r="K14" s="23" t="s">
+      <c r="L14" s="38" t="s">
         <v>301</v>
       </c>
-      <c r="L14" s="23" t="s">
+      <c r="M14" s="39" t="s">
         <v>302</v>
-      </c>
-      <c r="M14" s="23" t="s">
-        <v>303</v>
       </c>
       <c r="N14" s="33"/>
       <c r="O14" s="33"/>
@@ -6253,44 +6245,44 @@
       <c r="EU14" s="33"/>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="B15" s="23">
+      <c r="A15" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="B15" s="41">
         <v>5.0</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="41">
         <v>7.0</v>
       </c>
-      <c r="D15" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="E15" s="23">
+      <c r="D15" s="41" t="s">
+        <v>213</v>
+      </c>
+      <c r="E15" s="41">
         <v>27.0</v>
       </c>
-      <c r="F15" s="23">
+      <c r="F15" s="41">
         <v>4.0</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="41">
         <v>14.0</v>
       </c>
-      <c r="H15" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="I15" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="J15" s="23" t="s">
+      <c r="H15" s="41" t="s">
+        <v>214</v>
+      </c>
+      <c r="I15" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="J15" s="41" t="s">
+        <v>303</v>
+      </c>
+      <c r="K15" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="K15" s="23" t="s">
+      <c r="L15" s="41" t="s">
         <v>305</v>
       </c>
-      <c r="L15" s="23" t="s">
+      <c r="M15" s="42" t="s">
         <v>306</v>
-      </c>
-      <c r="M15" s="23" t="s">
-        <v>307</v>
       </c>
       <c r="N15" s="33"/>
       <c r="O15" s="33"/>
@@ -6436,16 +6428,19 @@
         <v>269</v>
       </c>
       <c r="B16" s="43">
-        <v>190.0</v>
+        <f t="shared" ref="B16:C16" si="1">SUM(B7:B15)</f>
+        <v>190</v>
       </c>
       <c r="C16" s="43">
-        <v>240.0</v>
+        <f t="shared" si="1"/>
+        <v>240</v>
       </c>
       <c r="D16" s="44"/>
       <c r="E16" s="44"/>
       <c r="F16" s="44"/>
       <c r="G16" s="43">
-        <v>318.0</v>
+        <f>SUM(G7:G15)</f>
+        <v>318</v>
       </c>
       <c r="H16" s="44"/>
       <c r="I16" s="44"/>
@@ -6750,7 +6745,7 @@
         <v>228</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C18" s="44"/>
       <c r="D18" s="33"/>
@@ -6927,7 +6922,7 @@
         <v>150</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C1" s="31"/>
       <c r="D1" s="32"/>
@@ -6965,7 +6960,7 @@
         <v>79</v>
       </c>
       <c r="B3" s="29" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C3" s="44"/>
       <c r="D3" s="33"/>
@@ -7051,371 +7046,371 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="B7" s="23">
-        <v>20.0</v>
-      </c>
-      <c r="C7" s="23">
-        <v>25.0</v>
-      </c>
-      <c r="D7" s="23" t="s">
+      <c r="B7" s="48">
+        <v>15.0</v>
+      </c>
+      <c r="C7" s="48">
+        <v>19.0</v>
+      </c>
+      <c r="D7" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="E7" s="23">
+      <c r="E7" s="48">
         <v>40.0</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="48">
         <v>5.0</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="48">
         <v>30.0</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="48" t="s">
         <v>206</v>
       </c>
-      <c r="I7" s="23" t="s">
+      <c r="I7" s="48" t="s">
         <v>207</v>
       </c>
-      <c r="J7" s="23" t="s">
+      <c r="J7" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="K7" s="23" t="s">
+      <c r="K7" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="L7" s="23" t="s">
+      <c r="L7" s="48" t="s">
+        <v>310</v>
+      </c>
+      <c r="M7" s="48" t="s">
         <v>311</v>
       </c>
-      <c r="M7" s="23" t="s">
+    </row>
+    <row r="8">
+      <c r="A8" s="48" t="s">
+        <v>170</v>
+      </c>
+      <c r="B8" s="48">
+        <v>13.0</v>
+      </c>
+      <c r="C8" s="48">
+        <v>17.0</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="48">
+        <v>41.0</v>
+      </c>
+      <c r="F8" s="48">
+        <v>5.0</v>
+      </c>
+      <c r="G8" s="48">
+        <v>30.0</v>
+      </c>
+      <c r="H8" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="I8" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="J8" s="48" t="s">
         <v>312</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="B8" s="23">
+      <c r="K8" s="48" t="s">
+        <v>313</v>
+      </c>
+      <c r="L8" s="48" t="s">
+        <v>314</v>
+      </c>
+      <c r="M8" s="48" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="48" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9" s="48">
+        <v>12.0</v>
+      </c>
+      <c r="C9" s="48">
+        <v>15.0</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="48">
+        <v>42.0</v>
+      </c>
+      <c r="F9" s="48">
+        <v>5.0</v>
+      </c>
+      <c r="G9" s="48">
+        <v>30.0</v>
+      </c>
+      <c r="H9" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="I9" s="48" t="s">
+        <v>207</v>
+      </c>
+      <c r="J9" s="48" t="s">
+        <v>316</v>
+      </c>
+      <c r="K9" s="48" t="s">
+        <v>317</v>
+      </c>
+      <c r="L9" s="48" t="s">
+        <v>318</v>
+      </c>
+      <c r="M9" s="48" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="48" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="48">
+        <v>11.0</v>
+      </c>
+      <c r="C10" s="48">
+        <v>14.0</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>187</v>
+      </c>
+      <c r="E10" s="48">
+        <v>43.0</v>
+      </c>
+      <c r="F10" s="48">
+        <v>4.0</v>
+      </c>
+      <c r="G10" s="48">
+        <v>14.0</v>
+      </c>
+      <c r="H10" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="I10" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="J10" s="48" t="s">
+        <v>320</v>
+      </c>
+      <c r="K10" s="48" t="s">
+        <v>321</v>
+      </c>
+      <c r="L10" s="48" t="s">
+        <v>322</v>
+      </c>
+      <c r="M10" s="48" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="48" t="s">
+        <v>192</v>
+      </c>
+      <c r="B11" s="48">
+        <v>10.0</v>
+      </c>
+      <c r="C11" s="48">
         <v>13.0</v>
       </c>
-      <c r="C8" s="23">
-        <v>17.0</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="E8" s="23">
-        <v>41.0</v>
-      </c>
-      <c r="F8" s="23">
-        <v>5.0</v>
-      </c>
-      <c r="G8" s="23">
-        <v>30.0</v>
-      </c>
-      <c r="H8" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="J8" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="K8" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="L8" s="23" t="s">
-        <v>315</v>
-      </c>
-      <c r="M8" s="23" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="B9" s="23">
+      <c r="D11" s="48" t="s">
+        <v>193</v>
+      </c>
+      <c r="E11" s="48">
+        <v>44.0</v>
+      </c>
+      <c r="F11" s="48">
+        <v>4.0</v>
+      </c>
+      <c r="G11" s="48">
+        <v>14.0</v>
+      </c>
+      <c r="H11" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="I11" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="J11" s="48" t="s">
+        <v>324</v>
+      </c>
+      <c r="K11" s="48" t="s">
+        <v>325</v>
+      </c>
+      <c r="L11" s="48" t="s">
+        <v>326</v>
+      </c>
+      <c r="M11" s="48" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="B12" s="48">
+        <v>10.0</v>
+      </c>
+      <c r="C12" s="48">
+        <v>13.0</v>
+      </c>
+      <c r="D12" s="48" t="s">
+        <v>199</v>
+      </c>
+      <c r="E12" s="48">
+        <v>45.0</v>
+      </c>
+      <c r="F12" s="48">
+        <v>4.0</v>
+      </c>
+      <c r="G12" s="48">
+        <v>14.0</v>
+      </c>
+      <c r="H12" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="I12" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="J12" s="48" t="s">
+        <v>328</v>
+      </c>
+      <c r="K12" s="48" t="s">
+        <v>329</v>
+      </c>
+      <c r="L12" s="48" t="s">
+        <v>330</v>
+      </c>
+      <c r="M12" s="48" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="48" t="s">
+        <v>204</v>
+      </c>
+      <c r="B13" s="48">
+        <v>10.0</v>
+      </c>
+      <c r="C13" s="48">
+        <v>13.0</v>
+      </c>
+      <c r="D13" s="48" t="s">
+        <v>205</v>
+      </c>
+      <c r="E13" s="48">
+        <v>46.0</v>
+      </c>
+      <c r="F13" s="48">
+        <v>4.0</v>
+      </c>
+      <c r="G13" s="48">
+        <v>14.0</v>
+      </c>
+      <c r="H13" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="I13" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="J13" s="48" t="s">
+        <v>332</v>
+      </c>
+      <c r="K13" s="48" t="s">
+        <v>333</v>
+      </c>
+      <c r="L13" s="48" t="s">
+        <v>334</v>
+      </c>
+      <c r="M13" s="48" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="48" t="s">
+        <v>336</v>
+      </c>
+      <c r="B14" s="48">
+        <v>9.0</v>
+      </c>
+      <c r="C14" s="48">
         <v>12.0</v>
       </c>
-      <c r="C9" s="23">
-        <v>15.0</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="E9" s="23">
-        <v>42.0</v>
-      </c>
-      <c r="F9" s="23">
-        <v>5.0</v>
-      </c>
-      <c r="G9" s="23">
-        <v>30.0</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="K9" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="L9" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="M9" s="23" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="B10" s="23">
-        <v>11.0</v>
-      </c>
-      <c r="C10" s="23">
+      <c r="D14" s="48" t="s">
+        <v>221</v>
+      </c>
+      <c r="E14" s="48">
+        <v>99.0</v>
+      </c>
+      <c r="F14" s="48">
+        <v>4.0</v>
+      </c>
+      <c r="G14" s="48">
         <v>14.0</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="E10" s="23">
-        <v>43.0</v>
-      </c>
-      <c r="F10" s="23">
+      <c r="H14" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="I14" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="J14" s="48" t="s">
+        <v>337</v>
+      </c>
+      <c r="K14" s="48" t="s">
+        <v>338</v>
+      </c>
+      <c r="L14" s="48" t="s">
+        <v>339</v>
+      </c>
+      <c r="M14" s="48" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="48" t="s">
+        <v>212</v>
+      </c>
+      <c r="B15" s="48">
+        <v>6.0</v>
+      </c>
+      <c r="C15" s="48">
+        <v>8.0</v>
+      </c>
+      <c r="D15" s="48" t="s">
+        <v>213</v>
+      </c>
+      <c r="E15" s="48">
+        <v>47.0</v>
+      </c>
+      <c r="F15" s="48">
         <v>4.0</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G15" s="48">
         <v>14.0</v>
       </c>
-      <c r="H10" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="J10" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="K10" s="23" t="s">
-        <v>322</v>
-      </c>
-      <c r="L10" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="M10" s="23" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="B11" s="23">
-        <v>10.0</v>
-      </c>
-      <c r="C11" s="23">
-        <v>13.0</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11" s="23">
-        <v>44.0</v>
-      </c>
-      <c r="F11" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G11" s="23">
-        <v>14.0</v>
-      </c>
-      <c r="H11" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="J11" s="23" t="s">
-        <v>325</v>
-      </c>
-      <c r="K11" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="L11" s="23" t="s">
-        <v>327</v>
-      </c>
-      <c r="M11" s="23" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="B12" s="23">
-        <v>9.0</v>
-      </c>
-      <c r="C12" s="23">
-        <v>12.0</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="E12" s="23">
-        <v>45.0</v>
-      </c>
-      <c r="F12" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G12" s="23">
-        <v>14.0</v>
-      </c>
-      <c r="H12" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="I12" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="J12" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="K12" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="L12" s="23" t="s">
-        <v>331</v>
-      </c>
-      <c r="M12" s="23" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="B13" s="23">
-        <v>8.0</v>
-      </c>
-      <c r="C13" s="23">
-        <v>10.0</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="E13" s="23">
-        <v>46.0</v>
-      </c>
-      <c r="F13" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G13" s="23">
-        <v>14.0</v>
-      </c>
-      <c r="H13" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="I13" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="J13" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="K13" s="23" t="s">
-        <v>334</v>
-      </c>
-      <c r="L13" s="23" t="s">
-        <v>335</v>
-      </c>
-      <c r="M13" s="23" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="s">
-        <v>295</v>
-      </c>
-      <c r="B14" s="23">
-        <v>7.0</v>
-      </c>
-      <c r="C14" s="23">
-        <v>9.0</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>213</v>
-      </c>
-      <c r="E14" s="23">
-        <v>99.0</v>
-      </c>
-      <c r="F14" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G14" s="23">
-        <v>14.0</v>
-      </c>
-      <c r="H14" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="I14" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="J14" s="23" t="s">
-        <v>337</v>
-      </c>
-      <c r="K14" s="23" t="s">
-        <v>338</v>
-      </c>
-      <c r="L14" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="M14" s="23" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="B15" s="23">
-        <v>6.0</v>
-      </c>
-      <c r="C15" s="23">
-        <v>8.0</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="E15" s="23">
-        <v>47.0</v>
-      </c>
-      <c r="F15" s="23">
-        <v>4.0</v>
-      </c>
-      <c r="G15" s="23">
-        <v>14.0</v>
-      </c>
-      <c r="H15" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="I15" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="J15" s="23" t="s">
+      <c r="H15" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="I15" s="48" t="s">
+        <v>215</v>
+      </c>
+      <c r="J15" s="48" t="s">
         <v>341</v>
       </c>
-      <c r="K15" s="23" t="s">
+      <c r="K15" s="48" t="s">
         <v>342</v>
       </c>
-      <c r="L15" s="23" t="s">
+      <c r="L15" s="48" t="s">
         <v>343</v>
       </c>
-      <c r="M15" s="23" t="s">
+      <c r="M15" s="48" t="s">
         <v>344</v>
       </c>
     </row>
@@ -7424,17 +7419,17 @@
         <v>269</v>
       </c>
       <c r="B16" s="43">
-        <v>96.0</v>
+        <f t="shared" ref="B16:C16" si="1">SUM(B7:B15)</f>
+        <v>96</v>
       </c>
       <c r="C16" s="43">
-        <v>123.0</v>
+        <f t="shared" si="1"/>
+        <v>124</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
       <c r="F16" s="33"/>
-      <c r="G16" s="43">
-        <v>174.0</v>
-      </c>
+      <c r="G16" s="43"/>
       <c r="H16" s="33"/>
       <c r="I16" s="33"/>
       <c r="J16" s="33"/>
@@ -7461,7 +7456,7 @@
       <c r="A18" s="25" t="s">
         <v>228</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="49" t="s">
         <v>345</v>
       </c>
       <c r="C18" s="27"/>
@@ -7608,43 +7603,43 @@
       <c r="N5" s="33"/>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="50" t="s">
         <v>155</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="50" t="s">
         <v>158</v>
       </c>
-      <c r="E6" s="49" t="s">
+      <c r="E6" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="I6" s="22" t="s">
+      <c r="I6" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="J6" s="22" t="s">
+      <c r="J6" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="K6" s="22" t="s">
+      <c r="K6" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="22" t="s">
+      <c r="L6" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="M6" s="22" t="s">
+      <c r="M6" s="50" t="s">
         <v>163</v>
       </c>
       <c r="N6" s="33"/>
@@ -7654,15 +7649,15 @@
         <v>164</v>
       </c>
       <c r="B7" s="35">
-        <v>32.0</v>
+        <v>31.0</v>
       </c>
       <c r="C7" s="35">
-        <v>40.0</v>
+        <v>39.0</v>
       </c>
       <c r="D7" s="35" t="s">
         <v>165</v>
       </c>
-      <c r="E7" s="50">
+      <c r="E7" s="35">
         <v>50.0</v>
       </c>
       <c r="F7" s="35">
@@ -7704,7 +7699,7 @@
       <c r="D8" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="38">
         <v>51.0</v>
       </c>
       <c r="F8" s="38">
@@ -7746,7 +7741,7 @@
       <c r="D9" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="38">
         <v>52.0</v>
       </c>
       <c r="F9" s="38">
@@ -7756,10 +7751,10 @@
         <v>14.0</v>
       </c>
       <c r="H9" s="38" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I9" s="38" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J9" s="38" t="s">
         <v>354</v>
@@ -7788,7 +7783,7 @@
       <c r="D10" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="38">
         <v>53.0</v>
       </c>
       <c r="F10" s="38">
@@ -7798,10 +7793,10 @@
         <v>14.0</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J10" s="38" t="s">
         <v>358</v>
@@ -7819,19 +7814,19 @@
     </row>
     <row r="11">
       <c r="A11" s="37" t="s">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="B11" s="38">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="C11" s="38">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="D11" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="E11" s="51">
-        <v>54.0</v>
+        <v>221</v>
+      </c>
+      <c r="E11" s="38">
+        <v>55.0</v>
       </c>
       <c r="F11" s="38">
         <v>4.0</v>
@@ -7840,10 +7835,10 @@
         <v>14.0</v>
       </c>
       <c r="H11" s="38" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I11" s="38" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J11" s="38" t="s">
         <v>362</v>
@@ -7861,7 +7856,7 @@
     </row>
     <row r="12">
       <c r="A12" s="37" t="s">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="B12" s="38">
         <v>8.0</v>
@@ -7870,10 +7865,10 @@
         <v>10.0</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>213</v>
-      </c>
-      <c r="E12" s="51">
-        <v>55.0</v>
+        <v>193</v>
+      </c>
+      <c r="E12" s="38">
+        <v>54.0</v>
       </c>
       <c r="F12" s="38">
         <v>4.0</v>
@@ -7882,10 +7877,10 @@
         <v>14.0</v>
       </c>
       <c r="H12" s="38" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J12" s="38" t="s">
         <v>366</v>
@@ -7914,7 +7909,7 @@
       <c r="D13" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="38">
         <v>56.0</v>
       </c>
       <c r="F13" s="38">
@@ -7924,10 +7919,10 @@
         <v>14.0</v>
       </c>
       <c r="H13" s="38" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I13" s="38" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J13" s="38" t="s">
         <v>370</v>
@@ -7956,7 +7951,7 @@
       <c r="D14" s="38" t="s">
         <v>205</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="38">
         <v>57.0</v>
       </c>
       <c r="F14" s="38">
@@ -7966,10 +7961,10 @@
         <v>14.0</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J14" s="38" t="s">
         <v>374</v>
@@ -7987,7 +7982,7 @@
     </row>
     <row r="15">
       <c r="A15" s="40" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="B15" s="41">
         <v>5.0</v>
@@ -7996,9 +7991,9 @@
         <v>7.0</v>
       </c>
       <c r="D15" s="41" t="s">
-        <v>219</v>
-      </c>
-      <c r="E15" s="52">
+        <v>213</v>
+      </c>
+      <c r="E15" s="41">
         <v>58.0</v>
       </c>
       <c r="F15" s="41">
@@ -8008,10 +8003,10 @@
         <v>14.0</v>
       </c>
       <c r="H15" s="41" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="I15" s="41" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="J15" s="41" t="s">
         <v>378</v>
@@ -8028,21 +8023,21 @@
       <c r="N15" s="33"/>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="51" t="s">
         <v>269</v>
       </c>
-      <c r="B16" s="43">
+      <c r="B16" s="52">
         <f t="shared" ref="B16:C16" si="1">SUM(B7:B15)</f>
         <v>105</v>
       </c>
-      <c r="C16" s="43">
+      <c r="C16" s="52">
         <f t="shared" si="1"/>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D16" s="33"/>
       <c r="E16" s="33"/>
       <c r="F16" s="33"/>
-      <c r="G16" s="43">
+      <c r="G16" s="52">
         <f>SUM(G7:G15)</f>
         <v>190</v>
       </c>

--- a/excel-final/Esquema de Direccionamiento IP.xlsx
+++ b/excel-final/Esquema de Direccionamiento IP.xlsx
@@ -7826,7 +7826,7 @@
         <v>221</v>
       </c>
       <c r="E11" s="38">
-        <v>55.0</v>
+        <v>99.0</v>
       </c>
       <c r="F11" s="38">
         <v>4.0</v>
